--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -863,16 +863,16 @@
         <v>1.44</v>
       </c>
       <c r="H2" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I2" t="n">
         <v>10.5</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 01:44:27</t>
+          <t>2026-05-25 03:56:28</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>2.02</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>3.9</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
         <v>2.16</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 01:44:27</t>
+          <t>2026-05-25 03:56:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -863,16 +863,16 @@
         <v>1.44</v>
       </c>
       <c r="H2" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>10.5</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="G3" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,498 +843,1006 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1.44</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.59</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 06:08:15</t>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Kazakhstan Premier League</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Irtysh Pavlodar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FK Ulytau Zhezkazgan</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Universidad de Venezuela</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Independiente (Ecu)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Rosario Central</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F5" t="n">
         <v>1.99</v>
       </c>
-      <c r="G3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="G5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J5" t="n">
         <v>3.2</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K5" t="n">
         <v>3.6</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q5" t="n">
         <v>2.2</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-05-25 06:08:15</t>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -860,19 +860,19 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
@@ -1114,227 +1114,227 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J3" t="n">
         <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="G4" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="H4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>2.18</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>870</v>
       </c>
       <c r="J2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>870</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,36 +1351,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1.48</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,261 +1588,769 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Defensores Unidos</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Villa Dalmine</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K5" t="n">
+        <v>950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-05-25 12:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Universidad de Venezuela</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-05-25 12:48:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Independiente (Ecu)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Rosario Central</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F7" t="n">
         <v>1.99</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G7" t="n">
         <v>2.18</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H7" t="n">
         <v>4.2</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I7" t="n">
         <v>4.8</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J7" t="n">
         <v>3.2</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K7" t="n">
         <v>3.6</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q7" t="n">
         <v>2.2</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-05-25 10:35:46</t>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>600</v>
+        <v>970</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>870</v>
+        <v>970</v>
       </c>
       <c r="J2" t="n">
         <v>1.1</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
         <v>1.42</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>600</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>870</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.37</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,244 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Klubi-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,36 +1859,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.48</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -2118,239 +2118,493 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Universidad de Venezuela</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:59:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Independiente (Ecu)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Rosario Central</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>1.99</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G8" t="n">
         <v>2.18</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H8" t="n">
         <v>4.2</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>4.8</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="J8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.6</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.2</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-05-25 12:48:21</t>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.42</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>600</v>
+        <v>970</v>
       </c>
       <c r="H3" t="n">
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>870</v>
+        <v>970</v>
       </c>
       <c r="J3" t="n">
         <v>1.1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>3.55</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="H4" t="n">
         <v>2.1</v>
@@ -1398,7 +1398,7 @@
         <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
@@ -1413,7 +1413,7 @@
         <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W4" t="n">
         <v>1.33</v>
@@ -1476,7 +1476,7 @@
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.4</v>
+        <v>3.15</v>
       </c>
       <c r="AR4" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
         <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="AW4" t="n">
         <v>16.5</v>
@@ -1506,22 +1506,22 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG4" t="n">
         <v>11.5</v>
@@ -1530,19 +1530,19 @@
         <v>3.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BN4" t="n">
         <v>7</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BT4" t="n">
         <v>5</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -1631,22 +1631,22 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
@@ -1655,184 +1655,184 @@
         <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -1885,22 +1885,22 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
@@ -1909,184 +1909,184 @@
         <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,234 +2113,234 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB7" t="n">
         <v>8.4</v>
       </c>
-      <c r="I7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -2372,239 +2372,493 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Universidad de Venezuela</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-05-25 17:08:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Independiente (Ecu)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Rosario Central</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>1.99</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G9" t="n">
         <v>2.18</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H9" t="n">
         <v>4.2</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>4.8</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="J9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.2</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-05-25 14:59:08</t>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,13 +860,13 @@
         <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="H2" t="n">
         <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J2" t="n">
         <v>1.1</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
         <v>1.42</v>
@@ -896,13 +896,13 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.02</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="H3" t="n">
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J3" t="n">
         <v>1.1</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
         <v>1.37</v>
@@ -1150,13 +1150,13 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.02</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Klubi-04</t>
+          <t>FC Urartu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>FC Noah</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.84</v>
+        <v>1.24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>1.23</v>
       </c>
       <c r="T4" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,33 +1605,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>FC Pyunik</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>FC Van Yerevan</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,28 +1643,28 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="R5" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1835,21 +1835,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Klubi-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,234 +2113,234 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.02</v>
+        <v>600</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>870</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>1.52</v>
       </c>
       <c r="T7" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>85</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>60</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>70</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,234 +2367,234 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.49</v>
+        <v>600</v>
       </c>
       <c r="H8" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>9.6</v>
+        <v>870</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>1.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,234 +2621,234 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1.99</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,515 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Universidad de Venezuela</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>140</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>46</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="G2" t="n">
         <v>990</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="I2" t="n">
         <v>990</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1276,65 +1276,65 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1395,7 +1395,7 @@
         <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q4" t="n">
         <v>1.24</v>
@@ -1404,7 +1404,7 @@
         <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1784,65 +1784,65 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
         <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
         <v>3.85</v>
@@ -1903,13 +1903,13 @@
         <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
         <v>3.3</v>
@@ -1924,7 +1924,7 @@
         <v>1.78</v>
       </c>
       <c r="W6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
         <v>18.5</v>
@@ -1933,7 +1933,7 @@
         <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA6" t="n">
         <v>34</v>
@@ -1969,7 +1969,7 @@
         <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1984,7 +1984,7 @@
         <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.4</v>
+        <v>3.15</v>
       </c>
       <c r="AR6" t="n">
         <v>10</v>
@@ -1999,7 +1999,7 @@
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
         <v>16.5</v>
@@ -2014,22 +2014,22 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC6" t="n">
         <v>3.9</v>
       </c>
-      <c r="BB6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>30</v>
-      </c>
       <c r="BD6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4</v>
       </c>
-      <c r="BE6" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BG6" t="n">
         <v>11.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="G7" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I7" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2166,7 +2166,7 @@
         <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,7 +2175,7 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2292,55 +2292,55 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J8" t="n">
         <v>1.1</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2546,55 +2546,55 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>1.99</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
         <v>4.6</v>
@@ -2662,7 +2662,7 @@
         <v>3.35</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P9" t="n">
         <v>1.79</v>
@@ -2686,7 +2686,7 @@
         <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
         <v>11.5</v>
@@ -2698,7 +2698,7 @@
         <v>32</v>
       </c>
       <c r="AA9" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB9" t="n">
         <v>8.6</v>
@@ -2725,7 +2725,7 @@
         <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
         <v>22</v>
@@ -2764,7 +2764,7 @@
         <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2779,10 +2779,10 @@
         <v>65</v>
       </c>
       <c r="BB9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
         <v>38</v>
@@ -2791,7 +2791,7 @@
         <v>110</v>
       </c>
       <c r="BF9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG9" t="n">
         <v>70</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>1.44</v>
       </c>
       <c r="G10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H10" t="n">
         <v>8.4</v>
@@ -2904,16 +2904,16 @@
         <v>4.8</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
@@ -2928,13 +2928,13 @@
         <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V10" t="n">
         <v>1.11</v>
@@ -2949,7 +2949,7 @@
         <v>34</v>
       </c>
       <c r="Z10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AA10" t="n">
         <v>350</v>
@@ -2961,7 +2961,7 @@
         <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
         <v>160</v>
@@ -2973,7 +2973,7 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>130</v>
@@ -3000,13 +3000,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
@@ -3018,7 +3018,7 @@
         <v>24</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AX10" t="n">
         <v>7.6</v>
@@ -3030,7 +3030,7 @@
         <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
         <v>9.6</v>
@@ -3039,40 +3039,40 @@
         <v>12</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>140</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="n">
         <v>4.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BJ10" t="n">
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="BN10" t="n">
         <v>4.1</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BP10" t="n">
         <v>8.800000000000001</v>
@@ -3084,35 +3084,35 @@
         <v>25</v>
       </c>
       <c r="BS10" t="n">
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
         <v>13</v>
       </c>
       <c r="BU10" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10" t="n">
         <v>14.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.96</v>
       </c>
       <c r="G11" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="n">
         <v>4.2</v>
@@ -3161,16 +3161,16 @@
         <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
         <v>1.7</v>
@@ -3179,194 +3179,194 @@
         <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V11" t="n">
         <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF11" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AK11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA11" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ11" t="n">
+      <c r="BB11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF11" t="n">
         <v>13.5</v>
       </c>
-      <c r="BA11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP11" t="n">
         <v>15.5</v>
       </c>
-      <c r="BK11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN11" t="n">
+      <c r="BQ11" t="n">
         <v>6.2</v>
       </c>
-      <c r="BO11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BR11" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BS11" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="BT11" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU11" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW11" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BZ11" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="CA11" t="n">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,33 +843,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FK Altay</t>
+          <t>Dalian Yingbo II</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Astana</t>
+          <t>Shandong Taishan B</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
         <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -905,7 +905,7 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
@@ -1073,21 +1073,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,33 +1097,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>Xian Chongde Ronghai</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Ulytau Zhezkazgan</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
         <v>990</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
         <v>990</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1159,10 +1159,10 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1327,21 +1327,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Armenian Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,30 +1351,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Urartu</t>
+          <t>Xiamen Feilu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Noah</t>
+          <t>Jiangxi Lushan</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
         <v>990</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
         <v>1.02</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="R4" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1581,21 +1581,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Armenian Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,30 +1605,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Pyunik</t>
+          <t>Changchun Xidu</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Van Yerevan</t>
+          <t>Beijing Tech FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
         <v>990</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
         <v>1.02</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1835,21 +1835,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Klubi-04</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.55</v>
+        <v>1.29</v>
       </c>
       <c r="G6" t="n">
-        <v>3.95</v>
+        <v>990</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>990</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>1.42</v>
       </c>
       <c r="T6" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.78</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,33 +2113,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Haimen Codion</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Shanghai Second</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
         <v>990</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
         <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2154,19 +2154,19 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="R7" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,7 +2175,7 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Guangdong Mingtu</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2393,7 +2393,7 @@
         <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>FK Ulytau Zhezkazgan</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.99</v>
+        <v>1.26</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>990</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>1.26</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>1.36</v>
       </c>
       <c r="O9" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.22</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.93</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,498 +2875,2276 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>FC Pyunik</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>FC Van Yerevan</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="G10" t="n">
-        <v>1.48</v>
+        <v>990</v>
       </c>
       <c r="H10" t="n">
-        <v>8.4</v>
+        <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>9.6</v>
+        <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>4.8</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>1.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>1.23</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>2.76</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Armenian Premier League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FC Urartu</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FC Noah</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G11" t="n">
+        <v>990</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I11" t="n">
+        <v>990</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-05-25 23:36:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Czech 1 Liga</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SK Artis Brno</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Slovacko</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="K12" t="n">
+        <v>500</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-05-25 23:36:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Finnish Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Klubi-04</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PK-35 RY</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>10</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-05-25 23:36:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Argentino de Quilmes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Excursionistas</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G14" t="n">
+        <v>990</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I14" t="n">
+        <v>990</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-05-25 23:36:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Defensores Unidos</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Villa Dalmine</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G15" t="n">
+        <v>990</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>990</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>950</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-05-25 23:36:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-25 23:36:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Universidad de Venezuela</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-25 23:36:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Independiente (Ecu)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Rosario Central</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="F18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H18" t="n">
         <v>4.2</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I18" t="n">
         <v>4.8</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L18" t="n">
         <v>1.39</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M18" t="n">
         <v>1.09</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N18" t="n">
         <v>3.1</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O18" t="n">
         <v>1.39</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P18" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q18" t="n">
         <v>2.2</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R18" t="n">
         <v>1.26</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S18" t="n">
         <v>4</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T18" t="n">
         <v>1.94</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U18" t="n">
         <v>1.88</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V18" t="n">
         <v>1.26</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="W18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X18" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y18" t="n">
         <v>14</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="Z18" t="n">
         <v>34</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA18" t="n">
         <v>140</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AB18" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AC18" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AD18" t="n">
         <v>19</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AE18" t="n">
         <v>70</v>
       </c>
-      <c r="AF11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="AF18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AH18" t="n">
         <v>23</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AI18" t="n">
         <v>80</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AJ18" t="n">
         <v>25</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AK18" t="n">
         <v>25</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AL18" t="n">
         <v>48</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AM18" t="n">
         <v>220</v>
       </c>
-      <c r="AN11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO11" t="n">
+      <c r="AN18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO18" t="n">
         <v>110</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AP18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AQ18" t="n">
         <v>11</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AR18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT18" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA18" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX11" t="n">
+      <c r="BB18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AY11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE11" t="n">
+      <c r="BN18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT18" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG11" t="n">
+      <c r="BU18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA18" t="n">
         <v>8</v>
       </c>
-      <c r="BH11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>34</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>8</v>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>2026-05-25 21:27:12</t>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>990</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1150,7 +1150,7 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
         <v>1.49</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q5" t="n">
         <v>1.48</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="G6" t="n">
         <v>990</v>
       </c>
       <c r="H6" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="I6" t="n">
         <v>990</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2160,7 +2160,7 @@
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="G9" t="n">
         <v>990</v>
       </c>
       <c r="H9" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="n">
         <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2683,7 +2683,7 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FC Pyunik</t>
+          <t>FC Urartu</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Van Yerevan</t>
+          <t>FC Noah</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2916,10 +2916,10 @@
         <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q10" t="n">
         <v>1.23</v>
@@ -2928,7 +2928,7 @@
         <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FC Urartu</t>
+          <t>FC Pyunik</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Noah</t>
+          <t>FC Van Yerevan</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3170,10 +3170,10 @@
         <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q11" t="n">
         <v>1.23</v>
@@ -3182,7 +3182,7 @@
         <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Finnish Kakkonen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,36 +3383,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>VPS Vaasa II</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Slovacko</t>
+          <t>FCV</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="P12" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3613,21 +3613,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Klubi-04</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>Slovacko</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="G13" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
         <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
         <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,244 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Klubi-04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.14</v>
+        <v>3.55</v>
       </c>
       <c r="G14" t="n">
-        <v>990</v>
+        <v>3.85</v>
       </c>
       <c r="H14" t="n">
-        <v>1.13</v>
+        <v>2.14</v>
       </c>
       <c r="I14" t="n">
-        <v>990</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>1.05</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.07</v>
+        <v>1.78</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -4150,22 +4150,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="G15" t="n">
         <v>990</v>
       </c>
       <c r="H15" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="I15" t="n">
         <v>990</v>
@@ -4207,7 +4207,7 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
         <v>1.01</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,234 +4399,234 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.99</v>
+        <v>1.17</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>990</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>1.19</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6</v>
+        <v>990</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.93</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,244 +4653,244 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>1.99</v>
       </c>
       <c r="G17" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB17" t="n">
         <v>8.4</v>
       </c>
-      <c r="I17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="AC17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH17" t="n">
         <v>21</v>
       </c>
-      <c r="Y17" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>350</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AI17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
         <v>12</v>
       </c>
-      <c r="AD17" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="BZ17" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -4912,184 +4912,184 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.93</v>
       </c>
-      <c r="G18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="U18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH18" t="n">
         <v>4.2</v>
       </c>
-      <c r="I18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF18" t="n">
+      <c r="BI18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ18" t="n">
         <v>12</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>11</v>
       </c>
       <c r="BK18" t="n">
         <v>5.4</v>
@@ -5098,53 +5098,1323 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-26 01:46:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP19" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BN18" t="n">
+      <c r="AQ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN19" t="n">
         <v>4.7</v>
       </c>
-      <c r="BO18" t="n">
+      <c r="BO19" t="n">
         <v>3.5</v>
       </c>
-      <c r="BP18" t="n">
+      <c r="BP19" t="n">
         <v>15.5</v>
       </c>
-      <c r="BQ18" t="n">
+      <c r="BQ19" t="n">
         <v>6.2</v>
       </c>
-      <c r="BR18" t="n">
+      <c r="BR19" t="n">
         <v>34</v>
       </c>
-      <c r="BS18" t="n">
+      <c r="BS19" t="n">
         <v>8</v>
       </c>
-      <c r="BT18" t="n">
+      <c r="BT19" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="BU19" t="n">
         <v>4.6</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="BV19" t="n">
         <v>46</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="BW19" t="n">
         <v>8.6</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="BX19" t="n">
         <v>60</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="BY19" t="n">
         <v>9</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="BZ19" t="n">
         <v>34</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CA19" t="n">
         <v>8</v>
       </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>2026-05-25 23:36:26</t>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-05-26 01:46:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Deportivo La Guaira</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H20" t="n">
+        <v>20</v>
+      </c>
+      <c r="I20" t="n">
+        <v>27</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>260</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>510</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>340</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>360</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>22</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-26 01:46:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-26 01:46:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-26 01:46:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>23</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
         <v>1.55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>990</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1150,7 +1150,7 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>990</v>
       </c>
       <c r="J5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q5" t="n">
         <v>1.48</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,28 +1864,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FK Altay</t>
+          <t>Guangzhou Alpha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Astana</t>
+          <t>Ganzhou Ruishi FC</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1900,28 +1900,28 @@
         <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2038,72 +2038,72 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,33 +2113,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Haimen Codion</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shanghai Second</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>990</v>
+        <v>3.95</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="I7" t="n">
         <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2154,19 +2154,19 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2343,14 +2343,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns II</t>
+          <t>Haimen Codion</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Guangdong Mingtu</t>
+          <t>Shanghai Second</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2393,7 +2393,7 @@
         <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2408,19 +2408,19 @@
         <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,33 +2621,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Ulytau Zhezkazgan</t>
+          <t>Guangdong Mingtu</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
         <v>990</v>
       </c>
       <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
         <v>1.09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>990</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.03</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="P9" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2686,7 +2686,7 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2851,21 +2851,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Armenian Premier League</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,33 +2875,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FC Urartu</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Noah</t>
+          <t>FK Ulytau Zhezkazgan</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="G10" t="n">
         <v>990</v>
       </c>
       <c r="H10" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="I10" t="n">
         <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
         <v>950</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="R10" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2940,7 +2940,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FC Pyunik</t>
+          <t>FC Urartu</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Van Yerevan</t>
+          <t>FC Noah</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3170,10 +3170,10 @@
         <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" t="n">
         <v>1.23</v>
@@ -3182,7 +3182,7 @@
         <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Finnish Kakkonen</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,33 +3383,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VPS Vaasa II</t>
+          <t>FC Pyunik</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FCV</t>
+          <t>FC Van Yerevan</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
@@ -3424,19 +3424,19 @@
         <v>1.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3613,21 +3613,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Finnish Kakkonen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,60 +3637,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>VPS Vaasa II</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Slovacko</t>
+          <t>FCV</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>2.92</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="P13" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>2.92</v>
+        <v>1.05</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3699,10 +3699,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3867,21 +3867,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Klubi-04</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>Slovacko</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="G14" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>950</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AB14" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AG14" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ14" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AO14" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AP14" t="n">
-        <v>11</v>
+        <v>2.26</v>
       </c>
       <c r="AQ14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB14" t="n">
         <v>3.2</v>
       </c>
-      <c r="AR14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>2.56</v>
       </c>
       <c r="BF14" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>11.5</v>
+        <v>2.36</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>6</v>
+        <v>1.35</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="BN14" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.58</v>
+        <v>1.08</v>
       </c>
       <c r="BT14" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>8</v>
+        <v>1.11</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>10.5</v>
+        <v>1.11</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>10</v>
+        <v>1.08</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,244 +4145,244 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Klubi-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.17</v>
+        <v>3.5</v>
       </c>
       <c r="G15" t="n">
-        <v>990</v>
+        <v>3.95</v>
       </c>
       <c r="H15" t="n">
-        <v>1.17</v>
+        <v>2.14</v>
       </c>
       <c r="I15" t="n">
-        <v>990</v>
+        <v>2.32</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.08</v>
+        <v>1.77</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -4404,22 +4404,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
         <v>990</v>
       </c>
       <c r="H16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I16" t="n">
         <v>990</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,234 +4653,234 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.99</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>990</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>1.22</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>990</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.93</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,244 +4907,244 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="H18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC18" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="AD18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>21</v>
       </c>
-      <c r="Y18" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z18" t="n">
+      <c r="AK18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO18" t="n">
         <v>80</v>
       </c>
-      <c r="AA18" t="n">
-        <v>310</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AP18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
         <v>12</v>
       </c>
-      <c r="AD18" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BZ18" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -5166,184 +5166,184 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="G19" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W19" t="n">
         <v>3.1</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="X19" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="Z19" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AA19" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE19" t="n">
         <v>140</v>
       </c>
-      <c r="AB19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>19</v>
       </c>
-      <c r="AE19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="BA19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC19" t="n">
         <v>12</v>
       </c>
-      <c r="AG19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY19" t="n">
+      <c r="BD19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE19" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BF19" t="n">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI19" t="n">
         <v>3.2</v>
       </c>
-      <c r="BI19" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BJ19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK19" t="n">
         <v>5.4</v>
@@ -5352,53 +5352,53 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ19" t="n">
         <v>4.7</v>
       </c>
-      <c r="BO19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BR19" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BS19" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="CA19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -5415,244 +5415,244 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.17</v>
+        <v>1.93</v>
       </c>
       <c r="G20" t="n">
-        <v>1.18</v>
+        <v>2.12</v>
       </c>
       <c r="H20" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS20" t="n">
         <v>8.6</v>
       </c>
-      <c r="K20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="AT20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU20" t="n">
         <v>5.8</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="X20" t="n">
+      <c r="BV20" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ20" t="n">
         <v>32</v>
       </c>
-      <c r="Y20" t="n">
-        <v>70</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>260</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>510</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>340</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>360</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS20" t="n">
+      <c r="CA20" t="n">
         <v>8</v>
       </c>
-      <c r="BT20" t="n">
-        <v>22</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>4.8</v>
-      </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -5674,239 +5674,239 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.88</v>
+        <v>1.15</v>
       </c>
       <c r="G21" t="n">
-        <v>1.99</v>
+        <v>1.18</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
+        <v>11</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="X21" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>260</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>370</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN21" t="n">
         <v>3.7</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU21" t="n">
+      <c r="BO21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>23</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="CA21" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>38</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>11</v>
-      </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -5928,239 +5928,239 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="G22" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="I22" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="U22" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="V22" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="X22" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AA22" t="n">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="AB22" t="n">
         <v>6.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AF22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AJ22" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="AN22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="AP22" t="n">
         <v>8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD22" t="n">
         <v>40</v>
       </c>
-      <c r="AS22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX22" t="n">
+      <c r="BE22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ22" t="n">
         <v>8</v>
       </c>
-      <c r="AY22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>16</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS22" t="n">
         <v>11.5</v>
       </c>
       <c r="BT22" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA22" t="n">
         <v>11.5</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -6182,239 +6182,493 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.56</v>
+        <v>1.79</v>
       </c>
       <c r="G23" t="n">
-        <v>2.7</v>
+        <v>1.81</v>
       </c>
       <c r="H23" t="n">
-        <v>2.74</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>2.84</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="L23" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>2.62</v>
       </c>
       <c r="O23" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.76</v>
+        <v>2.58</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="S23" t="n">
-        <v>2.78</v>
+        <v>5.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="V23" t="n">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="W23" t="n">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="X23" t="n">
-        <v>19.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y23" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="AA23" t="n">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="AB23" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AE23" t="n">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="AF23" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AG23" t="n">
         <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AI23" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="AJ23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR23" t="n">
         <v>40</v>
       </c>
-      <c r="AK23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AS23" t="n">
-        <v>38</v>
+        <v>8.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU23" t="n">
         <v>7.4</v>
       </c>
       <c r="AV23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-26 03:56:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW24" t="n">
         <v>25</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AX24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF24" t="n">
         <v>16</v>
       </c>
-      <c r="AY23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB23" t="n">
+      <c r="BG24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BX24" t="n">
         <v>34</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BY24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BZ24" t="n">
         <v>23</v>
       </c>
-      <c r="BD23" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>18</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>2026-05-26 01:46:10</t>
+      <c r="CA24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -887,7 +887,7 @@
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q2" t="n">
         <v>1.55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="G3" t="n">
-        <v>990</v>
+        <v>2.56</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I3" t="n">
-        <v>990</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>1.49</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
-        <v>990</v>
+        <v>2.94</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="O4" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.49</v>
+        <v>2.14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>1.49</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -1619,220 +1619,220 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>990</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
-        <v>990</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="K5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y5" t="n">
         <v>950</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
         <v>1.57</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="G7" t="n">
         <v>3.95</v>
@@ -2139,7 +2139,7 @@
         <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>2.08</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Q7" t="n">
         <v>1.42</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J9" t="n">
         <v>1.09</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="G10" t="n">
         <v>990</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
         <v>1.36</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>990</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="O11" t="n">
         <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S11" t="n">
-        <v>1.24</v>
+        <v>2.58</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>990</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
@@ -3430,13 +3430,13 @@
         <v>1.09</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="R12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S12" t="n">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H13" t="n">
         <v>1.04</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>Klubi-04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Slovacko</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="H14" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="I14" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.35</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.47</v>
-      </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AA14" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF14" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.26</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.3</v>
+        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.1</v>
+        <v>19.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.22</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.42</v>
+        <v>16.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.38</v>
+        <v>19.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.24</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.56</v>
+        <v>4.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.36</v>
+        <v>11.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.35</v>
+        <v>6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.08</v>
+        <v>3.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.11</v>
+        <v>8</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.08</v>
+        <v>10</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,239 +4150,239 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Klubi-04</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>Slovacko</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="G15" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="H15" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="I15" t="n">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
         <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="X15" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA15" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AB15" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF15" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ15" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AK15" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AL15" t="n">
         <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AO15" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>2.26</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.800000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>10.5</v>
+        <v>2.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>19.5</v>
+        <v>3.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>2.22</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.199999999999999</v>
+        <v>2.18</v>
       </c>
       <c r="AW15" t="n">
-        <v>16.5</v>
+        <v>2.42</v>
       </c>
       <c r="AX15" t="n">
-        <v>19.5</v>
+        <v>2.38</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>2.24</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12.5</v>
+        <v>2.3</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG15" t="n">
-        <v>11.5</v>
+        <v>2.36</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.7</v>
+        <v>1.35</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="BN15" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>10.5</v>
+        <v>1.08</v>
       </c>
       <c r="BT15" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BV15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.4</v>
+        <v>1.11</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.6</v>
+        <v>1.11</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="G16" t="n">
         <v>990</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="I16" t="n">
         <v>990</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="G17" t="n">
         <v>990</v>
       </c>
       <c r="H17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="I17" t="n">
         <v>990</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.4</v>
@@ -4954,19 +4954,19 @@
         <v>1.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T18" t="n">
         <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V18" t="n">
         <v>1.28</v>
@@ -5005,55 +5005,55 @@
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
         <v>80</v>
       </c>
       <c r="AJ18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
         <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
         <v>17</v>
       </c>
       <c r="AO18" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS18" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="AT18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU18" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU18" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AV18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW18" t="n">
         <v>55</v>
       </c>
       <c r="AX18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
         <v>10</v>
@@ -5062,22 +5062,22 @@
         <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB18" t="n">
         <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE18" t="n">
         <v>110</v>
       </c>
       <c r="BF18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG18" t="n">
         <v>70</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>1.48</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="K19" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="O19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.24</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.47</v>
-      </c>
       <c r="S19" t="n">
-        <v>2.68</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,244 +5415,244 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.09</v>
       </c>
-      <c r="N20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.39</v>
-      </c>
       <c r="P20" t="n">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>4.1</v>
+        <v>1.09</v>
       </c>
       <c r="T20" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP20" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV20" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -5669,244 +5669,244 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="G21" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="H21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X21" t="n">
         <v>21</v>
       </c>
-      <c r="I21" t="n">
-        <v>26</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="Y21" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR21" t="n">
         <v>9</v>
       </c>
-      <c r="K21" t="n">
-        <v>11</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="X21" t="n">
-        <v>38</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>260</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="AS21" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
+      <c r="AT21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX21" t="n">
         <v>7.6</v>
       </c>
-      <c r="AG21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>370</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>430</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ21" t="n">
+      <c r="AY21" t="n">
         <v>8</v>
       </c>
-      <c r="AR21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD21" t="n">
         <v>8</v>
       </c>
       <c r="BE21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
         <v>9</v>
       </c>
-      <c r="BF21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>23</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>10</v>
-      </c>
       <c r="BZ21" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="CA21" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -5923,244 +5923,244 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="G22" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="P22" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="X22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF22" t="n">
         <v>12</v>
       </c>
-      <c r="Y22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>11</v>
-      </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>23</v>
       </c>
       <c r="AK22" t="n">
         <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM22" t="n">
         <v>220</v>
       </c>
       <c r="AN22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO22" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AP22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW22" t="n">
         <v>8</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR22" t="n">
+      <c r="AX22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG22" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="BH22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
         <v>10</v>
       </c>
-      <c r="AT22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>15</v>
-      </c>
       <c r="BN22" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BP22" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BR22" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS22" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU22" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW22" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY22" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BZ22" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="CA22" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -6182,239 +6182,239 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.79</v>
+        <v>1.16</v>
       </c>
       <c r="G23" t="n">
-        <v>1.81</v>
+        <v>1.18</v>
       </c>
       <c r="H23" t="n">
+        <v>19</v>
+      </c>
+      <c r="I23" t="n">
+        <v>25</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>11</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W23" t="n">
         <v>6</v>
       </c>
-      <c r="I23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.22</v>
-      </c>
       <c r="X23" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="Y23" t="n">
-        <v>16.5</v>
+        <v>65</v>
       </c>
       <c r="Z23" t="n">
-        <v>46</v>
+        <v>250</v>
       </c>
       <c r="AA23" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.4</v>
+        <v>25</v>
       </c>
       <c r="AD23" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AE23" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AF23" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AI23" t="n">
-        <v>160</v>
+        <v>330</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AK23" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="AL23" t="n">
         <v>65</v>
       </c>
       <c r="AM23" t="n">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="AN23" t="n">
-        <v>22</v>
+        <v>3.55</v>
       </c>
       <c r="AO23" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV23" t="n">
         <v>8</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>23</v>
-      </c>
       <c r="AW23" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX23" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="BA23" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BB23" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="BC23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT23" t="n">
         <v>22</v>
       </c>
-      <c r="BD23" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG23" t="n">
+      <c r="BU23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ23" t="n">
         <v>8.4</v>
       </c>
-      <c r="BH23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA23" t="n">
-        <v>9.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -6436,239 +6436,747 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="G24" t="n">
-        <v>2.72</v>
+        <v>2.02</v>
       </c>
       <c r="H24" t="n">
-        <v>2.74</v>
+        <v>4.7</v>
       </c>
       <c r="I24" t="n">
-        <v>2.84</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
       <c r="O24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.24</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.54</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="X24" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>23</v>
       </c>
-      <c r="AA24" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF24" t="n">
+      <c r="AK24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN24" t="n">
         <v>21</v>
       </c>
-      <c r="AG24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>970</v>
-      </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AP24" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="AT24" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AU24" t="n">
         <v>7.2</v>
       </c>
       <c r="AV24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ24" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="BK24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-26 06:06:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-05-26 06:06:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW26" t="n">
         <v>25</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AX26" t="n">
         <v>15.5</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="AY26" t="n">
         <v>11</v>
       </c>
-      <c r="AZ24" t="n">
+      <c r="AZ26" t="n">
         <v>14</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BA26" t="n">
         <v>29</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BB26" t="n">
         <v>34</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BC26" t="n">
         <v>23</v>
       </c>
-      <c r="BD24" t="n">
+      <c r="BD26" t="n">
         <v>30</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BE26" t="n">
         <v>55</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BF26" t="n">
         <v>16</v>
       </c>
-      <c r="BG24" t="n">
-        <v>18</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI24" t="n">
+      <c r="BG26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI26" t="n">
         <v>2.98</v>
       </c>
-      <c r="BJ24" t="n">
+      <c r="BJ26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
         <v>9.6</v>
       </c>
-      <c r="BK24" t="n">
+      <c r="BN26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO26" t="n">
         <v>4.3</v>
       </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS24" t="n">
+      <c r="BP26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT26" t="n">
         <v>6.4</v>
       </c>
-      <c r="BT24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU24" t="n">
+      <c r="BU26" t="n">
         <v>4.6</v>
       </c>
-      <c r="BV24" t="n">
+      <c r="BV26" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ26" t="n">
         <v>23</v>
       </c>
-      <c r="BW24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="CB24" t="inlineStr">
-        <is>
-          <t>2026-05-26 03:56:23</t>
+      <c r="CA26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,16 +860,16 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -887,16 +887,16 @@
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N3" t="n">
         <v>3.15</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
         <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AP3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT3" t="n">
         <v>3.6</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AU3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB3" t="n">
+      <c r="BD3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF3" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG3" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW3" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>2.18</v>
       </c>
       <c r="BX3" t="n">
         <v>55</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.22</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J4" t="n">
         <v>2.88</v>
       </c>
-      <c r="I4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
         <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
         <v>19.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL4" t="n">
         <v>55</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AM4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO4" t="n">
         <v>46</v>
       </c>
-      <c r="AL4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>70</v>
-      </c>
       <c r="AP4" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AQ4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT4" t="n">
         <v>3.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.35</v>
       </c>
       <c r="AU4" t="n">
         <v>3.15</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AX4" t="n">
         <v>4</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BA4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5</v>
-      </c>
       <c r="BF4" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.88</v>
+        <v>4.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BN4" t="n">
         <v>5.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.62</v>
+        <v>3.55</v>
       </c>
       <c r="BP4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.06</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="BT4" t="n">
         <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.66</v>
+        <v>3.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
         <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>3.5</v>
@@ -1643,7 +1643,7 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="O5" t="n">
         <v>1.48</v>
@@ -1667,7 +1667,7 @@
         <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
         <v>1.8</v>
@@ -1676,13 +1676,13 @@
         <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB5" t="n">
         <v>8.4</v>
@@ -1694,19 +1694,19 @@
         <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
         <v>34</v>
@@ -1727,58 +1727,58 @@
         <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AQ5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY5" t="n">
         <v>3.35</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AZ5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF5" t="n">
         <v>3.9</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH5" t="n">
         <v>2.9</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -1873,112 +1873,112 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I6" t="n">
-        <v>110</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>1.28</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="P6" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP6" t="n">
         <v>1.03</v>
@@ -2029,22 +2029,22 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG6" t="n">
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,28 +2053,28 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="n">
-        <v>3.95</v>
+        <v>990</v>
       </c>
       <c r="H7" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="I7" t="n">
         <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>2.08</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G8" t="n">
         <v>990</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="n">
         <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G9" t="n">
         <v>990</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="n">
         <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2659,13 +2659,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
         <v>1.02</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q9" t="n">
         <v>1.51</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="G10" t="n">
         <v>990</v>
@@ -2928,7 +2928,7 @@
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>990</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.24</v>
       </c>
       <c r="P11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S11" t="n">
         <v>1.24</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.58</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>990</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
@@ -3421,16 +3421,16 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="R12" t="n">
         <v>1.09</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J13" t="n">
         <v>1.03</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Klubi-04</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>Slovacko</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G14" t="n">
         <v>3.5</v>
       </c>
-      <c r="G14" t="n">
-        <v>3.85</v>
-      </c>
       <c r="H14" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AB14" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AG14" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ14" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AO14" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AP14" t="n">
-        <v>11</v>
+        <v>2.26</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.800000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.5</v>
+        <v>2.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>19.5</v>
+        <v>3.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>10.5</v>
+        <v>2.22</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.199999999999999</v>
+        <v>2.18</v>
       </c>
       <c r="AW14" t="n">
-        <v>16.5</v>
+        <v>2.42</v>
       </c>
       <c r="AX14" t="n">
-        <v>19.5</v>
+        <v>2.38</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>2.24</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.5</v>
+        <v>2.3</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>11.5</v>
+        <v>2.36</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>6</v>
+        <v>1.35</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.68</v>
+        <v>1.1</v>
       </c>
       <c r="BN14" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>3.5</v>
+        <v>1.08</v>
       </c>
       <c r="BT14" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>8</v>
+        <v>1.11</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>10.5</v>
+        <v>1.11</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>10</v>
+        <v>1.08</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>Klubi-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Slovacko</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="G15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.75</v>
       </c>
-      <c r="H15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="W15" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB15" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AG15" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ15" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AK15" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AL15" t="n">
         <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN15" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AO15" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.26</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.3</v>
+        <v>10.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.1</v>
+        <v>19.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.22</v>
+        <v>10.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.42</v>
+        <v>16.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.38</v>
+        <v>19.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>2.24</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.56</v>
+        <v>4.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.36</v>
+        <v>11.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.35</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.08</v>
+        <v>3.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.11</v>
+        <v>8</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.08</v>
+        <v>10</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,33 +4399,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="H16" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -4437,28 +4437,28 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O16" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="P16" t="n">
         <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R16" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
@@ -4521,52 +4521,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -4578,72 +4578,72 @@
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,126 +4653,126 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.23</v>
+        <v>2.46</v>
       </c>
       <c r="G17" t="n">
-        <v>990</v>
+        <v>2.82</v>
       </c>
       <c r="H17" t="n">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="I17" t="n">
-        <v>990</v>
+        <v>2.92</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.44</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="n">
         <v>1.01</v>
@@ -4829,75 +4829,75 @@
         <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="G18" t="n">
-        <v>2.02</v>
+        <v>1.34</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I18" t="n">
+        <v>13</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X18" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN18" t="n">
         <v>4.5</v>
       </c>
-      <c r="J18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="BO18" t="n">
         <v>3.3</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>70</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK18" t="n">
+      <c r="BP18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BU18" t="n">
         <v>6.6</v>
       </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>6</v>
-      </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,28 +5199,28 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -5340,72 +5340,72 @@
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,36 +5415,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5453,28 +5453,28 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -5594,72 +5594,72 @@
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1.47</v>
+        <v>110</v>
       </c>
       <c r="H21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>9.4</v>
+        <v>110</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>1.02</v>
       </c>
       <c r="K21" t="n">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="O21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P21" t="n">
         <v>1.24</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q21" t="n">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>1.34</v>
       </c>
       <c r="T21" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP21" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR21" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="U22" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="X22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA22" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>80</v>
       </c>
       <c r="AJ22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR22" t="n">
         <v>25</v>
       </c>
-      <c r="AK22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO22" t="n">
+      <c r="AS22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE22" t="n">
         <v>110</v>
       </c>
-      <c r="AP22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU22" t="n">
+      <c r="BF22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK22" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW22" t="n">
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ22" t="n">
         <v>8</v>
       </c>
-      <c r="AX22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BR22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BT22" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BV22" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BX22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY22" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BZ22" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,251 +6177,251 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.16</v>
+        <v>3.75</v>
       </c>
       <c r="G23" t="n">
-        <v>1.18</v>
+        <v>5.1</v>
       </c>
       <c r="H23" t="n">
-        <v>19</v>
+        <v>1.74</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>1.93</v>
       </c>
       <c r="J23" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>1.82</v>
       </c>
       <c r="O23" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="P23" t="n">
-        <v>2.66</v>
+        <v>1.82</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="R23" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="S23" t="n">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="T23" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="W23" t="n">
-        <v>6</v>
+        <v>1.24</v>
       </c>
       <c r="X23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,251 +6431,251 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="G24" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="H24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
         <v>4.7</v>
       </c>
-      <c r="I24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BR24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>11</v>
+        <v>2.2</v>
       </c>
       <c r="BT24" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>12</v>
+        <v>1.72</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>13</v>
+        <v>1.72</v>
       </c>
       <c r="BZ24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,251 +6685,251 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H25" t="n">
         <v>1.79</v>
       </c>
-      <c r="G25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H25" t="n">
-        <v>6.4</v>
-      </c>
       <c r="I25" t="n">
-        <v>6.8</v>
+        <v>1.92</v>
       </c>
       <c r="J25" t="n">
         <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="M25" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.64</v>
+        <v>5.9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>2.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.52</v>
+        <v>1.49</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="S25" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="U25" t="n">
-        <v>1.67</v>
+        <v>2.58</v>
       </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="W25" t="n">
-        <v>2.24</v>
+        <v>1.23</v>
       </c>
       <c r="X25" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS25" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="BT25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>12</v>
+      </c>
+      <c r="BW25" t="n">
         <v>6.2</v>
       </c>
-      <c r="AC25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="BX25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BY25" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="BZ25" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA25" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,192 +6939,192 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.56</v>
+        <v>1.45</v>
       </c>
       <c r="G26" t="n">
-        <v>2.7</v>
+        <v>1.56</v>
       </c>
       <c r="H26" t="n">
-        <v>2.74</v>
+        <v>5.3</v>
       </c>
       <c r="I26" t="n">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="J26" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="M26" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="R26" t="n">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="S26" t="n">
-        <v>2.76</v>
+        <v>1.94</v>
       </c>
       <c r="T26" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="U26" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="W26" t="n">
-        <v>1.58</v>
+        <v>2.8</v>
       </c>
       <c r="X26" t="n">
-        <v>19.5</v>
+        <v>46</v>
       </c>
       <c r="Y26" t="n">
-        <v>14.5</v>
+        <v>44</v>
       </c>
       <c r="Z26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH26" t="n">
         <v>22</v>
       </c>
-      <c r="AA26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK26" t="n">
         <v>16.5</v>
       </c>
-      <c r="AI26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>27</v>
-      </c>
       <c r="AL26" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AM26" t="n">
         <v>75</v>
       </c>
       <c r="AN26" t="n">
-        <v>970</v>
+        <v>5.1</v>
       </c>
       <c r="AO26" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="BJ26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
@@ -7133,50 +7133,1574 @@
         <v>9.6</v>
       </c>
       <c r="BN26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:17:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Universidad de Venezuela</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>6</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:17:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>8</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:17:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Deportivo La Guaira</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H29" t="n">
+        <v>19</v>
+      </c>
+      <c r="I29" t="n">
+        <v>29</v>
+      </c>
+      <c r="J29" t="n">
+        <v>9</v>
+      </c>
+      <c r="K29" t="n">
+        <v>11</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>300</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>580</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>380</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>22</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:17:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="X30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:17:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:17:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN32" t="n">
         <v>5.9</v>
       </c>
-      <c r="BO26" t="n">
+      <c r="BO32" t="n">
         <v>4.3</v>
       </c>
-      <c r="BP26" t="n">
+      <c r="BP32" t="n">
         <v>19</v>
       </c>
-      <c r="BQ26" t="n">
+      <c r="BQ32" t="n">
         <v>6.8</v>
       </c>
-      <c r="BR26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS26" t="n">
+      <c r="BR32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS32" t="n">
         <v>7.8</v>
       </c>
-      <c r="BT26" t="n">
+      <c r="BT32" t="n">
         <v>6.4</v>
       </c>
-      <c r="BU26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV26" t="n">
+      <c r="BU32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV32" t="n">
         <v>22</v>
       </c>
-      <c r="BW26" t="n">
+      <c r="BW32" t="n">
         <v>7.2</v>
       </c>
-      <c r="BX26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY26" t="n">
+      <c r="BX32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY32" t="n">
         <v>8</v>
       </c>
-      <c r="BZ26" t="n">
+      <c r="BZ32" t="n">
         <v>23</v>
       </c>
-      <c r="CA26" t="n">
+      <c r="CA32" t="n">
         <v>7.2</v>
       </c>
-      <c r="CB26" t="inlineStr">
-        <is>
-          <t>2026-05-26 06:06:28</t>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -863,13 +863,13 @@
         <v>990</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -887,16 +887,16 @@
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -905,10 +905,10 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="n">
         <v>2.14</v>
@@ -1123,40 +1123,40 @@
         <v>5.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="V3" t="n">
         <v>1.24</v>
@@ -1165,19 +1165,19 @@
         <v>1.87</v>
       </c>
       <c r="X3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
         <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA3" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
         <v>8.6</v>
@@ -1189,7 +1189,7 @@
         <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
         <v>12</v>
@@ -1198,7 +1198,7 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -1222,13 +1222,13 @@
         <v>4.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
         <v>3.6</v>
@@ -1246,13 +1246,13 @@
         <v>4.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AZ3" t="n">
         <v>4.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
         <v>4.9</v>
@@ -1261,7 +1261,7 @@
         <v>4.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
         <v>5.7</v>
@@ -1270,13 +1270,13 @@
         <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BN3" t="n">
         <v>4.9</v>
@@ -1306,25 +1306,25 @@
         <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW3" t="n">
         <v>7.2</v>
       </c>
       <c r="BX3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="H4" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
         <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AF4" t="n">
         <v>19.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AK4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AN4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX4" t="n">
         <v>36</v>
       </c>
-      <c r="AO4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ4" t="n">
+      <c r="BY4" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>2.28</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -1619,58 +1619,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O5" t="n">
         <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
         <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1679,13 +1679,13 @@
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
         <v>9</v>
@@ -1694,13 +1694,13 @@
         <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF5" t="n">
         <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
@@ -1709,79 +1709,79 @@
         <v>110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BI5" t="n">
         <v>2.32</v>
@@ -1790,49 +1790,49 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.81</v>
+        <v>1.22</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -1873,220 +1873,220 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>1.59</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="X6" t="n">
         <v>10.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z6" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AA6" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AB6" t="n">
         <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI6" t="n">
         <v>130</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>150</v>
       </c>
       <c r="AJ6" t="n">
         <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
         <v>230</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="BJ6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BN6" t="n">
         <v>4.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BP6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>28</v>
+        <v>2.24</v>
       </c>
       <c r="BT6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -2127,46 +2127,46 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M7" t="n">
         <v>1.09</v>
       </c>
-      <c r="G7" t="n">
-        <v>990</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>990</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K7" t="n">
-        <v>950</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>2.58</v>
       </c>
       <c r="O7" t="n">
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -2381,178 +2381,178 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="G8" t="n">
-        <v>990</v>
+        <v>1.69</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
-        <v>990</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
+        <v>100</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X8" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y8" t="n">
         <v>950</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2564,31 +2564,31 @@
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -2635,178 +2635,178 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>990</v>
+        <v>2.62</v>
       </c>
       <c r="H9" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>990</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>2.56</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.51</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.51</v>
+        <v>1.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,13 +2818,13 @@
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2836,7 +2836,7 @@
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>990</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>1.09</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>990</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.36</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>1.05</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="G11" t="n">
         <v>990</v>
       </c>
       <c r="H11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
         <v>990</v>
@@ -3191,10 +3191,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
         <v>990</v>
       </c>
       <c r="H12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="I12" t="n">
         <v>990</v>
@@ -3430,13 +3430,13 @@
         <v>1.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="R12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>1.23</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3448,7 +3448,7 @@
         <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G13" t="n">
-        <v>990</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>1.04</v>
@@ -3663,7 +3663,7 @@
         <v>990</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -3702,7 +3702,7 @@
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>2.98</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H14" t="n">
         <v>2.36</v>
@@ -3923,13 +3923,13 @@
         <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
@@ -4076,13 +4076,13 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
@@ -4094,13 +4094,13 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
         <v>1.11</v>
       </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>1.08</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -4413,160 +4413,160 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G16" t="n">
-        <v>110</v>
+        <v>2.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>110</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>2.8</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.24</v>
+        <v>2.92</v>
       </c>
       <c r="O16" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.39</v>
+        <v>2.26</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>1.39</v>
+        <v>4.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
         <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -4575,68 +4575,68 @@
         <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -4667,70 +4667,70 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="G17" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="H17" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="I17" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T17" t="n">
         <v>1.54</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>2.5</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.44</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="X17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA17" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
         <v>18.5</v>
@@ -4739,106 +4739,106 @@
         <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
         <v>40</v>
       </c>
       <c r="AJ17" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK17" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL17" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO17" t="n">
         <v>21</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4853,44 +4853,44 @@
         <v>3.85</v>
       </c>
       <c r="BP17" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BQ17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT17" t="n">
         <v>6.6</v>
       </c>
-      <c r="BR17" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BU17" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BV17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
         <v>6.8</v>
       </c>
       <c r="BX17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ17" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="G18" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="H18" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="J18" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>1.17</v>
@@ -4945,70 +4945,70 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.26</v>
+        <v>8.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q18" t="n">
         <v>1.31</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="S18" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U18" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="X18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Z18" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AA18" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="AB18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD18" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AE18" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AF18" t="n">
         <v>14</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI18" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ18" t="n">
         <v>14</v>
@@ -5020,131 +5020,131 @@
         <v>32</v>
       </c>
       <c r="AM18" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AO18" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ18" t="n">
         <v>11</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BN18" t="n">
         <v>4.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BP18" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR18" t="n">
         <v>17.5</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ18" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="G19" t="n">
         <v>990</v>
       </c>
       <c r="H19" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="I19" t="n">
         <v>990</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="G20" t="n">
         <v>990</v>
       </c>
       <c r="H20" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="I20" t="n">
         <v>990</v>
@@ -5453,13 +5453,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O20" t="n">
         <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q20" t="n">
         <v>1.01</v>
@@ -5468,7 +5468,7 @@
         <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>1.05</v>
+        <v>1.61</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -5683,160 +5683,160 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="G21" t="n">
-        <v>110</v>
+        <v>3.35</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="I21" t="n">
-        <v>110</v>
+        <v>3.15</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>2.8</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.24</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S21" t="n">
-        <v>1.34</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR21" t="n">
         <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -5845,68 +5845,68 @@
         <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G22" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I22" t="n">
         <v>4.6</v>
@@ -5952,43 +5952,43 @@
         <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
         <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R22" t="n">
         <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U22" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X22" t="n">
         <v>11.5</v>
@@ -6003,19 +6003,19 @@
         <v>110</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE22" t="n">
         <v>65</v>
       </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG22" t="n">
         <v>10.5</v>
@@ -6024,7 +6024,7 @@
         <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ22" t="n">
         <v>23</v>
@@ -6039,28 +6039,28 @@
         <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP22" t="n">
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR22" t="n">
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AT22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV22" t="n">
         <v>17</v>
@@ -6075,25 +6075,25 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB22" t="n">
         <v>20</v>
       </c>
       <c r="BC22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BF22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BG22" t="n">
         <v>70</v>
@@ -6102,7 +6102,7 @@
         <v>3.05</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BJ22" t="n">
         <v>10.5</v>
@@ -6114,10 +6114,10 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BN22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO22" t="n">
         <v>4.1</v>
@@ -6126,13 +6126,13 @@
         <v>15</v>
       </c>
       <c r="BQ22" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BR22" t="n">
         <v>32</v>
       </c>
       <c r="BS22" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT22" t="n">
         <v>7.8</v>
@@ -6141,16 +6141,16 @@
         <v>6</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW22" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BX22" t="n">
         <v>55</v>
       </c>
       <c r="BY22" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -6191,23 +6191,23 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
         <v>5.1</v>
       </c>
-      <c r="H23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>6.6</v>
-      </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
@@ -6215,22 +6215,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="O23" t="n">
         <v>1.11</v>
       </c>
       <c r="P23" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q23" t="n">
         <v>1.11</v>
       </c>
       <c r="R23" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="S23" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6239,10 +6239,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -6445,64 +6445,64 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H24" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="I24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K24" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
         <v>1.19</v>
       </c>
       <c r="P24" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="Q24" t="n">
         <v>1.56</v>
       </c>
       <c r="R24" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
         <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="V24" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="X24" t="n">
         <v>26</v>
       </c>
       <c r="Y24" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z24" t="n">
         <v>90</v>
@@ -6511,19 +6511,19 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC24" t="n">
         <v>970</v>
       </c>
       <c r="AD24" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AE24" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="n">
         <v>970</v>
@@ -6556,7 +6556,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
         <v>1.03</v>
@@ -6565,7 +6565,7 @@
         <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU24" t="n">
         <v>9</v>
@@ -6577,7 +6577,7 @@
         <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AY24" t="n">
         <v>7.8</v>
@@ -6589,7 +6589,7 @@
         <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
         <v>1.03</v>
@@ -6601,74 +6601,74 @@
         <v>1.03</v>
       </c>
       <c r="BF24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BN24" t="n">
         <v>4.1</v>
       </c>
-      <c r="BG24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BO24" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="BT24" t="n">
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.72</v>
+        <v>2.68</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.72</v>
+        <v>2.68</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>3.65</v>
       </c>
       <c r="G25" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="H25" t="n">
         <v>1.79</v>
@@ -6711,7 +6711,7 @@
         <v>1.92</v>
       </c>
       <c r="J25" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K25" t="n">
         <v>4.8</v>
@@ -6720,28 +6720,28 @@
         <v>1.22</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
         <v>1.16</v>
       </c>
       <c r="P25" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q25" t="n">
         <v>1.49</v>
       </c>
       <c r="R25" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T25" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U25" t="n">
         <v>2.58</v>
@@ -6750,13 +6750,13 @@
         <v>2.08</v>
       </c>
       <c r="W25" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
         <v>36</v>
       </c>
       <c r="Y25" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z25" t="n">
         <v>18.5</v>
@@ -6777,7 +6777,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG25" t="n">
         <v>22</v>
@@ -6807,58 +6807,58 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH25" t="n">
         <v>4.8</v>
@@ -6870,7 +6870,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6888,13 +6888,13 @@
         <v>29</v>
       </c>
       <c r="BQ25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR25" t="n">
         <v>32</v>
       </c>
       <c r="BS25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT25" t="n">
         <v>5.2</v>
@@ -6912,17 +6912,17 @@
         <v>20</v>
       </c>
       <c r="BY25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA25" t="n">
         <v>6.6</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="G26" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="H26" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="I26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L26" t="n">
         <v>1.19</v>
@@ -6977,34 +6977,34 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="R26" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="S26" t="n">
         <v>1.94</v>
       </c>
       <c r="T26" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U26" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V26" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W26" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="X26" t="n">
         <v>46</v>
@@ -7022,7 +7022,7 @@
         <v>18</v>
       </c>
       <c r="AC26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD26" t="n">
         <v>30</v>
@@ -7031,22 +7031,22 @@
         <v>80</v>
       </c>
       <c r="AF26" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG26" t="n">
         <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
         <v>65</v>
       </c>
       <c r="AJ26" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL26" t="n">
         <v>28</v>
@@ -7055,73 +7055,73 @@
         <v>75</v>
       </c>
       <c r="AN26" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AO26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH26" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="BJ26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BK26" t="n">
         <v>5.1</v>
@@ -7130,31 +7130,31 @@
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BR26" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS26" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BU26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
@@ -7166,17 +7166,17 @@
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ26" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G27" t="n">
         <v>1.47</v>
@@ -7222,7 +7222,7 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.3</v>
@@ -7255,7 +7255,7 @@
         <v>1.87</v>
       </c>
       <c r="V27" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W27" t="n">
         <v>3.1</v>
@@ -7402,7 +7402,7 @@
         <v>25</v>
       </c>
       <c r="BS27" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BT27" t="n">
         <v>12.5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>1.93</v>
       </c>
       <c r="G28" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H28" t="n">
         <v>4.2</v>
@@ -7476,7 +7476,7 @@
         <v>3.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L28" t="n">
         <v>1.39</v>
@@ -7512,7 +7512,7 @@
         <v>1.26</v>
       </c>
       <c r="W28" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X28" t="n">
         <v>12.5</v>
@@ -7527,7 +7527,7 @@
         <v>130</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC28" t="n">
         <v>8.4</v>
@@ -7575,10 +7575,10 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT28" t="n">
         <v>6.6</v>
@@ -7590,7 +7590,7 @@
         <v>15.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX28" t="n">
         <v>8.4</v>
@@ -7602,7 +7602,7 @@
         <v>18</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB28" t="n">
         <v>19.5</v>
@@ -7614,13 +7614,13 @@
         <v>36</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF28" t="n">
         <v>15</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH28" t="n">
         <v>3.2</v>
@@ -7644,7 +7644,7 @@
         <v>4.7</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP28" t="n">
         <v>15.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -7721,13 +7721,13 @@
         <v>1.18</v>
       </c>
       <c r="H29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I29" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>11</v>
@@ -7739,31 +7739,31 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
         <v>1.16</v>
       </c>
       <c r="P29" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q29" t="n">
         <v>1.46</v>
       </c>
       <c r="R29" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S29" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T29" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
         <v>6.2</v>
@@ -7775,7 +7775,7 @@
         <v>80</v>
       </c>
       <c r="Z29" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -7790,7 +7790,7 @@
         <v>950</v>
       </c>
       <c r="AE29" t="n">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="AF29" t="n">
         <v>7.6</v>
@@ -7799,10 +7799,10 @@
         <v>15</v>
       </c>
       <c r="AH29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI29" t="n">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AJ29" t="n">
         <v>8.199999999999999</v>
@@ -7823,16 +7823,16 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT29" t="n">
         <v>8.4</v>
@@ -7844,7 +7844,7 @@
         <v>8</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX29" t="n">
         <v>6.2</v>
@@ -7856,7 +7856,7 @@
         <v>7.6</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB29" t="n">
         <v>6.2</v>
@@ -7865,16 +7865,16 @@
         <v>11.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF29" t="n">
         <v>3.1</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH29" t="n">
         <v>5</v>
@@ -7898,19 +7898,19 @@
         <v>3.75</v>
       </c>
       <c r="BO29" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BP29" t="n">
         <v>6.2</v>
       </c>
       <c r="BQ29" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BR29" t="n">
         <v>26</v>
       </c>
       <c r="BS29" t="n">
-        <v>18.5</v>
+        <v>7.6</v>
       </c>
       <c r="BT29" t="n">
         <v>22</v>
@@ -7934,11 +7934,11 @@
         <v>8.4</v>
       </c>
       <c r="CA29" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
         <v>11</v>
       </c>
       <c r="BH30" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BI30" t="n">
         <v>2.44</v>
@@ -8140,13 +8140,13 @@
         <v>11.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN30" t="n">
         <v>4.4</v>
@@ -8158,41 +8158,41 @@
         <v>15.5</v>
       </c>
       <c r="BQ30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR30" t="n">
         <v>38</v>
       </c>
       <c r="BS30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV30" t="n">
         <v>55</v>
       </c>
       <c r="BW30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ30" t="n">
         <v>38</v>
       </c>
       <c r="CA30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -8223,40 +8223,40 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.77</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.78</v>
-      </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I31" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L31" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M31" t="n">
         <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O31" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P31" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R31" t="n">
         <v>1.2</v>
@@ -8265,13 +8265,13 @@
         <v>5.3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V31" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W31" t="n">
         <v>2.28</v>
@@ -8280,7 +8280,7 @@
         <v>10</v>
       </c>
       <c r="Y31" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z31" t="n">
         <v>55</v>
@@ -8289,7 +8289,7 @@
         <v>230</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC31" t="n">
         <v>9.4</v>
@@ -8331,7 +8331,7 @@
         <v>250</v>
       </c>
       <c r="AP31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ31" t="n">
         <v>13.5</v>
@@ -8340,7 +8340,7 @@
         <v>40</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT31" t="n">
         <v>5.6</v>
@@ -8352,10 +8352,10 @@
         <v>23</v>
       </c>
       <c r="AW31" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
@@ -8364,10 +8364,10 @@
         <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC31" t="n">
         <v>21</v>
@@ -8376,13 +8376,13 @@
         <v>46</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF31" t="n">
         <v>16</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH31" t="n">
         <v>2.82</v>
@@ -8394,7 +8394,7 @@
         <v>12.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
@@ -8412,7 +8412,7 @@
         <v>13.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
@@ -8430,7 +8430,7 @@
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -8480,10 +8480,10 @@
         <v>2.56</v>
       </c>
       <c r="G32" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H32" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="I32" t="n">
         <v>2.84</v>
@@ -8495,7 +8495,7 @@
         <v>3.85</v>
       </c>
       <c r="L32" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M32" t="n">
         <v>1.05</v>
@@ -8510,7 +8510,7 @@
         <v>2.12</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="R32" t="n">
         <v>1.45</v>
@@ -8528,7 +8528,7 @@
         <v>1.54</v>
       </c>
       <c r="W32" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X32" t="n">
         <v>19.5</v>
@@ -8579,7 +8579,7 @@
         <v>75</v>
       </c>
       <c r="AN32" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AO32" t="n">
         <v>22</v>
@@ -8600,7 +8600,7 @@
         <v>11.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV32" t="n">
         <v>11.5</v>
@@ -8678,7 +8678,7 @@
         <v>6.4</v>
       </c>
       <c r="BU32" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV32" t="n">
         <v>22</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>990</v>
@@ -881,10 +881,10 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
         <v>1.36</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
         <v>5.1</v>
@@ -1135,22 +1135,22 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
         <v>1.87</v>
@@ -1168,7 +1168,7 @@
         <v>14</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
         <v>40</v>
@@ -1180,13 +1180,13 @@
         <v>9</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="n">
         <v>13.5</v>
@@ -1195,7 +1195,7 @@
         <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
         <v>90</v>
@@ -1204,73 +1204,73 @@
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AW3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ3" t="n">
+      <c r="BA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD3" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BE3" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.3</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -1365,76 +1365,76 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I4" t="n">
         <v>3.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
         <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
         <v>15</v>
@@ -1443,52 +1443,52 @@
         <v>36</v>
       </c>
       <c r="AF4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
         <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AR4" t="n">
         <v>4.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT4" t="n">
         <v>3.95</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AV4" t="n">
         <v>4.1</v>
@@ -1503,22 +1503,22 @@
         <v>4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BD4" t="n">
         <v>5</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF4" t="n">
         <v>4.6</v>
@@ -1527,22 +1527,22 @@
         <v>4.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN4" t="n">
         <v>6</v>
@@ -1557,7 +1557,7 @@
         <v>5.9</v>
       </c>
       <c r="BR4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS4" t="n">
         <v>6.6</v>
@@ -1569,16 +1569,16 @@
         <v>3.65</v>
       </c>
       <c r="BV4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G5" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>1.44</v>
@@ -1643,61 +1643,61 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="O5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P5" t="n">
         <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AA5" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
@@ -1706,10 +1706,10 @@
         <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1721,76 +1721,76 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO5" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AQ5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>4</v>
       </c>
-      <c r="AR5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="BA5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE5" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="BF5" t="n">
         <v>3.9</v>
       </c>
-      <c r="AY5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG5" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="n">
         <v>2.94</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,7 +1799,7 @@
         <v>1.22</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO5" t="n">
         <v>3.2</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1820,13 +1820,13 @@
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I6" t="n">
         <v>6.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
         <v>3.7</v>
@@ -1894,43 +1894,43 @@
         <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
         <v>1.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
         <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="X6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z6" t="n">
         <v>60</v>
@@ -1939,13 +1939,13 @@
         <v>240</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AE6" t="n">
         <v>140</v>
@@ -1957,118 +1957,118 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AJ6" t="n">
         <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
         <v>230</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AQ6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS6" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AT6" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AY6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>3.9</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BA6" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BN6" t="n">
         <v>4.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BT6" t="n">
         <v>9.800000000000001</v>
@@ -2080,13 +2080,13 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>2.3</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>2.32</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2.26</v>
       </c>
-      <c r="I7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S7" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
@@ -2414,13 +2414,13 @@
         <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R8" t="n">
         <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -2432,7 +2432,7 @@
         <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
         <v>4.6</v>
@@ -2662,7 +2662,7 @@
         <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P9" t="n">
         <v>1.51</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>2.76</v>
       </c>
       <c r="G10" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>2.98</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
         <v>1.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
         <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AL10" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG10" t="n">
         <v>26</v>
       </c>
-      <c r="AO10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BP10" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BQ10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT10" t="n">
         <v>6.2</v>
       </c>
-      <c r="BR10" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT10" t="n">
+      <c r="BU10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
         <v>7</v>
       </c>
-      <c r="BU10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>36</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>7.2</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -3143,112 +3143,112 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.07</v>
+        <v>4.7</v>
       </c>
       <c r="G11" t="n">
-        <v>990</v>
+        <v>7.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="I11" t="n">
-        <v>990</v>
+        <v>1.72</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X11" t="n">
         <v>950</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AP11" t="n">
         <v>1.01</v>
@@ -3284,7 +3284,7 @@
         <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
         <v>1.01</v>
@@ -3305,10 +3305,10 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
@@ -3341,7 +3341,7 @@
         <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU11" t="n">
         <v>1.04</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -3397,112 +3397,112 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="G12" t="n">
-        <v>990</v>
+        <v>1.3</v>
       </c>
       <c r="H12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.05</v>
       </c>
-      <c r="I12" t="n">
-        <v>990</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="W12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y12" t="n">
         <v>950</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AP12" t="n">
         <v>1.01</v>
@@ -3559,13 +3559,13 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI12" t="n">
         <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK12" t="n">
         <v>1.04</v>
@@ -3577,25 +3577,25 @@
         <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BQ12" t="n">
         <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS12" t="n">
         <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BU12" t="n">
         <v>1.04</v>
@@ -3613,14 +3613,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA12" t="n">
         <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>210</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="I13" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
         <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,34 +3675,34 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="O13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.02</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Q13" t="n">
         <v>1.01</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="S13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3816,55 +3816,55 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>2.98</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
         <v>2.36</v>
@@ -3923,37 +3923,37 @@
         <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1.91</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.87</v>
       </c>
       <c r="R14" t="n">
         <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W14" t="n">
         <v>1.41</v>
@@ -3962,7 +3962,7 @@
         <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
         <v>970</v>
@@ -3971,10 +3971,10 @@
         <v>40</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
         <v>970</v>
@@ -4007,64 +4007,64 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.26</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.1</v>
+        <v>23</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.18</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.42</v>
+        <v>4.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.24</v>
+        <v>3.85</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.3</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.56</v>
+        <v>4.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4076,59 +4076,59 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
         <v>1.06</v>
       </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>1.11</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
         <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
         <v>1.95</v>
@@ -4195,31 +4195,31 @@
         <v>1.92</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
         <v>1.62</v>
       </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W15" t="n">
         <v>1.35</v>
       </c>
       <c r="X15" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z15" t="n">
         <v>17.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>17</v>
       </c>
       <c r="AA15" t="n">
         <v>34</v>
@@ -4231,7 +4231,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
@@ -4240,22 +4240,22 @@
         <v>34</v>
       </c>
       <c r="AG15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ15" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK15" t="n">
         <v>55</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -4264,67 +4264,67 @@
         <v>55</v>
       </c>
       <c r="AO15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.35</v>
+        <v>8</v>
       </c>
       <c r="AR15" t="n">
         <v>10.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="AW15" t="n">
         <v>16.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE15" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BF15" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BG15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH15" t="n">
         <v>3.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>3.55</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.44</v>
@@ -4437,193 +4437,193 @@
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.92</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
         <v>1.43</v>
       </c>
       <c r="P16" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U16" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="W16" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB16" t="n">
         <v>12</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>10.5</v>
       </c>
       <c r="AC16" t="n">
         <v>8.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AG16" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
         <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AK16" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AL16" t="n">
         <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN16" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AP16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="n">
         <v>3.05</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="BJ16" t="n">
         <v>11</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP16" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR16" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX16" t="n">
         <v>42</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>48</v>
       </c>
       <c r="BY16" t="n">
         <v>8.6</v>
@@ -4632,11 +4632,11 @@
         <v>42</v>
       </c>
       <c r="CA16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H17" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="I17" t="n">
         <v>3.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.24</v>
@@ -4691,55 +4691,55 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V17" t="n">
         <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y17" t="n">
         <v>21</v>
       </c>
       <c r="Z17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA17" t="n">
         <v>55</v>
       </c>
       <c r="AB17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE17" t="n">
         <v>34</v>
@@ -4757,10 +4757,10 @@
         <v>40</v>
       </c>
       <c r="AJ17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
         <v>36</v>
@@ -4769,28 +4769,28 @@
         <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO17" t="n">
         <v>21</v>
       </c>
       <c r="AP17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR17" t="n">
         <v>17</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AS17" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AT17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
         <v>9.800000000000001</v>
@@ -4805,92 +4805,92 @@
         <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BA17" t="n">
         <v>3.85</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE17" t="n">
         <v>4</v>
       </c>
       <c r="BF17" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BJ17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN17" t="n">
         <v>6.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR17" t="n">
         <v>25</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW17" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>6.8</v>
       </c>
       <c r="BX17" t="n">
         <v>27</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BZ17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="G18" t="n">
         <v>1.31</v>
       </c>
       <c r="H18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
         <v>14.5</v>
@@ -4936,31 +4936,31 @@
         <v>6.2</v>
       </c>
       <c r="K18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
         <v>8</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>8.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q18" t="n">
         <v>1.31</v>
       </c>
       <c r="R18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S18" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="T18" t="n">
         <v>1.72</v>
@@ -4972,7 +4972,7 @@
         <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X18" t="n">
         <v>60</v>
@@ -4981,13 +4981,13 @@
         <v>70</v>
       </c>
       <c r="Z18" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AA18" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="AB18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC18" t="n">
         <v>22</v>
@@ -4999,7 +4999,7 @@
         <v>160</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG18" t="n">
         <v>14.5</v>
@@ -5023,7 +5023,7 @@
         <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AO18" t="n">
         <v>130</v>
@@ -5041,10 +5041,10 @@
         <v>5.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV18" t="n">
         <v>4.9</v>
@@ -5077,7 +5077,7 @@
         <v>5.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="BG18" t="n">
         <v>5.3</v>
@@ -5086,10 +5086,10 @@
         <v>6.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BJ18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK18" t="n">
         <v>6</v>
@@ -5110,13 +5110,13 @@
         <v>7</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT18" t="n">
         <v>15</v>
@@ -5128,7 +5128,7 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
@@ -5140,11 +5140,11 @@
         <v>7</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="G19" t="n">
         <v>990</v>
       </c>
       <c r="H19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="I19" t="n">
         <v>990</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="G20" t="n">
         <v>990</v>
       </c>
       <c r="H20" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="I20" t="n">
         <v>990</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         <v>2.8</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.4</v>
@@ -5707,22 +5707,22 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O21" t="n">
         <v>1.41</v>
       </c>
       <c r="P21" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R21" t="n">
         <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T21" t="n">
         <v>1.83</v>
@@ -5740,7 +5740,7 @@
         <v>13.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
         <v>22</v>
@@ -5767,7 +5767,7 @@
         <v>970</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
         <v>65</v>
@@ -5791,10 +5791,10 @@
         <v>46</v>
       </c>
       <c r="AP21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR21" t="n">
         <v>1.03</v>
@@ -5803,10 +5803,10 @@
         <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AV21" t="n">
         <v>9.6</v>
@@ -5821,7 +5821,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
         <v>1.01</v>
@@ -5848,7 +5848,7 @@
         <v>3.2</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="BJ21" t="n">
         <v>11</v>
@@ -5866,7 +5866,7 @@
         <v>6.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
@@ -5884,7 +5884,7 @@
         <v>6.2</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -5937,58 +5937,58 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I22" t="n">
         <v>4.5</v>
       </c>
-      <c r="I22" t="n">
-        <v>4.6</v>
-      </c>
       <c r="J22" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
         <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X22" t="n">
         <v>11.5</v>
@@ -5997,7 +5997,7 @@
         <v>13.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA22" t="n">
         <v>110</v>
@@ -6006,7 +6006,7 @@
         <v>9</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
         <v>18.5</v>
@@ -6015,7 +6015,7 @@
         <v>65</v>
       </c>
       <c r="AF22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
         <v>10.5</v>
@@ -6024,10 +6024,10 @@
         <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
         <v>21</v>
@@ -6039,28 +6039,28 @@
         <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP22" t="n">
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS22" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AT22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV22" t="n">
         <v>17</v>
@@ -6075,10 +6075,10 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BB22" t="n">
         <v>20</v>
@@ -6108,7 +6108,7 @@
         <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6126,7 +6126,7 @@
         <v>15</v>
       </c>
       <c r="BQ22" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BR22" t="n">
         <v>32</v>
@@ -6138,7 +6138,7 @@
         <v>7.8</v>
       </c>
       <c r="BU22" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BV22" t="n">
         <v>42</v>
@@ -6150,7 +6150,7 @@
         <v>55</v>
       </c>
       <c r="BY22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -6194,227 +6194,227 @@
         <v>3.7</v>
       </c>
       <c r="G23" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H23" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="I23" t="n">
         <v>1.96</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
         <v>5.1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>1.81</v>
+        <v>6.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>1.81</v>
+        <v>3.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="R23" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="S23" t="n">
         <v>1.98</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="V23" t="n">
         <v>2.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
         <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="G24" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="H24" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="I24" t="n">
         <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.25</v>
@@ -6469,148 +6469,148 @@
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T24" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="U24" t="n">
         <v>1.94</v>
       </c>
       <c r="V24" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="X24" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Y24" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Z24" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AD24" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF24" t="n">
         <v>11</v>
       </c>
       <c r="AG24" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI24" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AJ24" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AL24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM24" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN24" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD24" t="n">
         <v>1.03</v>
       </c>
-      <c r="AR24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BG24" t="n">
         <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
@@ -6622,16 +6622,16 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.64</v>
+        <v>2.56</v>
       </c>
       <c r="BN24" t="n">
         <v>4.1</v>
       </c>
       <c r="BO24" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BQ24" t="n">
         <v>4.5</v>
@@ -6640,35 +6640,35 @@
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>2.76</v>
+        <v>7</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>2.68</v>
+        <v>6.4</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="G25" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="H25" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="I25" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.22</v>
@@ -6726,31 +6726,31 @@
         <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P25" t="n">
         <v>2.72</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R25" t="n">
         <v>1.69</v>
       </c>
       <c r="S25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T25" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U25" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V25" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X25" t="n">
         <v>36</v>
@@ -6765,10 +6765,10 @@
         <v>26</v>
       </c>
       <c r="AB25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AC25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD25" t="n">
         <v>13.5</v>
@@ -6777,31 +6777,31 @@
         <v>21</v>
       </c>
       <c r="AF25" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AG25" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI25" t="n">
         <v>30</v>
       </c>
       <c r="AJ25" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL25" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM25" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN25" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AO25" t="n">
         <v>8.800000000000001</v>
@@ -6825,13 +6825,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW25" t="n">
         <v>12</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AY25" t="n">
         <v>13</v>
@@ -6843,22 +6843,22 @@
         <v>18</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BF25" t="n">
         <v>20</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH25" t="n">
         <v>4.8</v>
@@ -6867,10 +6867,10 @@
         <v>3.65</v>
       </c>
       <c r="BJ25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6879,50 +6879,50 @@
         <v>11</v>
       </c>
       <c r="BN25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BY25" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BO25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>29</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>12</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>20</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>8</v>
-      </c>
       <c r="BZ25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CA25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -6956,43 +6956,43 @@
         <v>1.4</v>
       </c>
       <c r="G26" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H26" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="K26" t="n">
         <v>6.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>7.4</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="P26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="R26" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="S26" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="T26" t="n">
         <v>1.58</v>
@@ -7001,37 +7001,37 @@
         <v>2.38</v>
       </c>
       <c r="V26" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Y26" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Z26" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AB26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE26" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF26" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AG26" t="n">
         <v>13</v>
@@ -7040,7 +7040,7 @@
         <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ26" t="n">
         <v>16.5</v>
@@ -7052,70 +7052,70 @@
         <v>28</v>
       </c>
       <c r="AM26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN26" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AX26" t="n">
         <v>10</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.7</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="BC26" t="n">
         <v>10.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BE26" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH26" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BI26" t="n">
         <v>4.4</v>
@@ -7124,59 +7124,59 @@
         <v>10</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN26" t="n">
         <v>4.8</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP26" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR26" t="n">
         <v>17.5</v>
       </c>
       <c r="BS26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT26" t="n">
         <v>12</v>
       </c>
       <c r="BU26" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BX26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BZ26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA26" t="n">
         <v>4.9</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -7213,16 +7213,16 @@
         <v>1.47</v>
       </c>
       <c r="H27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J27" t="n">
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L27" t="n">
         <v>1.3</v>
@@ -7237,13 +7237,13 @@
         <v>1.24</v>
       </c>
       <c r="P27" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R27" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S27" t="n">
         <v>2.8</v>
@@ -7261,7 +7261,7 @@
         <v>3.1</v>
       </c>
       <c r="X27" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y27" t="n">
         <v>950</v>
@@ -7270,31 +7270,31 @@
         <v>80</v>
       </c>
       <c r="AA27" t="n">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC27" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AE27" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AF27" t="n">
         <v>9.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AI27" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ27" t="n">
         <v>13</v>
@@ -7306,67 +7306,67 @@
         <v>38</v>
       </c>
       <c r="AM27" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AN27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO27" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AP27" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS27" t="n">
         <v>7.6</v>
       </c>
-      <c r="AR27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>10</v>
-      </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV27" t="n">
-        <v>24</v>
+        <v>6.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX27" t="n">
         <v>7.6</v>
       </c>
       <c r="AY27" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB27" t="n">
         <v>9.4</v>
       </c>
-      <c r="BB27" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BC27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD27" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF27" t="n">
         <v>5.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BH27" t="n">
         <v>4.1</v>
@@ -7378,7 +7378,7 @@
         <v>12</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
@@ -7390,25 +7390,25 @@
         <v>4.1</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BP27" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ27" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR27" t="n">
         <v>25</v>
       </c>
       <c r="BS27" t="n">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="BT27" t="n">
         <v>12.5</v>
       </c>
       <c r="BU27" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
@@ -7426,11 +7426,11 @@
         <v>15</v>
       </c>
       <c r="CA27" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G28" t="n">
         <v>2.04</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J28" t="n">
         <v>3.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L28" t="n">
         <v>1.39</v>
@@ -7503,67 +7503,67 @@
         <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="U28" t="n">
         <v>1.87</v>
       </c>
       <c r="V28" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W28" t="n">
         <v>1.96</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA28" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AF28" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG28" t="n">
         <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI28" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AK28" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL28" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM28" t="n">
         <v>220</v>
       </c>
       <c r="AN28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO28" t="n">
         <v>110</v>
@@ -7572,55 +7572,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AT28" t="n">
         <v>6.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
         <v>15.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY28" t="n">
         <v>9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB28" t="n">
         <v>19.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD28" t="n">
         <v>36</v>
       </c>
       <c r="BE28" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="BF28" t="n">
         <v>15</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH28" t="n">
         <v>3.2</v>
@@ -7662,7 +7662,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU28" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BV28" t="n">
         <v>46</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G29" t="n">
         <v>1.18</v>
@@ -7724,10 +7724,10 @@
         <v>20</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K29" t="n">
         <v>11</v>
@@ -7745,19 +7745,19 @@
         <v>1.16</v>
       </c>
       <c r="P29" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R29" t="n">
         <v>1.67</v>
       </c>
       <c r="S29" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U29" t="n">
         <v>1.57</v>
@@ -7766,46 +7766,46 @@
         <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="X29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y29" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Z29" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD29" t="n">
         <v>950</v>
       </c>
       <c r="AE29" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="AF29" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AG29" t="n">
         <v>15</v>
       </c>
       <c r="AH29" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AI29" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AJ29" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK29" t="n">
         <v>17.5</v>
@@ -7814,7 +7814,7 @@
         <v>65</v>
       </c>
       <c r="AM29" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AN29" t="n">
         <v>3.55</v>
@@ -7823,40 +7823,40 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU29" t="n">
         <v>17</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AX29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA29" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BB29" t="n">
         <v>6.2</v>
@@ -7865,16 +7865,16 @@
         <v>11.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="BG29" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BH29" t="n">
         <v>5</v>
@@ -7898,13 +7898,13 @@
         <v>3.75</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BP29" t="n">
         <v>6.2</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BR29" t="n">
         <v>26</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -7969,16 +7969,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G30" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H30" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
         <v>3.4</v>
@@ -7990,37 +7990,37 @@
         <v>1.46</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P30" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R30" t="n">
         <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U30" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="V30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="X30" t="n">
         <v>11.5</v>
@@ -8032,10 +8032,10 @@
         <v>36</v>
       </c>
       <c r="AA30" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC30" t="n">
         <v>8</v>
@@ -8044,7 +8044,7 @@
         <v>21</v>
       </c>
       <c r="AE30" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF30" t="n">
         <v>11</v>
@@ -8056,13 +8056,13 @@
         <v>25</v>
       </c>
       <c r="AI30" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="n">
         <v>55</v>
@@ -8071,7 +8071,7 @@
         <v>220</v>
       </c>
       <c r="AN30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
         <v>150</v>
@@ -8083,22 +8083,22 @@
         <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="AS30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT30" t="n">
         <v>6</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AX30" t="n">
         <v>9.199999999999999</v>
@@ -8107,28 +8107,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB30" t="n">
         <v>20</v>
       </c>
       <c r="BC30" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BD30" t="n">
         <v>40</v>
       </c>
       <c r="BE30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF30" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH30" t="n">
         <v>2.86</v>
@@ -8149,10 +8149,10 @@
         <v>15</v>
       </c>
       <c r="BN30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO30" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="BP30" t="n">
         <v>15.5</v>
@@ -8167,13 +8167,13 @@
         <v>11.5</v>
       </c>
       <c r="BT30" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU30" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BV30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW30" t="n">
         <v>12.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -8253,10 +8253,10 @@
         <v>1.52</v>
       </c>
       <c r="P31" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R31" t="n">
         <v>1.2</v>
@@ -8280,7 +8280,7 @@
         <v>10</v>
       </c>
       <c r="Y31" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z31" t="n">
         <v>55</v>
@@ -8310,7 +8310,7 @@
         <v>34</v>
       </c>
       <c r="AI31" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ31" t="n">
         <v>19.5</v>
@@ -8328,7 +8328,7 @@
         <v>21</v>
       </c>
       <c r="AO31" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AP31" t="n">
         <v>8.199999999999999</v>
@@ -8394,7 +8394,7 @@
         <v>12.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
@@ -8406,13 +8406,13 @@
         <v>4.1</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BP31" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
@@ -8424,7 +8424,7 @@
         <v>9.6</v>
       </c>
       <c r="BU31" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G32" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="H32" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="I32" t="n">
         <v>2.84</v>
       </c>
       <c r="J32" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K32" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.29</v>
@@ -8513,13 +8513,13 @@
         <v>1.78</v>
       </c>
       <c r="R32" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S32" t="n">
         <v>2.78</v>
       </c>
       <c r="T32" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U32" t="n">
         <v>2.32</v>
@@ -8528,7 +8528,7 @@
         <v>1.54</v>
       </c>
       <c r="W32" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X32" t="n">
         <v>19.5</v>
@@ -8552,7 +8552,7 @@
         <v>13</v>
       </c>
       <c r="AE32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF32" t="n">
         <v>19.5</v>
@@ -8579,10 +8579,10 @@
         <v>75</v>
       </c>
       <c r="AN32" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AO32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP32" t="n">
         <v>16</v>
@@ -8600,7 +8600,7 @@
         <v>11.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV32" t="n">
         <v>11.5</v>
@@ -8609,7 +8609,7 @@
         <v>25</v>
       </c>
       <c r="AX32" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY32" t="n">
         <v>11</v>
@@ -8648,31 +8648,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK32" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN32" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP32" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT32" t="n">
         <v>6.4</v>
@@ -8684,23 +8684,23 @@
         <v>22</v>
       </c>
       <c r="BW32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ32" t="n">
         <v>23</v>
       </c>
       <c r="CA32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB34"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,46 +857,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.68</v>
       </c>
       <c r="G2" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.71</v>
       </c>
       <c r="I2" t="n">
-        <v>990</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N2" t="n">
         <v>1.1</v>
       </c>
-      <c r="N2" t="n">
-        <v>1.36</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.09</v>
+        <v>2.14</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.56</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
         <v>4.2</v>
@@ -1129,7 +1129,7 @@
         <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1138,13 +1138,13 @@
         <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
@@ -1162,7 +1162,7 @@
         <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
@@ -1177,10 +1177,10 @@
         <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
@@ -1213,64 +1213,64 @@
         <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO3" t="n">
         <v>100</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AQ3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY3" t="n">
         <v>4</v>
       </c>
-      <c r="AR3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF3" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH3" t="n">
         <v>3.3</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1479,7 +1479,7 @@
         <v>4.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS4" t="n">
         <v>5.3</v>
@@ -1488,13 +1488,13 @@
         <v>4</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
         <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
         <v>4.6</v>
@@ -1518,7 +1518,7 @@
         <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF4" t="n">
         <v>4.8</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G5" t="n">
         <v>1.95</v>
@@ -1634,19 +1634,19 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P5" t="n">
         <v>1.6</v>
@@ -1655,13 +1655,13 @@
         <v>2.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
         <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
         <v>1.73</v>
@@ -1673,7 +1673,7 @@
         <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1739,31 +1739,31 @@
         <v>4.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AZ5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB5" t="n">
         <v>4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.95</v>
       </c>
       <c r="BC5" t="n">
         <v>4</v>
@@ -1772,10 +1772,10 @@
         <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG5" t="n">
         <v>4.5</v>
@@ -1784,7 +1784,7 @@
         <v>2.94</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H6" t="n">
         <v>5.1</v>
@@ -1990,10 +1990,10 @@
         <v>4.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AU6" t="n">
         <v>3.15</v>
@@ -2011,7 +2011,7 @@
         <v>3.45</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA6" t="n">
         <v>4.5</v>
@@ -2023,7 +2023,7 @@
         <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
         <v>4.6</v>
@@ -2032,13 +2032,13 @@
         <v>3.85</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH6" t="n">
         <v>2.96</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -2133,19 +2133,19 @@
         <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
@@ -2274,7 +2274,7 @@
         <v>4.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD7" t="n">
         <v>4.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
         <v>9</v>
@@ -2405,7 +2405,7 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
@@ -2420,7 +2420,7 @@
         <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -2432,7 +2432,7 @@
         <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2486,7 +2486,7 @@
         <v>970</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
         <v>3.4</v>
@@ -2498,28 +2498,28 @@
         <v>4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AU8" t="n">
         <v>3.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AW8" t="n">
         <v>4.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AY8" t="n">
         <v>3.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BA8" t="n">
         <v>4.1</v>
@@ -2531,13 +2531,13 @@
         <v>3.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BG8" t="n">
         <v>4.2</v>
@@ -2546,7 +2546,7 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
         <v>3.3</v>
@@ -2647,7 +2647,7 @@
         <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K9" t="n">
         <v>3.3</v>
@@ -2656,19 +2656,19 @@
         <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P9" t="n">
         <v>1.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2677,7 +2677,7 @@
         <v>1.05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
         <v>1.74</v>
@@ -2740,25 +2740,25 @@
         <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AR9" t="n">
         <v>4.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="AT9" t="n">
         <v>3.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV9" t="n">
         <v>4.1</v>
@@ -2767,34 +2767,34 @@
         <v>4.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ9" t="n">
         <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BC9" t="n">
         <v>4.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.76</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="n">
         <v>3.9</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G10" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H10" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.45</v>
@@ -2916,16 +2916,16 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
         <v>3.95</v>
@@ -2937,10 +2937,10 @@
         <v>1.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
@@ -2949,61 +2949,61 @@
         <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC10" t="n">
         <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
         <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL10" t="n">
         <v>55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>60</v>
       </c>
       <c r="AM10" t="n">
         <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
         <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS10" t="n">
         <v>38</v>
@@ -3012,22 +3012,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
         <v>29</v>
       </c>
       <c r="AX10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
         <v>40</v>
@@ -3036,46 +3036,46 @@
         <v>34</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BG10" t="n">
         <v>28</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI10" t="n">
         <v>2.48</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BQ10" t="n">
         <v>6.4</v>
@@ -3084,35 +3084,35 @@
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
         <v>7.2</v>
       </c>
-      <c r="BT10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>7</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="G11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="I11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J11" t="n">
         <v>6.8</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.19</v>
@@ -3176,34 +3176,34 @@
         <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="R11" t="n">
         <v>1.77</v>
       </c>
       <c r="S11" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="T11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="X11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y11" t="n">
         <v>80</v>
       </c>
       <c r="Z11" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -3212,13 +3212,13 @@
         <v>14</v>
       </c>
       <c r="AC11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AD11" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AE11" t="n">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="AF11" t="n">
         <v>10.5</v>
@@ -3227,10 +3227,10 @@
         <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AI11" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AJ11" t="n">
         <v>10.5</v>
@@ -3242,79 +3242,79 @@
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN11" t="n">
         <v>3.75</v>
       </c>
       <c r="AO11" t="n">
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="AP11" t="n">
-        <v>26</v>
+        <v>4.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU11" t="n">
-        <v>14.5</v>
+        <v>4</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>3.75</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.6</v>
+        <v>3.35</v>
       </c>
       <c r="BC11" t="n">
-        <v>10.5</v>
+        <v>3.85</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BH11" t="n">
         <v>5.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11" t="n">
         <v>15</v>
       </c>
       <c r="BK11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3332,19 +3332,19 @@
         <v>6.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="BR11" t="n">
         <v>23</v>
       </c>
       <c r="BS11" t="n">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="BT11" t="n">
         <v>21</v>
       </c>
       <c r="BU11" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3362,11 +3362,11 @@
         <v>7.8</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -3400,22 +3400,22 @@
         <v>5.2</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I12" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -3427,10 +3427,10 @@
         <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
         <v>1.32</v>
@@ -3439,10 +3439,10 @@
         <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
         <v>2.3</v>
@@ -3508,10 +3508,10 @@
         <v>4.9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS12" t="n">
         <v>5.1</v>
@@ -3520,7 +3520,7 @@
         <v>3.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV12" t="n">
         <v>7.8</v>
@@ -3538,10 +3538,10 @@
         <v>5.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BC12" t="n">
         <v>2.32</v>
@@ -3553,7 +3553,7 @@
         <v>1.85</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BG12" t="n">
         <v>4.4</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G13" t="n">
         <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="J13" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.26</v>
@@ -3681,7 +3681,7 @@
         <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
         <v>1.6</v>
@@ -3699,7 +3699,7 @@
         <v>1.67</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
         <v>4.2</v>
@@ -3711,7 +3711,7 @@
         <v>55</v>
       </c>
       <c r="Z13" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -3720,13 +3720,13 @@
         <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AE13" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -3738,7 +3738,7 @@
         <v>40</v>
       </c>
       <c r="AI13" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AJ13" t="n">
         <v>10.5</v>
@@ -3750,67 +3750,67 @@
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN13" t="n">
         <v>5.1</v>
       </c>
       <c r="AO13" t="n">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="AP13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
         <v>4.5</v>
@@ -3819,10 +3819,10 @@
         <v>3.1</v>
       </c>
       <c r="BJ13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3831,7 +3831,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BO13" t="n">
         <v>3</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Finnish Kakkonen</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SJK Akatemia 2</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Hercules</t>
+          <t>Slovacko</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>Klubi-04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Slovacko</t>
+          <t>PK-35 RY</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="G16" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="H16" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
         <v>1.92</v>
       </c>
       <c r="R16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.35</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Y16" t="n">
         <v>12.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB16" t="n">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF16" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH16" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AJ16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL16" t="n">
         <v>65</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AM16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN16" t="n">
         <v>42</v>
       </c>
-      <c r="AL16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>40</v>
-      </c>
       <c r="AO16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AP16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW16" t="n">
+      <c r="BA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE16" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY16" t="n">
+      <c r="BF16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU16" t="n">
         <v>3.85</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.59</v>
+        <v>8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.68</v>
+        <v>10.5</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.64</v>
+        <v>10</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Klubi-04</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PK-35 RY</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.55</v>
+        <v>2.66</v>
       </c>
       <c r="G17" t="n">
-        <v>3.85</v>
+        <v>2.82</v>
       </c>
       <c r="H17" t="n">
-        <v>2.14</v>
+        <v>2.96</v>
       </c>
       <c r="I17" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="L17" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF17" t="n">
         <v>17</v>
       </c>
-      <c r="AC17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>34</v>
-      </c>
       <c r="AG17" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AH17" t="n">
         <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AK17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL17" t="n">
         <v>55</v>
       </c>
-      <c r="AL17" t="n">
-        <v>65</v>
-      </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AN17" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AO17" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AP17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR17" t="n">
+      <c r="AZ17" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BK17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT17" t="n">
         <v>6</v>
       </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>5</v>
-      </c>
       <c r="BU17" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY17" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA17" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,239 +4912,239 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="G18" t="n">
-        <v>2.82</v>
+        <v>1.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.96</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>14.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.69</v>
+        <v>3.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>1.31</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="S18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W18" t="n">
         <v>4.3</v>
       </c>
-      <c r="T18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.54</v>
-      </c>
       <c r="X18" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>410</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BJ18" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="BK18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>27</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>42</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BZ18" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -5166,246 +5166,246 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="G19" t="n">
-        <v>1.31</v>
+        <v>2.64</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>2.74</v>
       </c>
       <c r="I19" t="n">
-        <v>14.5</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="P19" t="n">
-        <v>3.7</v>
+        <v>2.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="R19" t="n">
-        <v>2.08</v>
+        <v>1.61</v>
       </c>
       <c r="S19" t="n">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="T19" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="U19" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="V19" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="X19" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="Y19" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="AA19" t="n">
-        <v>410</v>
+        <v>55</v>
       </c>
       <c r="AB19" t="n">
         <v>19.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>50</v>
+        <v>16.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AI19" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AK19" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.4</v>
+        <v>16</v>
       </c>
       <c r="AO19" t="n">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.1</v>
+        <v>15.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="AT19" t="n">
         <v>13</v>
       </c>
       <c r="AU19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG19" t="n">
         <v>14.5</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BH19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU19" t="n">
         <v>4.9</v>
       </c>
-      <c r="AW19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD19" t="n">
+      <c r="BV19" t="n">
         <v>21</v>
       </c>
-      <c r="BE19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK19" t="n">
+      <c r="BW19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="CA19" t="n">
         <v>6</v>
       </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>7</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>5.3</v>
-      </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,244 +5415,244 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="G20" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="H20" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.1</v>
       </c>
-      <c r="J20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>5.4</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.18</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.6</v>
-      </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>5.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
-        <v>2.52</v>
+        <v>1.79</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="X20" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z20" t="n">
         <v>21</v>
       </c>
-      <c r="Z20" t="n">
-        <v>29</v>
-      </c>
       <c r="AA20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AD20" t="n">
         <v>16.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX20" t="n">
         <v>15</v>
       </c>
-      <c r="AH20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN20" t="n">
+      <c r="AY20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>15.5</v>
       </c>
-      <c r="AO20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT20" t="n">
+      <c r="BA20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ20" t="n">
         <v>11.5</v>
       </c>
-      <c r="AU20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BK20" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BN20" t="n">
         <v>6.2</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP20" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BR20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BV20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX20" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BZ20" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -5674,229 +5674,229 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X21" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BE21" t="n">
         <v>2.66</v>
       </c>
-      <c r="G21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BF21" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BJ21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="BP21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>2.06</v>
+        <v>4</v>
       </c>
       <c r="BT21" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU21" t="n">
         <v>3.85</v>
       </c>
       <c r="BV21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>2.02</v>
+        <v>6.6</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.3</v>
+        <v>2.64</v>
       </c>
       <c r="G22" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="H22" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="I22" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.12</v>
+        <v>2.92</v>
       </c>
       <c r="O22" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="P22" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.84</v>
+        <v>2.24</v>
       </c>
       <c r="R22" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>1.61</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="X22" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="Y22" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA22" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB22" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD22" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE22" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF22" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AG22" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO22" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AP22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD22" t="n">
         <v>3.1</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="BE22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH22" t="n">
         <v>3.1</v>
       </c>
-      <c r="AR22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY22" t="n">
+      <c r="BI22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO22" t="n">
         <v>4.2</v>
       </c>
-      <c r="AZ22" t="n">
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU22" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.11</v>
+        <v>7.6</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.11</v>
+        <v>8.6</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,246 +6182,246 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.58</v>
+        <v>1.99</v>
       </c>
       <c r="G23" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>2.84</v>
+        <v>4.4</v>
       </c>
       <c r="I23" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="Q23" t="n">
         <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
         <v>4.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V23" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y23" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AA23" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AB23" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AF23" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AG23" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
         <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL23" t="n">
         <v>40</v>
       </c>
-      <c r="AL23" t="n">
-        <v>65</v>
-      </c>
       <c r="AM23" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AN23" t="n">
-        <v>46</v>
+        <v>16.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.8</v>
+        <v>29</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.7</v>
+        <v>90</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.5</v>
+        <v>55</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.8</v>
+        <v>19.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.8</v>
+        <v>70</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.8</v>
+        <v>36</v>
       </c>
       <c r="BE23" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.6</v>
+        <v>75</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="BJ23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ23" t="n">
         <v>11</v>
       </c>
-      <c r="BK23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BT23" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW23" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA23" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,244 +6431,244 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="G24" t="n">
-        <v>2.02</v>
+        <v>4.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>1.79</v>
       </c>
       <c r="I24" t="n">
-        <v>4.5</v>
+        <v>1.97</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="O24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.38</v>
       </c>
-      <c r="P24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.2</v>
-      </c>
       <c r="R24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.3</v>
       </c>
-      <c r="S24" t="n">
-        <v>4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.98</v>
-      </c>
       <c r="X24" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV24" t="n">
+      <c r="BA24" t="n">
         <v>17</v>
       </c>
-      <c r="AW24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>65</v>
-      </c>
       <c r="BB24" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
         <v>15.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>75</v>
+        <v>5.1</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.86</v>
+        <v>4.2</v>
       </c>
       <c r="BJ24" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK24" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="BN24" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP24" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="BQ24" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BR24" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BZ24" t="n">
         <v>11.5</v>
       </c>
-      <c r="BT24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>0</v>
-      </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -6690,239 +6690,239 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.7</v>
+        <v>1.32</v>
       </c>
       <c r="G25" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1.84</v>
+        <v>9.6</v>
       </c>
       <c r="I25" t="n">
-        <v>1.96</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="K25" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="R25" t="n">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="S25" t="n">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="T25" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>2.8</v>
+        <v>1.94</v>
       </c>
       <c r="V25" t="n">
-        <v>2.04</v>
+        <v>1.09</v>
       </c>
       <c r="W25" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="X25" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="Z25" t="n">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AA25" t="n">
-        <v>27</v>
+        <v>370</v>
       </c>
       <c r="AB25" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="AC25" t="n">
         <v>14.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="AE25" t="n">
-        <v>19.5</v>
+        <v>160</v>
       </c>
       <c r="AF25" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AI25" t="n">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="AJ25" t="n">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="AK25" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>7.4</v>
+        <v>190</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="AR25" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>17.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT25" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AU25" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
         <v>9</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>12</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>6.8</v>
       </c>
       <c r="BZ25" t="n">
         <v>11.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -6944,239 +6944,239 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.33</v>
+        <v>3.45</v>
       </c>
       <c r="G26" t="n">
-        <v>1.43</v>
+        <v>3.9</v>
       </c>
       <c r="H26" t="n">
-        <v>9.4</v>
+        <v>1.94</v>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>2.08</v>
       </c>
       <c r="J26" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="K26" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P26" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="S26" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T26" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="U26" t="n">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="V26" t="n">
-        <v>1.09</v>
+        <v>1.92</v>
       </c>
       <c r="W26" t="n">
-        <v>3.3</v>
+        <v>1.34</v>
       </c>
       <c r="X26" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR26" t="n">
         <v>29</v>
       </c>
-      <c r="Y26" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>180</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="BS26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ26" t="n">
         <v>13.5</v>
       </c>
-      <c r="AK26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>8</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>14</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BZ26" t="n">
-        <v>11.5</v>
-      </c>
       <c r="CA26" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -7198,184 +7198,184 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.45</v>
+        <v>1.39</v>
       </c>
       <c r="G27" t="n">
-        <v>3.9</v>
+        <v>1.47</v>
       </c>
       <c r="H27" t="n">
-        <v>1.94</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>2.08</v>
+        <v>8.4</v>
       </c>
       <c r="J27" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR27" t="n">
         <v>6</v>
       </c>
-      <c r="O27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X27" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD27" t="n">
+      <c r="AS27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT27" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ27" t="n">
+      <c r="AU27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC27" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX27" t="n">
+      <c r="BD27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI27" t="n">
         <v>4.4</v>
       </c>
-      <c r="AY27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BJ27" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BK27" t="n">
         <v>5.1</v>
@@ -7384,60 +7384,60 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BN27" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BO27" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP27" t="n">
-        <v>26</v>
+        <v>8.6</v>
       </c>
       <c r="BQ27" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR27" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="BS27" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BT27" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BV27" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX27" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ27" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA27" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7447,244 +7447,244 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="G28" t="n">
         <v>1.47</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="I28" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="J28" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>3.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="R28" t="n">
-        <v>1.92</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.87</v>
       </c>
-      <c r="T28" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.38</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W28" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X28" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="Y28" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="Z28" t="n">
         <v>80</v>
       </c>
       <c r="AA28" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="AB28" t="n">
-        <v>18.5</v>
+        <v>9</v>
       </c>
       <c r="AC28" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="AD28" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AE28" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AF28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ28" t="n">
         <v>15</v>
       </c>
-      <c r="AG28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>12</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ28" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="CA28" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -7706,239 +7706,239 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="G29" t="n">
-        <v>1.47</v>
+        <v>2.08</v>
       </c>
       <c r="H29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC29" t="n">
         <v>8.4</v>
       </c>
-      <c r="I29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J29" t="n">
-        <v>5</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="AD29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK29" t="n">
         <v>5.4</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X29" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>340</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV29" t="n">
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ29" t="n">
         <v>6.4</v>
       </c>
-      <c r="AW29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ29" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ29" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BR29" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BS29" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT29" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BU29" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BV29" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW29" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY29" t="n">
         <v>9</v>
       </c>
       <c r="BZ29" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="CA29" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -7955,244 +7955,244 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="G30" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="H30" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="O30" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="P30" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="R30" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN30" t="n">
         <v>4.1</v>
       </c>
-      <c r="T30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="X30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF30" t="n">
+      <c r="BO30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP30" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX30" t="n">
+      <c r="BQ30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT30" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BU30" t="n">
         <v>6</v>
       </c>
       <c r="BV30" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="BX30" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BZ30" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -8214,239 +8214,239 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.74</v>
+        <v>1.16</v>
       </c>
       <c r="G31" t="n">
-        <v>1.78</v>
+        <v>1.18</v>
       </c>
       <c r="H31" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="I31" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="L31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N31" t="n">
+        <v>6</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q31" t="n">
         <v>1.47</v>
       </c>
-      <c r="M31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.66</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>2.28</v>
+        <v>6.4</v>
       </c>
       <c r="X31" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="Y31" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="Z31" t="n">
-        <v>55</v>
+        <v>260</v>
       </c>
       <c r="AA31" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AE31" t="n">
-        <v>140</v>
+        <v>510</v>
       </c>
       <c r="AF31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AI31" t="n">
-        <v>150</v>
+        <v>340</v>
       </c>
       <c r="AJ31" t="n">
-        <v>19.5</v>
+        <v>9</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AL31" t="n">
         <v>65</v>
       </c>
       <c r="AM31" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AN31" t="n">
-        <v>22</v>
+        <v>3.55</v>
       </c>
       <c r="AO31" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>40</v>
+        <v>6.6</v>
       </c>
       <c r="AS31" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.4</v>
+        <v>17.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>24</v>
+        <v>6.2</v>
       </c>
       <c r="BA31" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="BB31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BJ31" t="n">
         <v>16.5</v>
       </c>
-      <c r="BC31" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BK31" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BN31" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="BP31" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="BQ31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS31" t="n">
         <v>7.4</v>
       </c>
-      <c r="BR31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS31" t="n">
-        <v>11</v>
-      </c>
       <c r="BT31" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BU31" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ31" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="CA31" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -8468,239 +8468,239 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.16</v>
+        <v>1.93</v>
       </c>
       <c r="G32" t="n">
-        <v>1.18</v>
+        <v>2.02</v>
       </c>
       <c r="H32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="X32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN32" t="n">
         <v>21</v>
       </c>
-      <c r="I32" t="n">
-        <v>25</v>
-      </c>
-      <c r="J32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="K32" t="n">
+      <c r="AO32" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW32" t="n">
         <v>10.5</v>
       </c>
-      <c r="L32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N32" t="n">
-        <v>6</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="X32" t="n">
+      <c r="AX32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR32" t="n">
         <v>38</v>
       </c>
-      <c r="Y32" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>260</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>510</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>340</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>350</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB32" t="n">
+      <c r="BS32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU32" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BV32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA32" t="n">
         <v>11.5</v>
       </c>
-      <c r="BD32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BJ32" t="n">
-        <v>16</v>
-      </c>
-      <c r="BK32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM32" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BO32" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BP32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BQ32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BR32" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS32" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BT32" t="n">
-        <v>22</v>
-      </c>
-      <c r="BU32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BV32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW32" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY32" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="CA32" t="n">
-        <v>6.4</v>
-      </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -8722,493 +8722,239 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.94</v>
+        <v>2.58</v>
       </c>
       <c r="G33" t="n">
-        <v>2.02</v>
+        <v>2.68</v>
       </c>
       <c r="H33" t="n">
-        <v>4.7</v>
+        <v>2.78</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>2.84</v>
       </c>
       <c r="J33" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K33" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R33" t="n">
         <v>1.46</v>
       </c>
-      <c r="M33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.23</v>
-      </c>
       <c r="S33" t="n">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="U33" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="V33" t="n">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="W33" t="n">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="X33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT33" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AU33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ33" t="n">
         <v>14</v>
       </c>
-      <c r="Z33" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC33" t="n">
+      <c r="BA33" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS33" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN33" t="n">
+      <c r="BT33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV33" t="n">
         <v>22</v>
       </c>
-      <c r="AO33" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP33" t="n">
+      <c r="BW33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
         <v>8</v>
       </c>
-      <c r="AQ33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO33" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BZ33" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="CA33" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Bolivar</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Independiente Rivadavia</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X34" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ34" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN34" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT34" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV34" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW34" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY34" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ34" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA34" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="CB34" t="inlineStr">
-        <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.68</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
-        <v>32</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -890,7 +890,7 @@
         <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
         <v>4.2</v>
@@ -1123,10 +1123,10 @@
         <v>5.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.4</v>
@@ -1162,7 +1162,7 @@
         <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.38</v>
       </c>
       <c r="G4" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H4" t="n">
         <v>2.72</v>
@@ -1407,46 +1407,46 @@
         <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U4" t="n">
         <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>36</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
         <v>18</v>
@@ -1458,13 +1458,13 @@
         <v>40</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AM4" t="n">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="AN4" t="n">
         <v>26</v>
@@ -1473,58 +1473,58 @@
         <v>34</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY4" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -1619,31 +1619,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="G5" t="n">
         <v>1.95</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O5" t="n">
         <v>1.48</v>
@@ -1652,139 +1652,139 @@
         <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
         <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
         <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
         <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
         <v>7.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AE5" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI5" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AJ5" t="n">
         <v>27</v>
       </c>
       <c r="AK5" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT5" t="n">
         <v>3.4</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BG5" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BH5" t="n">
         <v>2.94</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H6" t="n">
         <v>5.1</v>
@@ -1885,7 +1885,7 @@
         <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
         <v>3.6</v>
@@ -1924,121 +1924,121 @@
         <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
         <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>210</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>28</v>
       </c>
       <c r="AE6" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG6" t="n">
-        <v>13</v>
-      </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM6" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AS6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY6" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="n">
         <v>2.96</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J7" t="n">
         <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.49</v>
@@ -2169,28 +2169,28 @@
         <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U7" t="n">
         <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
         <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB7" t="n">
         <v>14.5</v>
@@ -2199,10 +2199,10 @@
         <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
         <v>34</v>
@@ -2214,25 +2214,25 @@
         <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ7" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>75</v>
       </c>
       <c r="AL7" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AM7" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP7" t="n">
         <v>7.8</v>
@@ -2247,10 +2247,10 @@
         <v>21</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>8.4</v>
@@ -2268,22 +2268,22 @@
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
         <v>17.5</v>
@@ -2304,13 +2304,13 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2325,16 +2325,16 @@
         <v>9.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BV7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.35</v>
@@ -2420,7 +2420,7 @@
         <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -2435,118 +2435,118 @@
         <v>2.42</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y8" t="n">
         <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
         <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN8" t="n">
         <v>55</v>
       </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>970</v>
-      </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB8" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BC8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE8" t="n">
         <v>4</v>
       </c>
-      <c r="AS8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF8" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -2641,10 +2641,10 @@
         <v>2.54</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
         <v>2.96</v>
@@ -2683,34 +2683,34 @@
         <v>1.74</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.64</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>970</v>
       </c>
       <c r="AC9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD9" t="n">
         <v>970</v>
       </c>
-      <c r="AD9" t="n">
-        <v>950</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
         <v>970</v>
@@ -2722,79 +2722,79 @@
         <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ9" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AO9" t="n">
         <v>800</v>
       </c>
       <c r="AP9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR9" t="n">
         <v>3.5</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AS9" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AW9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY9" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.6</v>
+        <v>2.22</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.6</v>
+        <v>2.14</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.7</v>
+        <v>2.18</v>
       </c>
       <c r="BE9" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>2.24</v>
       </c>
       <c r="BH9" t="n">
         <v>3.9</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
         <v>2.78</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I10" t="n">
         <v>3.05</v>
@@ -2904,7 +2904,7 @@
         <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.45</v>
@@ -2916,7 +2916,7 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P10" t="n">
         <v>1.73</v>
@@ -2940,7 +2940,7 @@
         <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
@@ -2967,10 +2967,10 @@
         <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
         <v>21</v>
@@ -3042,7 +3042,7 @@
         <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BF10" t="n">
         <v>22</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="H11" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="K11" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>1.19</v>
@@ -3167,31 +3167,31 @@
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>2.92</v>
+        <v>6.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="S11" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
         <v>5.1</v>
@@ -3200,10 +3200,10 @@
         <v>42</v>
       </c>
       <c r="Y11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Z11" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -3212,161 +3212,161 @@
         <v>14</v>
       </c>
       <c r="AC11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE11" t="n">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="AF11" t="n">
         <v>10.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI11" t="n">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="AJ11" t="n">
         <v>10.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM11" t="n">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>540</v>
+        <v>380</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY11" t="n">
         <v>4.6</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AZ11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC11" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BO11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU11" t="n">
         <v>6.4</v>
       </c>
-      <c r="BQ11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>23</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ11" t="n">
         <v>7.8</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -3397,85 +3397,85 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G12" t="n">
         <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q12" t="n">
         <v>1.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V12" t="n">
         <v>2.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
         <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AA12" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AB12" t="n">
         <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE12" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AG12" t="n">
         <v>950</v>
@@ -3484,143 +3484,143 @@
         <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
         <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AL12" t="n">
-        <v>95</v>
+        <v>700</v>
       </c>
       <c r="AM12" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AO12" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV12" t="n">
         <v>7.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BA12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.86</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH12" t="n">
         <v>3.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
         <v>5.4</v>
       </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -3651,46 +3651,46 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="H13" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="I13" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="J13" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="T13" t="n">
         <v>2.24</v>
@@ -3702,31 +3702,31 @@
         <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD13" t="n">
         <v>55</v>
       </c>
-      <c r="Z13" t="n">
-        <v>180</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>65</v>
-      </c>
       <c r="AE13" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -3735,13 +3735,13 @@
         <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI13" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AJ13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK13" t="n">
         <v>17</v>
@@ -3750,85 +3750,85 @@
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN13" t="n">
         <v>5.1</v>
       </c>
       <c r="AO13" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="AP13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU13" t="n">
         <v>5.1</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR13" t="n">
+      <c r="AV13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX13" t="n">
         <v>6</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AY13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BA13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF13" t="n">
         <v>3.95</v>
       </c>
-      <c r="AU13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BJ13" t="n">
         <v>14</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN13" t="n">
         <v>3.8</v>
@@ -3837,44 +3837,44 @@
         <v>3</v>
       </c>
       <c r="BP13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR13" t="n">
         <v>26</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT13" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -4174,10 +4174,10 @@
         <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -4213,176 +4213,176 @@
         <v>1.42</v>
       </c>
       <c r="X15" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y15" t="n">
         <v>970</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
         <v>970</v>
       </c>
       <c r="AA15" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AG15" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AJ15" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO15" t="n">
         <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>25</v>
       </c>
       <c r="AP15" t="n">
         <v>11</v>
       </c>
       <c r="AQ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE15" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BH15" t="n">
         <v>3.45</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.79</v>
+        <v>5.4</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU15" t="n">
         <v>4.4</v>
       </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.59</v>
+        <v>7.4</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.68</v>
+        <v>3.75</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.64</v>
+        <v>8.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="G16" t="n">
         <v>3.85</v>
@@ -4422,7 +4422,7 @@
         <v>2.14</v>
       </c>
       <c r="I16" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
         <v>3.45</v>
@@ -4437,16 +4437,16 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
         <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R16" t="n">
         <v>1.39</v>
@@ -4458,10 +4458,10 @@
         <v>1.62</v>
       </c>
       <c r="U16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="W16" t="n">
         <v>1.35</v>
@@ -4473,10 +4473,10 @@
         <v>12.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA16" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AB16" t="n">
         <v>17</v>
@@ -4500,76 +4500,76 @@
         <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AL16" t="n">
         <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
         <v>20</v>
       </c>
       <c r="AP16" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
         <v>8</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS16" t="n">
         <v>20</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.55</v>
+        <v>8.4</v>
       </c>
       <c r="AU16" t="n">
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="AY16" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.1</v>
+        <v>18</v>
       </c>
       <c r="BD16" t="n">
         <v>34</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BG16" t="n">
         <v>3.7</v>
@@ -4578,7 +4578,7 @@
         <v>3.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.4</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G17" t="n">
         <v>2.82</v>
       </c>
       <c r="H17" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I17" t="n">
         <v>3.2</v>
@@ -4682,10 +4682,10 @@
         <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -4697,37 +4697,37 @@
         <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
         <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
         <v>1.54</v>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y17" t="n">
         <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
         <v>55</v>
@@ -4736,10 +4736,10 @@
         <v>9.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>40</v>
@@ -4766,7 +4766,7 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
         <v>36</v>
@@ -4787,7 +4787,7 @@
         <v>42</v>
       </c>
       <c r="AT17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU17" t="n">
         <v>6.6</v>
@@ -4802,28 +4802,28 @@
         <v>14.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
         <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
-        <v>36</v>
+        <v>9.4</v>
       </c>
       <c r="BC17" t="n">
         <v>29</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BF17" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="BG17" t="n">
         <v>26</v>
@@ -4832,7 +4832,7 @@
         <v>3.1</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
@@ -4844,7 +4844,7 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN17" t="n">
         <v>5.9</v>
@@ -4856,13 +4856,13 @@
         <v>25</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR17" t="n">
         <v>42</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT17" t="n">
         <v>6</v>
@@ -4871,26 +4871,26 @@
         <v>4.6</v>
       </c>
       <c r="BV17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ17" t="n">
         <v>40</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="G18" t="n">
         <v>1.3</v>
@@ -4933,10 +4933,10 @@
         <v>14.5</v>
       </c>
       <c r="J18" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.16</v>
@@ -4945,7 +4945,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>1.1</v>
@@ -4957,10 +4957,10 @@
         <v>1.31</v>
       </c>
       <c r="R18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="T18" t="n">
         <v>1.72</v>
@@ -4969,19 +4969,19 @@
         <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
         <v>4.3</v>
       </c>
       <c r="X18" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="Y18" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="Z18" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA18" t="n">
         <v>410</v>
@@ -5002,25 +5002,25 @@
         <v>14.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
         <v>32</v>
       </c>
       <c r="AI18" t="n">
-        <v>110</v>
+        <v>390</v>
       </c>
       <c r="AJ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK18" t="n">
         <v>14</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>15.5</v>
       </c>
       <c r="AL18" t="n">
         <v>32</v>
       </c>
       <c r="AM18" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN18" t="n">
         <v>3.4</v>
@@ -5029,16 +5029,16 @@
         <v>130</v>
       </c>
       <c r="AP18" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT18" t="n">
         <v>13</v>
@@ -5047,10 +5047,10 @@
         <v>14.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX18" t="n">
         <v>9.4</v>
@@ -5062,7 +5062,7 @@
         <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BB18" t="n">
         <v>9.199999999999999</v>
@@ -5074,13 +5074,13 @@
         <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BF18" t="n">
         <v>2.76</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="BH18" t="n">
         <v>6.2</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G19" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H19" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.24</v>
@@ -5205,10 +5205,10 @@
         <v>1.18</v>
       </c>
       <c r="P19" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R19" t="n">
         <v>1.61</v>
@@ -5217,16 +5217,16 @@
         <v>2.34</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X19" t="n">
         <v>29</v>
@@ -5241,7 +5241,7 @@
         <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC19" t="n">
         <v>11.5</v>
@@ -5259,13 +5259,13 @@
         <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI19" t="n">
         <v>40</v>
       </c>
       <c r="AJ19" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
@@ -5277,7 +5277,7 @@
         <v>65</v>
       </c>
       <c r="AN19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO19" t="n">
         <v>21</v>
@@ -5289,49 +5289,49 @@
         <v>15.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AS19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT19" t="n">
         <v>13</v>
       </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
         <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="AX19" t="n">
         <v>14</v>
       </c>
       <c r="AY19" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.95</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="n">
         <v>19</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BG19" t="n">
         <v>14.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -5429,61 +5429,61 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.05</v>
       </c>
-      <c r="G20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.1</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="O20" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U20" t="n">
         <v>1.79</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y20" t="n">
         <v>10.5</v>
@@ -5492,10 +5492,10 @@
         <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
         <v>8</v>
@@ -5507,7 +5507,7 @@
         <v>55</v>
       </c>
       <c r="AF20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
         <v>18</v>
@@ -5516,49 +5516,49 @@
         <v>26</v>
       </c>
       <c r="AI20" t="n">
-        <v>85</v>
+        <v>460</v>
       </c>
       <c r="AJ20" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AK20" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AL20" t="n">
-        <v>95</v>
+        <v>460</v>
       </c>
       <c r="AM20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO20" t="n">
         <v>210</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>60</v>
       </c>
       <c r="AP20" t="n">
         <v>6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR20" t="n">
         <v>12.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT20" t="n">
         <v>7</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX20" t="n">
         <v>15</v>
@@ -5570,52 +5570,52 @@
         <v>15.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ20" t="n">
         <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
         <v>8.6</v>
@@ -5624,25 +5624,25 @@
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT20" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G21" t="n">
         <v>4.7</v>
@@ -5701,7 +5701,7 @@
         <v>3.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
         <v>1.15</v>
@@ -5713,7 +5713,7 @@
         <v>1.61</v>
       </c>
       <c r="P21" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q21" t="n">
         <v>2.84</v>
@@ -5722,7 +5722,7 @@
         <v>1.14</v>
       </c>
       <c r="S21" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="T21" t="n">
         <v>2.22</v>
@@ -5737,7 +5737,7 @@
         <v>1.27</v>
       </c>
       <c r="X21" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y21" t="n">
         <v>970</v>
@@ -5746,22 +5746,22 @@
         <v>970</v>
       </c>
       <c r="AA21" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
         <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AD21" t="n">
         <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AG21" t="n">
         <v>950</v>
@@ -5770,79 +5770,79 @@
         <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
         <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.52</v>
+        <v>6.4</v>
       </c>
       <c r="AT21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU21" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>3.55</v>
       </c>
-      <c r="AV21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BA21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF21" t="n">
         <v>2.62</v>
       </c>
-      <c r="BB21" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>2.68</v>
-      </c>
       <c r="BG21" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BH21" t="n">
         <v>2.62</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L22" t="n">
         <v>1.41</v>
@@ -5964,16 +5964,16 @@
         <v>2.92</v>
       </c>
       <c r="O22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
         <v>4.2</v>
@@ -5982,37 +5982,37 @@
         <v>1.89</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V22" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="X22" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC22" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AE22" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
         <v>970</v>
@@ -6021,28 +6021,28 @@
         <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AI22" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AK22" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AO22" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AP22" t="n">
         <v>8.199999999999999</v>
@@ -6051,52 +6051,52 @@
         <v>7.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT22" t="n">
         <v>7.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.95</v>
+        <v>7.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.97</v>
+        <v>7.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.02</v>
+        <v>8.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="BH22" t="n">
         <v>3.1</v>
@@ -6105,7 +6105,7 @@
         <v>2.42</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK22" t="n">
         <v>5.3</v>
@@ -6114,25 +6114,25 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN22" t="n">
         <v>5.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT22" t="n">
         <v>6.2</v>
@@ -6144,23 +6144,23 @@
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -6206,10 +6206,10 @@
         <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
@@ -6221,10 +6221,10 @@
         <v>1.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R23" t="n">
         <v>1.3</v>
@@ -6233,10 +6233,10 @@
         <v>4.1</v>
       </c>
       <c r="T23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.99</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.95</v>
       </c>
       <c r="V23" t="n">
         <v>1.28</v>
@@ -6248,7 +6248,7 @@
         <v>11</v>
       </c>
       <c r="Y23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z23" t="n">
         <v>32</v>
@@ -6263,7 +6263,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE23" t="n">
         <v>65</v>
@@ -6275,7 +6275,7 @@
         <v>10.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI23" t="n">
         <v>75</v>
@@ -6302,7 +6302,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR23" t="n">
         <v>29</v>
@@ -6368,7 +6368,7 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BN23" t="n">
         <v>4.5</v>
@@ -6386,7 +6386,7 @@
         <v>32</v>
       </c>
       <c r="BS23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BT23" t="n">
         <v>7.8</v>
@@ -6398,13 +6398,13 @@
         <v>42</v>
       </c>
       <c r="BW23" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="BX23" t="n">
         <v>55</v>
       </c>
       <c r="BY23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G24" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H24" t="n">
         <v>1.79</v>
       </c>
       <c r="I24" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K24" t="n">
         <v>5.1</v>
@@ -6469,7 +6469,7 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
         <v>1.13</v>
@@ -6478,13 +6478,13 @@
         <v>3.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R24" t="n">
         <v>1.84</v>
       </c>
       <c r="S24" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T24" t="n">
         <v>1.45</v>
@@ -6496,76 +6496,76 @@
         <v>2.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X24" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="Y24" t="n">
         <v>21</v>
       </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB24" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AC24" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AG24" t="n">
         <v>21</v>
       </c>
       <c r="AH24" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AJ24" t="n">
+        <v>470</v>
+      </c>
+      <c r="AK24" t="n">
         <v>85</v>
       </c>
-      <c r="AK24" t="n">
-        <v>42</v>
-      </c>
       <c r="AL24" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AM24" t="n">
         <v>55</v>
       </c>
       <c r="AN24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO24" t="n">
         <v>7.4</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ24" t="n">
         <v>13.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
         <v>9.4</v>
@@ -6577,7 +6577,7 @@
         <v>13</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY24" t="n">
         <v>13.5</v>
@@ -6586,25 +6586,25 @@
         <v>11.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH24" t="n">
         <v>5.5</v>
@@ -6616,16 +6616,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BO24" t="n">
         <v>4.7</v>
@@ -6634,13 +6634,13 @@
         <v>27</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT24" t="n">
         <v>5.6</v>
@@ -6652,7 +6652,7 @@
         <v>12</v>
       </c>
       <c r="BW24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX24" t="n">
         <v>18.5</v>
@@ -6664,11 +6664,11 @@
         <v>11.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="G25" t="n">
         <v>1.4</v>
@@ -6711,7 +6711,7 @@
         <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K25" t="n">
         <v>6.4</v>
@@ -6753,25 +6753,25 @@
         <v>3.5</v>
       </c>
       <c r="X25" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="Y25" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Z25" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AA25" t="n">
         <v>370</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD25" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AE25" t="n">
         <v>160</v>
@@ -6780,25 +6780,25 @@
         <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AI25" t="n">
-        <v>130</v>
+        <v>470</v>
       </c>
       <c r="AJ25" t="n">
         <v>12</v>
       </c>
       <c r="AK25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL25" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
-        <v>150</v>
+        <v>390</v>
       </c>
       <c r="AN25" t="n">
         <v>5</v>
@@ -6810,13 +6810,13 @@
         <v>19</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -6825,10 +6825,10 @@
         <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.9</v>
+        <v>18</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX25" t="n">
         <v>8</v>
@@ -6840,25 +6840,25 @@
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC25" t="n">
         <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH25" t="n">
         <v>4.6</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G26" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H26" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="I26" t="n">
         <v>2.08</v>
@@ -6983,7 +6983,7 @@
         <v>1.17</v>
       </c>
       <c r="P26" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="Q26" t="n">
         <v>1.5</v>
@@ -6992,7 +6992,7 @@
         <v>1.69</v>
       </c>
       <c r="S26" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T26" t="n">
         <v>1.52</v>
@@ -7028,7 +7028,7 @@
         <v>13.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AF26" t="n">
         <v>40</v>
@@ -7058,55 +7058,55 @@
         <v>28</v>
       </c>
       <c r="AO26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AP26" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="AQ26" t="n">
         <v>10.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>4.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AV26" t="n">
         <v>8.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX26" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AY26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA26" t="n">
         <v>13</v>
       </c>
-      <c r="AZ26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>18</v>
-      </c>
       <c r="BB26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC26" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC26" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD26" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF26" t="n">
         <v>20</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="G27" t="n">
         <v>1.47</v>
@@ -7219,7 +7219,7 @@
         <v>8.4</v>
       </c>
       <c r="J27" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K27" t="n">
         <v>6.4</v>
@@ -7237,7 +7237,7 @@
         <v>1.09</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q27" t="n">
         <v>1.33</v>
@@ -7261,13 +7261,13 @@
         <v>3.1</v>
       </c>
       <c r="X27" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="Y27" t="n">
         <v>50</v>
       </c>
       <c r="Z27" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AA27" t="n">
         <v>220</v>
@@ -7282,22 +7282,22 @@
         <v>32</v>
       </c>
       <c r="AE27" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
         <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AJ27" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AK27" t="n">
         <v>14.5</v>
@@ -7309,22 +7309,22 @@
         <v>70</v>
       </c>
       <c r="AN27" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AO27" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT27" t="n">
         <v>13.5</v>
@@ -7336,7 +7336,7 @@
         <v>22</v>
       </c>
       <c r="AW27" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX27" t="n">
         <v>10</v>
@@ -7348,7 +7348,7 @@
         <v>17</v>
       </c>
       <c r="BA27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB27" t="n">
         <v>11</v>
@@ -7360,13 +7360,13 @@
         <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BH27" t="n">
         <v>5.7</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -7494,7 +7494,7 @@
         <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="R28" t="n">
         <v>1.46</v>
@@ -7515,13 +7515,13 @@
         <v>3.15</v>
       </c>
       <c r="X28" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="n">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="Z28" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AA28" t="n">
         <v>340</v>
@@ -7554,10 +7554,10 @@
         <v>13</v>
       </c>
       <c r="AK28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL28" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="n">
         <v>160</v>
@@ -7575,10 +7575,10 @@
         <v>21</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT28" t="n">
         <v>7.4</v>
@@ -7587,10 +7587,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX28" t="n">
         <v>7.6</v>
@@ -7602,7 +7602,7 @@
         <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB28" t="n">
         <v>9.4</v>
@@ -7611,16 +7611,16 @@
         <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF28" t="n">
         <v>5.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH28" t="n">
         <v>4.1</v>
@@ -7644,13 +7644,13 @@
         <v>4.1</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BP28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR28" t="n">
         <v>25</v>
@@ -7662,7 +7662,7 @@
         <v>12.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
@@ -7680,11 +7680,11 @@
         <v>15</v>
       </c>
       <c r="CA28" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
         <v>1.95</v>
       </c>
       <c r="G29" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H29" t="n">
         <v>4.1</v>
@@ -7727,10 +7727,10 @@
         <v>4.7</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K29" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L29" t="n">
         <v>1.39</v>
@@ -7760,25 +7760,25 @@
         <v>1.96</v>
       </c>
       <c r="U29" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="V29" t="n">
         <v>1.27</v>
       </c>
       <c r="W29" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X29" t="n">
         <v>14.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z29" t="n">
         <v>34</v>
       </c>
       <c r="AA29" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
         <v>8.199999999999999</v>
@@ -7787,10 +7787,10 @@
         <v>8.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF29" t="n">
         <v>12.5</v>
@@ -7802,7 +7802,7 @@
         <v>23</v>
       </c>
       <c r="AI29" t="n">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="AJ29" t="n">
         <v>26</v>
@@ -7814,13 +7814,13 @@
         <v>48</v>
       </c>
       <c r="AM29" t="n">
-        <v>220</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
         <v>21</v>
       </c>
       <c r="AO29" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AP29" t="n">
         <v>8.800000000000001</v>
@@ -7829,10 +7829,10 @@
         <v>11.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT29" t="n">
         <v>6.6</v>
@@ -7844,10 +7844,10 @@
         <v>15.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY29" t="n">
         <v>9</v>
@@ -7856,7 +7856,7 @@
         <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB29" t="n">
         <v>19.5</v>
@@ -7868,13 +7868,13 @@
         <v>36</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF29" t="n">
         <v>15</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="BH29" t="n">
         <v>3.2</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
         <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L30" t="n">
         <v>1.48</v>
@@ -7993,13 +7993,13 @@
         <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O30" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P30" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="n">
         <v>2.58</v>
@@ -8014,10 +8014,10 @@
         <v>2.34</v>
       </c>
       <c r="U30" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V30" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W30" t="n">
         <v>2.3</v>
@@ -8038,7 +8038,7 @@
         <v>6</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD30" t="n">
         <v>30</v>
@@ -8056,7 +8056,7 @@
         <v>34</v>
       </c>
       <c r="AI30" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AJ30" t="n">
         <v>19.5</v>
@@ -8068,7 +8068,7 @@
         <v>65</v>
       </c>
       <c r="AM30" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AN30" t="n">
         <v>19</v>
@@ -8077,7 +8077,7 @@
         <v>300</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
         <v>13.5</v>
@@ -8086,7 +8086,7 @@
         <v>40</v>
       </c>
       <c r="AS30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT30" t="n">
         <v>5.6</v>
@@ -8098,7 +8098,7 @@
         <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX30" t="n">
         <v>7.8</v>
@@ -8113,7 +8113,7 @@
         <v>10</v>
       </c>
       <c r="BB30" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC30" t="n">
         <v>21</v>
@@ -8122,7 +8122,7 @@
         <v>46</v>
       </c>
       <c r="BE30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF30" t="n">
         <v>16</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -8232,10 +8232,10 @@
         <v>21</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="K31" t="n">
         <v>10.5</v>
@@ -8244,7 +8244,7 @@
         <v>1.23</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N31" t="n">
         <v>6</v>
@@ -8280,10 +8280,10 @@
         <v>38</v>
       </c>
       <c r="Y31" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="Z31" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
@@ -8295,10 +8295,10 @@
         <v>26</v>
       </c>
       <c r="AD31" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="AE31" t="n">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="AF31" t="n">
         <v>8.4</v>
@@ -8310,7 +8310,7 @@
         <v>60</v>
       </c>
       <c r="AI31" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AJ31" t="n">
         <v>9</v>
@@ -8322,7 +8322,7 @@
         <v>65</v>
       </c>
       <c r="AM31" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AN31" t="n">
         <v>3.55</v>
@@ -8331,28 +8331,28 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AR31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS31" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS31" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AT31" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AV31" t="n">
         <v>6.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX31" t="n">
         <v>6.4</v>
@@ -8361,10 +8361,10 @@
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB31" t="n">
         <v>6.2</v>
@@ -8373,16 +8373,16 @@
         <v>11.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF31" t="n">
         <v>2.86</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH31" t="n">
         <v>5</v>
@@ -8394,7 +8394,7 @@
         <v>16.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
@@ -8418,7 +8418,7 @@
         <v>26</v>
       </c>
       <c r="BS31" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BT31" t="n">
         <v>23</v>
@@ -8442,11 +8442,11 @@
         <v>8.4</v>
       </c>
       <c r="CA31" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
         <v>4.8</v>
       </c>
       <c r="I32" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>3.4</v>
@@ -8660,7 +8660,7 @@
         <v>4.4</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BP32" t="n">
         <v>15.5</v>
@@ -8678,7 +8678,7 @@
         <v>8</v>
       </c>
       <c r="BU32" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -8731,16 +8731,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G33" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H33" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="I33" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>3.7</v>
@@ -8779,10 +8779,10 @@
         <v>2.32</v>
       </c>
       <c r="V33" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W33" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X33" t="n">
         <v>19.5</v>
@@ -8791,10 +8791,10 @@
         <v>14.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB33" t="n">
         <v>13.5</v>
@@ -8833,7 +8833,7 @@
         <v>75</v>
       </c>
       <c r="AN33" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AO33" t="n">
         <v>23</v>
@@ -8896,37 +8896,37 @@
         <v>3.9</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK33" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN33" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO33" t="n">
         <v>4.4</v>
       </c>
       <c r="BP33" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BQ33" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT33" t="n">
         <v>6.4</v>
@@ -8935,26 +8935,26 @@
         <v>5.3</v>
       </c>
       <c r="BV33" t="n">
+        <v>970</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ33" t="n">
         <v>22</v>
       </c>
-      <c r="BW33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>23</v>
-      </c>
       <c r="CA33" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -857,46 +857,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G2" t="n">
         <v>110</v>
       </c>
       <c r="H2" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="I2" t="n">
         <v>44</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>2.58</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>32</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
         <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="P2" t="n">
         <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.16</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -1126,10 +1126,10 @@
         <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1159,7 +1159,7 @@
         <v>1.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W3" t="n">
         <v>1.88</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1392,25 +1392,25 @@
         <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
         <v>1.44</v>
@@ -1431,7 +1431,7 @@
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
         <v>8.800000000000001</v>
@@ -1449,7 +1449,7 @@
         <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
         <v>46</v>
@@ -1467,19 +1467,19 @@
         <v>260</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO4" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
         <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
         <v>6.6</v>
@@ -1500,10 +1500,10 @@
         <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BA4" t="n">
         <v>6.4</v>
@@ -1512,25 +1512,25 @@
         <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD4" t="n">
         <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
         <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
         <v>10</v>
@@ -1548,25 +1548,25 @@
         <v>5.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BP4" t="n">
         <v>21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV4" t="n">
         <v>25</v>
@@ -1575,10 +1575,10 @@
         <v>6.2</v>
       </c>
       <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>38</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>6.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -1619,40 +1619,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="n">
         <v>1.95</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="O5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R5" t="n">
         <v>1.21</v>
@@ -1661,10 +1661,10 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V5" t="n">
         <v>1.21</v>
@@ -1673,10 +1673,10 @@
         <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1685,10 +1685,10 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>42</v>
@@ -1697,10 +1697,10 @@
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
         <v>60</v>
@@ -1730,25 +1730,25 @@
         <v>4.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AU5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
         <v>4.9</v>
@@ -1757,28 +1757,28 @@
         <v>5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF5" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG5" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH5" t="n">
         <v>2.94</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="H6" t="n">
         <v>5.1</v>
@@ -1885,7 +1885,7 @@
         <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
         <v>3.6</v>
@@ -1906,7 +1906,7 @@
         <v>1.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
         <v>1.22</v>
@@ -1924,7 +1924,7 @@
         <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
         <v>10.5</v>
@@ -1972,7 +1972,7 @@
         <v>150</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>21</v>
@@ -1981,64 +1981,64 @@
         <v>700</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AU6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="n">
         <v>2.96</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
         <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I7" t="n">
         <v>2.24</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
@@ -2172,7 +2172,7 @@
         <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V7" t="n">
         <v>1.8</v>
@@ -2202,7 +2202,7 @@
         <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
         <v>34</v>
@@ -2226,16 +2226,16 @@
         <v>200</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
         <v>28</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.8</v>
@@ -2253,7 +2253,7 @@
         <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW7" t="n">
         <v>20</v>
@@ -2262,28 +2262,28 @@
         <v>20</v>
       </c>
       <c r="AY7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
         <v>17.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -2390,10 +2390,10 @@
         <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
         <v>4.9</v>
@@ -2414,7 +2414,7 @@
         <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
         <v>1.31</v>
@@ -2429,16 +2429,16 @@
         <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W8" t="n">
         <v>2.42</v>
       </c>
       <c r="X8" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
@@ -2447,10 +2447,10 @@
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
@@ -2459,22 +2459,22 @@
         <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI8" t="n">
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2483,7 +2483,7 @@
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
         <v>700</v>
@@ -2492,13 +2492,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" t="n">
         <v>4.4</v>
@@ -2507,46 +2507,46 @@
         <v>5.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AZ8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB8" t="n">
         <v>3.9</v>
       </c>
-      <c r="BA8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BC8" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
         <v>3.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L9" t="n">
         <v>1.5</v>
@@ -2665,7 +2665,7 @@
         <v>1.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q9" t="n">
         <v>2.6</v>
@@ -2674,7 +2674,7 @@
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.1</v>
@@ -2683,13 +2683,13 @@
         <v>1.74</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
@@ -2704,7 +2704,7 @@
         <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>970</v>
@@ -2725,7 +2725,7 @@
         <v>540</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
         <v>500</v>
@@ -2737,7 +2737,7 @@
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
         <v>800</v>
@@ -2749,10 +2749,10 @@
         <v>5.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="AT9" t="n">
         <v>4.2</v>
@@ -2761,46 +2761,46 @@
         <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.24</v>
+        <v>3.05</v>
       </c>
       <c r="AX9" t="n">
         <v>6.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.22</v>
+        <v>3.35</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.14</v>
+        <v>3.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.34</v>
+        <v>3.65</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.24</v>
+        <v>3.05</v>
       </c>
       <c r="BH9" t="n">
         <v>3.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.58</v>
       </c>
       <c r="G10" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H10" t="n">
         <v>2.92</v>
@@ -2904,7 +2904,7 @@
         <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>1.45</v>
@@ -2925,25 +2925,25 @@
         <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
         <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V10" t="n">
         <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
         <v>11.5</v>
@@ -2958,16 +2958,16 @@
         <v>9.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
         <v>13</v>
@@ -3000,22 +3000,22 @@
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS10" t="n">
         <v>38</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU10" t="n">
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW10" t="n">
         <v>29</v>
@@ -3024,13 +3024,13 @@
         <v>14</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB10" t="n">
         <v>34</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G11" t="n">
         <v>1.24</v>
       </c>
       <c r="H11" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="J11" t="n">
         <v>7.2</v>
@@ -3161,37 +3161,37 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="S11" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
         <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
         <v>5.1</v>
@@ -3233,7 +3233,7 @@
         <v>220</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AK11" t="n">
         <v>15</v>
@@ -3248,55 +3248,55 @@
         <v>3.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>380</v>
+        <v>450</v>
       </c>
       <c r="AP11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV11" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AW11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX11" t="n">
         <v>6.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
         <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
         <v>2.92</v>
@@ -3305,25 +3305,25 @@
         <v>15</v>
       </c>
       <c r="BH11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BJ11" t="n">
         <v>14</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO11" t="n">
         <v>3.05</v>
@@ -3332,41 +3332,41 @@
         <v>6.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR11" t="n">
         <v>22</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT11" t="n">
         <v>18.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="J12" t="n">
         <v>3.65</v>
@@ -3445,13 +3445,13 @@
         <v>1.88</v>
       </c>
       <c r="V12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="W12" t="n">
         <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y12" t="n">
         <v>14</v>
@@ -3505,7 +3505,7 @@
         <v>29</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ12" t="n">
         <v>4.2</v>
@@ -3514,10 +3514,10 @@
         <v>7.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="AU12" t="n">
         <v>4.4</v>
@@ -3526,13 +3526,13 @@
         <v>7.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX12" t="n">
         <v>7.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AZ12" t="n">
         <v>6.2</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -3681,22 +3681,22 @@
         <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="R13" t="n">
         <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
         <v>2.24</v>
       </c>
       <c r="U13" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V13" t="n">
         <v>1.06</v>
@@ -3744,7 +3744,7 @@
         <v>10</v>
       </c>
       <c r="AK13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL13" t="n">
         <v>55</v>
@@ -3765,7 +3765,7 @@
         <v>6.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS13" t="n">
         <v>7.4</v>
@@ -3774,13 +3774,13 @@
         <v>4.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AV13" t="n">
         <v>6.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX13" t="n">
         <v>6</v>
@@ -3789,7 +3789,7 @@
         <v>4.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA13" t="n">
         <v>7.2</v>
@@ -3801,13 +3801,13 @@
         <v>5.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
         <v>7.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BG13" t="n">
         <v>15</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -4165,16 +4165,16 @@
         <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I15" t="n">
         <v>2.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
         <v>1.4</v>
@@ -4189,34 +4189,34 @@
         <v>1.31</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="R15" t="n">
         <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
         <v>1.73</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z15" t="n">
         <v>970</v>
@@ -4240,7 +4240,7 @@
         <v>500</v>
       </c>
       <c r="AG15" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AH15" t="n">
         <v>29</v>
@@ -4261,7 +4261,7 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4276,13 +4276,13 @@
         <v>8.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
         <v>7.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
         <v>6.4</v>
@@ -4291,25 +4291,25 @@
         <v>13</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC15" t="n">
         <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BE15" t="n">
         <v>22</v>
@@ -4318,13 +4318,13 @@
         <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH15" t="n">
         <v>3.45</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4336,13 +4336,13 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="BN15" t="n">
         <v>6.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4354,13 +4354,13 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BT15" t="n">
         <v>5.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4378,11 +4378,11 @@
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
         <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
         <v>1.94</v>
@@ -4476,7 +4476,7 @@
         <v>17</v>
       </c>
       <c r="AA16" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AB16" t="n">
         <v>17</v>
@@ -4545,7 +4545,7 @@
         <v>10.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AY16" t="n">
         <v>11.5</v>
@@ -4557,7 +4557,7 @@
         <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC16" t="n">
         <v>18</v>
@@ -4572,7 +4572,7 @@
         <v>5.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BH16" t="n">
         <v>3.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
         <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -4715,13 +4715,13 @@
         <v>1.96</v>
       </c>
       <c r="V17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
         <v>1.54</v>
       </c>
       <c r="X17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="n">
         <v>11</v>
@@ -4778,7 +4778,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR17" t="n">
         <v>16.5</v>
@@ -4790,7 +4790,7 @@
         <v>8.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
         <v>12</v>
@@ -4802,7 +4802,7 @@
         <v>14.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>17</v>
@@ -4811,10 +4811,10 @@
         <v>10</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD17" t="n">
         <v>42</v>
@@ -4832,7 +4832,7 @@
         <v>3.1</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
         <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
         <v>4.3</v>
@@ -5029,10 +5029,10 @@
         <v>130</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR18" t="n">
         <v>6.2</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
         <v>2.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
         <v>1.63</v>
@@ -5292,7 +5292,7 @@
         <v>17</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT19" t="n">
         <v>13</v>
@@ -5328,7 +5328,7 @@
         <v>14.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF19" t="n">
         <v>9.6</v>
@@ -5340,7 +5340,7 @@
         <v>4.6</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BJ19" t="n">
         <v>8.800000000000001</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H20" t="n">
         <v>2.84</v>
@@ -5480,7 +5480,7 @@
         <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
         <v>9.4</v>
@@ -5546,7 +5546,7 @@
         <v>12.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT20" t="n">
         <v>7</v>
@@ -5558,7 +5558,7 @@
         <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX20" t="n">
         <v>15</v>
@@ -5573,16 +5573,16 @@
         <v>4.4</v>
       </c>
       <c r="BB20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC20" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.3</v>
       </c>
       <c r="BD20" t="n">
         <v>4.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF20" t="n">
         <v>9.4</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -5686,22 +5686,22 @@
         <v>3.65</v>
       </c>
       <c r="G21" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H21" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I21" t="n">
         <v>2.52</v>
       </c>
       <c r="J21" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M21" t="n">
         <v>1.15</v>
@@ -5713,19 +5713,19 @@
         <v>1.61</v>
       </c>
       <c r="P21" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
         <v>1.14</v>
       </c>
       <c r="S21" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U21" t="n">
         <v>1.62</v>
@@ -5740,7 +5740,7 @@
         <v>14</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z21" t="n">
         <v>970</v>
@@ -5752,7 +5752,7 @@
         <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="AD21" t="n">
         <v>970</v>
@@ -5791,7 +5791,7 @@
         <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AQ21" t="n">
         <v>3.85</v>
@@ -5800,7 +5800,7 @@
         <v>6.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT21" t="n">
         <v>4.9</v>
@@ -5812,40 +5812,40 @@
         <v>7.6</v>
       </c>
       <c r="AW21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX21" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>6.2</v>
       </c>
       <c r="AY21" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="BB21" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BI21" t="n">
         <v>2.12</v>
@@ -5854,13 +5854,13 @@
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
@@ -5872,7 +5872,7 @@
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
@@ -5881,10 +5881,10 @@
         <v>4</v>
       </c>
       <c r="BT21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5896,7 +5896,7 @@
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -5937,25 +5937,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G22" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="H22" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="I22" t="n">
         <v>3.25</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
         <v>3.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -5979,25 +5979,25 @@
         <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V22" t="n">
         <v>1.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="X22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y22" t="n">
         <v>17.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
@@ -6006,7 +6006,7 @@
         <v>18</v>
       </c>
       <c r="AC22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD22" t="n">
         <v>25</v>
@@ -6015,7 +6015,7 @@
         <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG22" t="n">
         <v>970</v>
@@ -6048,25 +6048,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT22" t="n">
         <v>7.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
         <v>7.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX22" t="n">
         <v>8.4</v>
@@ -6078,19 +6078,19 @@
         <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC22" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC22" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD22" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
         <v>6.8</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H23" t="n">
         <v>4.4</v>
@@ -6233,7 +6233,7 @@
         <v>4.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>1.99</v>
@@ -6242,13 +6242,13 @@
         <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z23" t="n">
         <v>32</v>
@@ -6257,13 +6257,13 @@
         <v>110</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
         <v>65</v>
@@ -6293,10 +6293,10 @@
         <v>120</v>
       </c>
       <c r="AN23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO23" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP23" t="n">
         <v>10.5</v>
@@ -6338,7 +6338,7 @@
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD23" t="n">
         <v>36</v>
@@ -6386,7 +6386,7 @@
         <v>32</v>
       </c>
       <c r="BS23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BT23" t="n">
         <v>7.8</v>
@@ -6398,7 +6398,7 @@
         <v>42</v>
       </c>
       <c r="BW23" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BX23" t="n">
         <v>55</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
         <v>16</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF24" t="n">
         <v>16</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -6708,10 +6708,10 @@
         <v>9.6</v>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K25" t="n">
         <v>6.4</v>
@@ -6747,7 +6747,7 @@
         <v>1.94</v>
       </c>
       <c r="V25" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W25" t="n">
         <v>3.5</v>
@@ -6795,7 +6795,7 @@
         <v>15</v>
       </c>
       <c r="AL25" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM25" t="n">
         <v>390</v>
@@ -6813,7 +6813,7 @@
         <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS25" t="n">
         <v>8.199999999999999</v>
@@ -6843,13 +6843,13 @@
         <v>7.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC25" t="n">
         <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE25" t="n">
         <v>7.8</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -7067,13 +7067,13 @@
         <v>10.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU26" t="n">
         <v>5.6</v>
@@ -7088,22 +7088,22 @@
         <v>4.7</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA26" t="n">
         <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE26" t="n">
         <v>4.9</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G28" t="n">
         <v>1.47</v>
@@ -7470,7 +7470,7 @@
         <v>8.4</v>
       </c>
       <c r="I28" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>5</v>
@@ -7494,7 +7494,7 @@
         <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="R28" t="n">
         <v>1.46</v>
@@ -7509,10 +7509,10 @@
         <v>1.87</v>
       </c>
       <c r="V28" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X28" t="n">
         <v>21</v>
@@ -7587,7 +7587,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="AW28" t="n">
         <v>8.199999999999999</v>
@@ -7650,7 +7650,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR28" t="n">
         <v>25</v>
@@ -7662,7 +7662,7 @@
         <v>12.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
@@ -7680,11 +7680,11 @@
         <v>15</v>
       </c>
       <c r="CA28" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
         <v>1.95</v>
       </c>
       <c r="G29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H29" t="n">
         <v>4.1</v>
@@ -7733,13 +7733,13 @@
         <v>3.75</v>
       </c>
       <c r="L29" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
         <v>1.4</v>
@@ -7748,25 +7748,25 @@
         <v>1.72</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="R29" t="n">
         <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T29" t="n">
         <v>1.96</v>
       </c>
       <c r="U29" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V29" t="n">
         <v>1.27</v>
       </c>
       <c r="W29" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X29" t="n">
         <v>14.5</v>
@@ -7844,7 +7844,7 @@
         <v>15.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX29" t="n">
         <v>10</v>
@@ -7856,7 +7856,7 @@
         <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB29" t="n">
         <v>19.5</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G30" t="n">
         <v>1.74</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.77</v>
       </c>
       <c r="H30" t="n">
         <v>6.6</v>
@@ -7984,10 +7984,10 @@
         <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="M30" t="n">
         <v>1.12</v>
@@ -7999,7 +7999,7 @@
         <v>1.53</v>
       </c>
       <c r="P30" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q30" t="n">
         <v>2.58</v>
@@ -8017,10 +8017,10 @@
         <v>1.63</v>
       </c>
       <c r="V30" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X30" t="n">
         <v>9.4</v>
@@ -8032,7 +8032,7 @@
         <v>55</v>
       </c>
       <c r="AA30" t="n">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AB30" t="n">
         <v>6</v>
@@ -8056,7 +8056,7 @@
         <v>34</v>
       </c>
       <c r="AI30" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ30" t="n">
         <v>19.5</v>
@@ -8128,7 +8128,7 @@
         <v>16</v>
       </c>
       <c r="BG30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH30" t="n">
         <v>2.82</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -8241,10 +8241,10 @@
         <v>10.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N31" t="n">
         <v>6</v>
@@ -8256,16 +8256,16 @@
         <v>2.68</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="R31" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S31" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T31" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U31" t="n">
         <v>1.57</v>
@@ -8277,13 +8277,13 @@
         <v>6.4</v>
       </c>
       <c r="X31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y31" t="n">
         <v>75</v>
       </c>
       <c r="Z31" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
@@ -8295,13 +8295,13 @@
         <v>26</v>
       </c>
       <c r="AD31" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AE31" t="n">
         <v>550</v>
       </c>
       <c r="AF31" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG31" t="n">
         <v>15</v>
@@ -8331,16 +8331,16 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT31" t="n">
         <v>8</v>
@@ -8349,10 +8349,10 @@
         <v>17</v>
       </c>
       <c r="AV31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX31" t="n">
         <v>6.4</v>
@@ -8361,10 +8361,10 @@
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB31" t="n">
         <v>6.2</v>
@@ -8373,16 +8373,16 @@
         <v>11.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH31" t="n">
         <v>5</v>
@@ -8394,7 +8394,7 @@
         <v>16.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
@@ -8412,13 +8412,13 @@
         <v>6.2</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BR31" t="n">
         <v>26</v>
       </c>
       <c r="BS31" t="n">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="BT31" t="n">
         <v>23</v>
@@ -8442,11 +8442,11 @@
         <v>8.4</v>
       </c>
       <c r="CA31" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -8477,169 +8477,169 @@
         </is>
       </c>
       <c r="F32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G32" t="n">
         <v>1.93</v>
       </c>
-      <c r="G32" t="n">
-        <v>2.02</v>
-      </c>
       <c r="H32" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L32" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
         <v>1.64</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S32" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="V32" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W32" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="X32" t="n">
         <v>11.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z32" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA32" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AB32" t="n">
         <v>7</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD32" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AE32" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG32" t="n">
         <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI32" t="n">
         <v>110</v>
       </c>
       <c r="AJ32" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK32" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL32" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM32" t="n">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="AN32" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO32" t="n">
         <v>150</v>
       </c>
       <c r="AP32" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ32" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR32" t="n">
         <v>30</v>
       </c>
       <c r="AS32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT32" t="n">
         <v>6</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV32" t="n">
         <v>17</v>
       </c>
       <c r="AW32" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY32" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BA32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB32" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BE32" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BG32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BI32" t="n">
         <v>2.46</v>
@@ -8654,34 +8654,34 @@
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BN32" t="n">
         <v>4.4</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP32" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT32" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BR32" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT32" t="n">
-        <v>8</v>
-      </c>
       <c r="BU32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV32" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW32" t="n">
         <v>12.5</v>
@@ -8690,17 +8690,17 @@
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ32" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G33" t="n">
         <v>2.64</v>
@@ -8740,7 +8740,7 @@
         <v>2.84</v>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="J33" t="n">
         <v>3.7</v>
@@ -8758,16 +8758,16 @@
         <v>4.3</v>
       </c>
       <c r="O33" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P33" t="n">
         <v>2.12</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="R33" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S33" t="n">
         <v>2.78</v>
@@ -8779,19 +8779,19 @@
         <v>2.32</v>
       </c>
       <c r="V33" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W33" t="n">
         <v>1.61</v>
       </c>
       <c r="X33" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y33" t="n">
         <v>14.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="n">
         <v>48</v>
@@ -8800,16 +8800,16 @@
         <v>13.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD33" t="n">
         <v>13</v>
       </c>
       <c r="AE33" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF33" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG33" t="n">
         <v>12.5</v>
@@ -8818,7 +8818,7 @@
         <v>16.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ33" t="n">
         <v>40</v>
@@ -8836,10 +8836,10 @@
         <v>18.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AP33" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>12</v>
@@ -8863,10 +8863,10 @@
         <v>25</v>
       </c>
       <c r="AX33" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ33" t="n">
         <v>14</v>
@@ -8875,7 +8875,7 @@
         <v>29</v>
       </c>
       <c r="BB33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC33" t="n">
         <v>23</v>
@@ -8902,13 +8902,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK33" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN33" t="n">
         <v>5.8</v>
@@ -8917,7 +8917,7 @@
         <v>4.4</v>
       </c>
       <c r="BP33" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BQ33" t="n">
         <v>7</v>
@@ -8926,7 +8926,7 @@
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT33" t="n">
         <v>6.4</v>
@@ -8938,23 +8938,23 @@
         <v>970</v>
       </c>
       <c r="BW33" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BZ33" t="n">
         <v>22</v>
       </c>
       <c r="CA33" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -860,43 +860,43 @@
         <v>3.3</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="H2" t="n">
         <v>1.75</v>
       </c>
       <c r="I2" t="n">
-        <v>44</v>
+        <v>2.46</v>
       </c>
       <c r="J2" t="n">
         <v>2.58</v>
       </c>
       <c r="K2" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>1.46</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="P2" t="n">
         <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -905,10 +905,10 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1010,7 +1010,7 @@
         <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>130</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>150</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
         <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -1138,10 +1138,10 @@
         <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q3" t="n">
         <v>2.1</v>
@@ -1162,7 +1162,7 @@
         <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
@@ -1213,7 +1213,7 @@
         <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO3" t="n">
         <v>100</v>
@@ -1225,16 +1225,16 @@
         <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AV3" t="n">
         <v>4.7</v>
@@ -1243,34 +1243,34 @@
         <v>5.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
         <v>4.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.7</v>
+        <v>85</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.3</v>
@@ -1279,7 +1279,7 @@
         <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
         <v>4.8</v>
@@ -1288,43 +1288,43 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.36</v>
+        <v>110</v>
       </c>
       <c r="BN3" t="n">
         <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP3" t="n">
         <v>16</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
         <v>36</v>
       </c>
       <c r="BS3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV3" t="n">
         <v>44</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX3" t="n">
         <v>60</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
@@ -1413,10 +1413,10 @@
         <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
         <v>15</v>
@@ -1464,7 +1464,7 @@
         <v>100</v>
       </c>
       <c r="AM4" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
         <v>25</v>
@@ -1479,10 +1479,10 @@
         <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
@@ -1491,28 +1491,28 @@
         <v>4.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
         <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
         <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
         <v>6.4</v>
@@ -1554,7 +1554,7 @@
         <v>21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -1622,28 +1622,28 @@
         <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
         <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
         <v>1.5</v>
@@ -1685,7 +1685,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AC5" t="n">
         <v>9.6</v>
@@ -1733,22 +1733,22 @@
         <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX5" t="n">
         <v>4.9</v>
@@ -1757,28 +1757,28 @@
         <v>5</v>
       </c>
       <c r="AZ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB5" t="n">
         <v>6</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD5" t="n">
         <v>7</v>
       </c>
-      <c r="BB5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE5" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="BH5" t="n">
         <v>2.94</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="BN5" t="n">
         <v>4.5</v>
@@ -1808,13 +1808,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H6" t="n">
         <v>5.1</v>
@@ -1885,7 +1885,7 @@
         <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
         <v>3.6</v>
@@ -1924,7 +1924,7 @@
         <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X6" t="n">
         <v>10.5</v>
@@ -1945,7 +1945,7 @@
         <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>700</v>
@@ -1987,13 +1987,13 @@
         <v>5.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AU6" t="n">
         <v>4.1</v>
@@ -2002,22 +2002,22 @@
         <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="n">
         <v>6.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
         <v>6.2</v>
@@ -2026,13 +2026,13 @@
         <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF6" t="n">
         <v>5.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH6" t="n">
         <v>2.96</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
         <v>2.06</v>
@@ -2145,22 +2145,22 @@
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
         <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
@@ -2169,22 +2169,22 @@
         <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V7" t="n">
         <v>1.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
         <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
         <v>15</v>
@@ -2196,7 +2196,7 @@
         <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>13.5</v>
@@ -2214,7 +2214,7 @@
         <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
@@ -2268,22 +2268,22 @@
         <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG7" t="n">
         <v>17.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G8" t="n">
         <v>1.7</v>
@@ -2453,7 +2453,7 @@
         <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
@@ -2471,10 +2471,10 @@
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AK8" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2483,7 +2483,7 @@
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
         <v>700</v>
@@ -2492,13 +2492,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR8" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
         <v>4.4</v>
@@ -2507,40 +2507,40 @@
         <v>5.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AW8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB8" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ8" t="n">
+      <c r="BC8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE8" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BF8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.7</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H9" t="n">
         <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
@@ -2662,22 +2662,22 @@
         <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
         <v>1.49</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
         <v>1.74</v>
@@ -2704,7 +2704,7 @@
         <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AD9" t="n">
         <v>970</v>
@@ -2749,10 +2749,10 @@
         <v>5.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="AT9" t="n">
         <v>4.2</v>
@@ -2761,58 +2761,58 @@
         <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="AX9" t="n">
         <v>6.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
@@ -2824,31 +2824,31 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.18</v>
+        <v>2.36</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -2889,73 +2889,73 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
         <v>1.45</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
         <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
         <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
         <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
@@ -2964,13 +2964,13 @@
         <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
         <v>17.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
         <v>21</v>
@@ -2985,16 +2985,16 @@
         <v>34</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM10" t="n">
         <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -3006,10 +3006,10 @@
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
         <v>6.8</v>
@@ -3024,34 +3024,34 @@
         <v>14</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
         <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB10" t="n">
         <v>34</v>
       </c>
       <c r="BC10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD10" t="n">
         <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BF10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG10" t="n">
         <v>28</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI10" t="n">
         <v>2.48</v>
@@ -3060,13 +3060,13 @@
         <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BN10" t="n">
         <v>5.9</v>
@@ -3075,16 +3075,16 @@
         <v>4.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
         <v>6.4</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
         <v>1.24</v>
@@ -3152,10 +3152,10 @@
         <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
         <v>8.199999999999999</v>
@@ -3191,7 +3191,7 @@
         <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
         <v>5.1</v>
@@ -3209,7 +3209,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC11" t="n">
         <v>22</v>
@@ -3221,13 +3221,13 @@
         <v>320</v>
       </c>
       <c r="AF11" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
         <v>220</v>
@@ -3251,16 +3251,16 @@
         <v>450</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>8.6</v>
@@ -3269,37 +3269,37 @@
         <v>14.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AX11" t="n">
         <v>6.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB11" t="n">
         <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BG11" t="n">
         <v>15</v>
@@ -3308,7 +3308,7 @@
         <v>5.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BJ11" t="n">
         <v>14</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -3397,82 +3397,82 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="I12" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="U12" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="W12" t="n">
         <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="Z12" t="n">
         <v>40</v>
       </c>
       <c r="AA12" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AB12" t="n">
         <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
-        <v>36</v>
+        <v>17.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
         <v>500</v>
@@ -3505,22 +3505,22 @@
         <v>29</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AV12" t="n">
         <v>7.8</v>
@@ -3535,46 +3535,46 @@
         <v>6.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA12" t="n">
         <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.8</v>
+        <v>3.15</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>8</v>
+        <v>2.68</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.54</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
@@ -3586,13 +3586,13 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.98</v>
+        <v>4.5</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.99</v>
+        <v>4.6</v>
       </c>
       <c r="BT12" t="n">
         <v>4.4</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>1.32</v>
       </c>
       <c r="H13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="I13" t="n">
         <v>16.5</v>
@@ -3681,10 +3681,10 @@
         <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="R13" t="n">
         <v>1.5</v>
@@ -3762,7 +3762,7 @@
         <v>5.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR13" t="n">
         <v>7</v>
@@ -3774,7 +3774,7 @@
         <v>4.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AV13" t="n">
         <v>6.6</v>
@@ -3789,7 +3789,7 @@
         <v>4.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA13" t="n">
         <v>7.2</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -4246,10 +4246,10 @@
         <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AK15" t="n">
         <v>500</v>
@@ -4291,7 +4291,7 @@
         <v>13</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY15" t="n">
         <v>10.5</v>
@@ -4303,13 +4303,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC15" t="n">
         <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE15" t="n">
         <v>22</v>
@@ -4318,7 +4318,7 @@
         <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="n">
         <v>3.45</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
         <v>18</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
         <v>17</v>
@@ -4482,10 +4482,10 @@
         <v>17</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE16" t="n">
         <v>28</v>
@@ -4524,7 +4524,7 @@
         <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AR16" t="n">
         <v>7.6</v>
@@ -4542,10 +4542,10 @@
         <v>6.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AY16" t="n">
         <v>11.5</v>
@@ -4557,22 +4557,22 @@
         <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
-        <v>18</v>
+        <v>4.9</v>
       </c>
       <c r="BD16" t="n">
         <v>34</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF16" t="n">
         <v>5.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH16" t="n">
         <v>3.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G17" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H17" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J17" t="n">
         <v>3.2</v>
@@ -4694,10 +4694,10 @@
         <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
         <v>2.22</v>
@@ -4706,19 +4706,19 @@
         <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T17" t="n">
         <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
         <v>1.46</v>
       </c>
       <c r="W17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X17" t="n">
         <v>11</v>
@@ -4739,7 +4739,7 @@
         <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE17" t="n">
         <v>40</v>
@@ -4778,7 +4778,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR17" t="n">
         <v>16.5</v>
@@ -4814,7 +4814,7 @@
         <v>10.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD17" t="n">
         <v>42</v>
@@ -4844,7 +4844,7 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN17" t="n">
         <v>5.9</v>
@@ -4856,13 +4856,13 @@
         <v>25</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR17" t="n">
         <v>42</v>
       </c>
       <c r="BS17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT17" t="n">
         <v>6</v>
@@ -4871,26 +4871,26 @@
         <v>4.6</v>
       </c>
       <c r="BV17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ17" t="n">
         <v>40</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -4927,19 +4927,19 @@
         <v>1.3</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I18" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="J18" t="n">
         <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
@@ -4969,10 +4969,10 @@
         <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X18" t="n">
         <v>240</v>
@@ -4984,7 +4984,7 @@
         <v>140</v>
       </c>
       <c r="AA18" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AB18" t="n">
         <v>19.5</v>
@@ -4993,7 +4993,7 @@
         <v>22</v>
       </c>
       <c r="AD18" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AE18" t="n">
         <v>160</v>
@@ -5032,7 +5032,7 @@
         <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR18" t="n">
         <v>6.2</v>
@@ -5062,7 +5062,7 @@
         <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB18" t="n">
         <v>9.199999999999999</v>
@@ -5086,7 +5086,7 @@
         <v>6.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BJ18" t="n">
         <v>11.5</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN18" t="n">
         <v>4.5</v>
@@ -5113,7 +5113,7 @@
         <v>5.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS18" t="n">
         <v>7.4</v>
@@ -5122,7 +5122,7 @@
         <v>15</v>
       </c>
       <c r="BU18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
@@ -5134,17 +5134,17 @@
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ18" t="n">
         <v>7</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G19" t="n">
         <v>2.58</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I19" t="n">
         <v>3.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
         <v>4.2</v>
@@ -5199,22 +5199,22 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R19" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="S19" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
         <v>1.58</v>
@@ -5229,31 +5229,31 @@
         <v>1.63</v>
       </c>
       <c r="X19" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA19" t="n">
         <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
         <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
         <v>15</v>
@@ -5268,19 +5268,19 @@
         <v>36</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AO19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP19" t="n">
         <v>17</v>
@@ -5292,7 +5292,7 @@
         <v>17</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AT19" t="n">
         <v>13</v>
@@ -5328,19 +5328,19 @@
         <v>14.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.7</v>
+        <v>38</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BG19" t="n">
         <v>14.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BJ19" t="n">
         <v>8.800000000000001</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN19" t="n">
         <v>6.2</v>
@@ -5364,19 +5364,19 @@
         <v>17</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR19" t="n">
         <v>25</v>
       </c>
       <c r="BS19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT19" t="n">
         <v>6.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV19" t="n">
         <v>21</v>
@@ -5385,20 +5385,20 @@
         <v>6.6</v>
       </c>
       <c r="BX19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -5429,103 +5429,103 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="G20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H20" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I20" t="n">
         <v>3.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="K20" t="n">
         <v>3.05</v>
       </c>
       <c r="L20" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
         <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
         <v>1.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T20" t="n">
         <v>2.06</v>
       </c>
       <c r="U20" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="V20" t="n">
         <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y20" t="n">
         <v>9.4</v>
       </c>
-      <c r="Y20" t="n">
-        <v>10.5</v>
-      </c>
       <c r="Z20" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AG20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AI20" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AK20" t="n">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AL20" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
         <v>500</v>
@@ -5534,64 +5534,64 @@
         <v>500</v>
       </c>
       <c r="AO20" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AP20" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU20" t="n">
         <v>5.7</v>
       </c>
       <c r="AV20" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF20" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG20" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BI20" t="n">
         <v>2.22</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN20" t="n">
         <v>6</v>
@@ -5618,13 +5618,13 @@
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT20" t="n">
         <v>5.9</v>
@@ -5633,16 +5633,16 @@
         <v>4.3</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>2.2</v>
       </c>
       <c r="I21" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>2.72</v>
@@ -5710,7 +5710,7 @@
         <v>2.24</v>
       </c>
       <c r="O21" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="P21" t="n">
         <v>1.41</v>
@@ -5725,16 +5725,16 @@
         <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U21" t="n">
         <v>1.62</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X21" t="n">
         <v>14</v>
@@ -5791,7 +5791,7 @@
         <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ21" t="n">
         <v>3.85</v>
@@ -5800,55 +5800,55 @@
         <v>6.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AT21" t="n">
         <v>4.9</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AV21" t="n">
         <v>7.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY21" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="BB21" t="n">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="BG21" t="n">
         <v>7.2</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
@@ -5860,31 +5860,31 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="BT21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5896,7 +5896,7 @@
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>3.25</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
         <v>3.5</v>
@@ -5979,10 +5979,10 @@
         <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V22" t="n">
         <v>1.45</v>
@@ -6015,7 +6015,7 @@
         <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG22" t="n">
         <v>970</v>
@@ -6048,13 +6048,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR22" t="n">
         <v>14</v>
       </c>
       <c r="AS22" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AT22" t="n">
         <v>7.2</v>
@@ -6078,19 +6078,19 @@
         <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB22" t="n">
         <v>8</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF22" t="n">
         <v>6.8</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V23" t="n">
         <v>1.28</v>
@@ -6263,7 +6263,7 @@
         <v>8</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE23" t="n">
         <v>65</v>
@@ -6299,7 +6299,7 @@
         <v>90</v>
       </c>
       <c r="AP23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
         <v>12.5</v>
@@ -6308,7 +6308,7 @@
         <v>29</v>
       </c>
       <c r="AS23" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AT23" t="n">
         <v>8</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -6448,49 +6448,49 @@
         <v>3.7</v>
       </c>
       <c r="G24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="I24" t="n">
         <v>1.96</v>
       </c>
       <c r="J24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K24" t="n">
         <v>5.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P24" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="R24" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="S24" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="T24" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="U24" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V24" t="n">
         <v>2.04</v>
@@ -6505,7 +6505,7 @@
         <v>21</v>
       </c>
       <c r="Z24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA24" t="n">
         <v>24</v>
@@ -6517,40 +6517,40 @@
         <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF24" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AG24" t="n">
         <v>21</v>
       </c>
       <c r="AH24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AJ24" t="n">
         <v>470</v>
       </c>
       <c r="AK24" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AL24" t="n">
         <v>80</v>
       </c>
       <c r="AM24" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AN24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO24" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AP24" t="n">
         <v>16</v>
@@ -6589,7 +6589,7 @@
         <v>19</v>
       </c>
       <c r="BB24" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC24" t="n">
         <v>18</v>
@@ -6598,7 +6598,7 @@
         <v>16</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF24" t="n">
         <v>16</v>
@@ -6607,40 +6607,40 @@
         <v>5.5</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BI24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN24" t="n">
         <v>8.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP24" t="n">
         <v>27</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT24" t="n">
         <v>5.6</v>
@@ -6652,23 +6652,23 @@
         <v>12</v>
       </c>
       <c r="BW24" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BX24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA24" t="n">
         <v>5.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -6708,13 +6708,13 @@
         <v>9.6</v>
       </c>
       <c r="I25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
         <v>5.4</v>
       </c>
       <c r="K25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.25</v>
@@ -6723,28 +6723,28 @@
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P25" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R25" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="S25" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T25" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U25" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V25" t="n">
         <v>1.11</v>
@@ -6756,7 +6756,7 @@
         <v>44</v>
       </c>
       <c r="Y25" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="Z25" t="n">
         <v>540</v>
@@ -6765,10 +6765,10 @@
         <v>370</v>
       </c>
       <c r="AB25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD25" t="n">
         <v>120</v>
@@ -6777,10 +6777,10 @@
         <v>160</v>
       </c>
       <c r="AF25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG25" t="n">
         <v>11</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
         <v>55</v>
@@ -6801,7 +6801,7 @@
         <v>390</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AO25" t="n">
         <v>190</v>
@@ -6813,10 +6813,10 @@
         <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -6828,7 +6828,7 @@
         <v>18</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AX25" t="n">
         <v>8</v>
@@ -6840,7 +6840,7 @@
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB25" t="n">
         <v>6.2</v>
@@ -6849,22 +6849,22 @@
         <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG25" t="n">
         <v>10.5</v>
       </c>
       <c r="BH25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BJ25" t="n">
         <v>12</v>
@@ -6888,7 +6888,7 @@
         <v>8</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BR25" t="n">
         <v>23</v>
@@ -6915,14 +6915,14 @@
         <v>9</v>
       </c>
       <c r="BZ25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CA25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -7061,22 +7061,22 @@
         <v>8.4</v>
       </c>
       <c r="AP26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS26" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AT26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV26" t="n">
         <v>8.4</v>
@@ -7085,25 +7085,25 @@
         <v>13</v>
       </c>
       <c r="AX26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA26" t="n">
         <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC26" t="n">
         <v>4.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE26" t="n">
         <v>4.9</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -7210,121 +7210,121 @@
         <v>1.42</v>
       </c>
       <c r="G27" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I27" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K27" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M27" t="n">
         <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>7.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R27" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="S27" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="T27" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U27" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="V27" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W27" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="X27" t="n">
         <v>100</v>
       </c>
       <c r="Y27" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="Z27" t="n">
         <v>170</v>
       </c>
       <c r="AA27" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AB27" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AC27" t="n">
         <v>15</v>
       </c>
       <c r="AD27" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AE27" t="n">
         <v>190</v>
       </c>
       <c r="AF27" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG27" t="n">
         <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI27" t="n">
         <v>150</v>
       </c>
       <c r="AJ27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK27" t="n">
         <v>14.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM27" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AO27" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR27" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT27" t="n">
         <v>13.5</v>
@@ -7336,7 +7336,7 @@
         <v>22</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX27" t="n">
         <v>10</v>
@@ -7345,10 +7345,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB27" t="n">
         <v>11</v>
@@ -7360,7 +7360,7 @@
         <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF27" t="n">
         <v>3.65</v>
@@ -7369,13 +7369,13 @@
         <v>10.5</v>
       </c>
       <c r="BH27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BI27" t="n">
         <v>4.4</v>
       </c>
       <c r="BJ27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK27" t="n">
         <v>5.1</v>
@@ -7384,19 +7384,19 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ27" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>4.7</v>
       </c>
       <c r="BR27" t="n">
         <v>17.5</v>
@@ -7405,16 +7405,16 @@
         <v>6.6</v>
       </c>
       <c r="BT27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU27" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -7461,25 +7461,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="G28" t="n">
         <v>1.47</v>
       </c>
       <c r="H28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K28" t="n">
         <v>5.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
@@ -7512,7 +7512,7 @@
         <v>1.12</v>
       </c>
       <c r="W28" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X28" t="n">
         <v>21</v>
@@ -7533,7 +7533,7 @@
         <v>12</v>
       </c>
       <c r="AD28" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AE28" t="n">
         <v>160</v>
@@ -7632,13 +7632,13 @@
         <v>12</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN28" t="n">
         <v>4.1</v>
@@ -7647,10 +7647,10 @@
         <v>3.25</v>
       </c>
       <c r="BP28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BQ28" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BR28" t="n">
         <v>25</v>
@@ -7662,19 +7662,19 @@
         <v>12.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ28" t="n">
         <v>15</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G29" t="n">
         <v>2.08</v>
@@ -7730,7 +7730,7 @@
         <v>3.45</v>
       </c>
       <c r="K29" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
         <v>1.47</v>
@@ -7739,7 +7739,7 @@
         <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
         <v>1.4</v>
@@ -7748,13 +7748,13 @@
         <v>1.72</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="R29" t="n">
         <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T29" t="n">
         <v>1.96</v>
@@ -7790,7 +7790,7 @@
         <v>18.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AF29" t="n">
         <v>12.5</v>
@@ -7808,7 +7808,7 @@
         <v>26</v>
       </c>
       <c r="AK29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL29" t="n">
         <v>48</v>
@@ -7820,7 +7820,7 @@
         <v>21</v>
       </c>
       <c r="AO29" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AP29" t="n">
         <v>8.800000000000001</v>
@@ -7844,7 +7844,7 @@
         <v>15.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AX29" t="n">
         <v>10</v>
@@ -7856,7 +7856,7 @@
         <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BB29" t="n">
         <v>19.5</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G30" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="H30" t="n">
         <v>6.6</v>
@@ -7984,10 +7984,10 @@
         <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M30" t="n">
         <v>1.12</v>
@@ -8002,7 +8002,7 @@
         <v>1.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
         <v>1.2</v>
@@ -8011,31 +8011,31 @@
         <v>5.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U30" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V30" t="n">
         <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="X30" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z30" t="n">
         <v>55</v>
       </c>
       <c r="AA30" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AB30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AC30" t="n">
         <v>9.4</v>
@@ -8053,7 +8053,7 @@
         <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AI30" t="n">
         <v>160</v>
@@ -8071,22 +8071,22 @@
         <v>300</v>
       </c>
       <c r="AN30" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AP30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR30" t="n">
         <v>40</v>
       </c>
       <c r="AS30" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT30" t="n">
         <v>5.6</v>
@@ -8098,7 +8098,7 @@
         <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX30" t="n">
         <v>7.8</v>
@@ -8110,7 +8110,7 @@
         <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB30" t="n">
         <v>14.5</v>
@@ -8122,34 +8122,34 @@
         <v>46</v>
       </c>
       <c r="BE30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF30" t="n">
         <v>16</v>
       </c>
       <c r="BG30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH30" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BJ30" t="n">
         <v>12.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BN30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO30" t="n">
         <v>3.6</v>
@@ -8158,41 +8158,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ30" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT30" t="n">
         <v>9.6</v>
       </c>
       <c r="BU30" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -8256,19 +8256,19 @@
         <v>2.68</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S31" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T31" t="n">
         <v>2.46</v>
       </c>
       <c r="U31" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V31" t="n">
         <v>1.04</v>
@@ -8301,7 +8301,7 @@
         <v>550</v>
       </c>
       <c r="AF31" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AG31" t="n">
         <v>15</v>
@@ -8331,16 +8331,16 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR31" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT31" t="n">
         <v>8</v>
@@ -8349,104 +8349,104 @@
         <v>17</v>
       </c>
       <c r="AV31" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX31" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB31" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>6.2</v>
       </c>
       <c r="BC31" t="n">
         <v>11.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF31" t="n">
         <v>2.88</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH31" t="n">
         <v>5</v>
       </c>
       <c r="BI31" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BJ31" t="n">
         <v>16.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN31" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP31" t="n">
         <v>6.2</v>
       </c>
       <c r="BQ31" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BR31" t="n">
         <v>26</v>
       </c>
       <c r="BS31" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT31" t="n">
         <v>23</v>
       </c>
       <c r="BU31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ31" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G32" t="n">
         <v>1.93</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I32" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.53</v>
@@ -8504,13 +8504,13 @@
         <v>2.98</v>
       </c>
       <c r="O32" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P32" t="n">
         <v>1.64</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R32" t="n">
         <v>1.24</v>
@@ -8519,28 +8519,28 @@
         <v>4.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U32" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V32" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W32" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X32" t="n">
         <v>11.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z32" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA32" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB32" t="n">
         <v>7</v>
@@ -8549,16 +8549,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE32" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF32" t="n">
         <v>10</v>
       </c>
       <c r="AG32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH32" t="n">
         <v>950</v>
@@ -8579,7 +8579,7 @@
         <v>270</v>
       </c>
       <c r="AN32" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO32" t="n">
         <v>150</v>
@@ -8588,13 +8588,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR32" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS32" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT32" t="n">
         <v>6</v>
@@ -8603,10 +8603,10 @@
         <v>7.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW32" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX32" t="n">
         <v>8.199999999999999</v>
@@ -8615,10 +8615,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BA32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB32" t="n">
         <v>18.5</v>
@@ -8630,13 +8630,13 @@
         <v>44</v>
       </c>
       <c r="BE32" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF32" t="n">
         <v>16</v>
       </c>
       <c r="BG32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH32" t="n">
         <v>2.9</v>
@@ -8660,7 +8660,7 @@
         <v>4.4</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BP32" t="n">
         <v>15</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -8731,16 +8731,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G33" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H33" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I33" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J33" t="n">
         <v>3.7</v>
@@ -8749,13 +8749,13 @@
         <v>3.8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M33" t="n">
         <v>1.05</v>
       </c>
       <c r="N33" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O33" t="n">
         <v>1.26</v>
@@ -8764,25 +8764,25 @@
         <v>2.12</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="R33" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S33" t="n">
         <v>2.78</v>
       </c>
       <c r="T33" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U33" t="n">
         <v>2.32</v>
       </c>
       <c r="V33" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X33" t="n">
         <v>17.5</v>
@@ -8791,10 +8791,10 @@
         <v>14.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA33" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB33" t="n">
         <v>13.5</v>
@@ -8806,7 +8806,7 @@
         <v>13</v>
       </c>
       <c r="AE33" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF33" t="n">
         <v>18.5</v>
@@ -8851,7 +8851,7 @@
         <v>38</v>
       </c>
       <c r="AT33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU33" t="n">
         <v>7.6</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -866,37 +866,37 @@
         <v>1.75</v>
       </c>
       <c r="I2" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
         <v>2.58</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>1.46</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.47</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -905,19 +905,19 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -965,58 +965,58 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BE2" t="n">
         <v>130</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U3" t="n">
         <v>1.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z3" t="n">
         <v>40</v>
@@ -1177,70 +1177,70 @@
         <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
         <v>80</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
         <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
         <v>21</v>
       </c>
       <c r="AO3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>3.65</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX3" t="n">
         <v>4.2</v>
@@ -1249,40 +1249,40 @@
         <v>4.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE3" t="n">
         <v>85</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,40 +1291,40 @@
         <v>110</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV3" t="n">
         <v>44</v>
       </c>
       <c r="BW3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BX3" t="n">
         <v>60</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -1365,34 +1365,34 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H4" t="n">
         <v>2.72</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
@@ -1401,28 +1401,28 @@
         <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
         <v>23</v>
@@ -1431,46 +1431,46 @@
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
         <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
         <v>19.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AP4" t="n">
         <v>7</v>
@@ -1479,79 +1479,79 @@
         <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="AX4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF4" t="n">
         <v>6</v>
       </c>
-      <c r="AY4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB4" t="n">
+      <c r="BG4" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>6</v>
-      </c>
       <c r="BH4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN4" t="n">
         <v>5.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ4" t="n">
         <v>6</v>
@@ -1560,22 +1560,22 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT4" t="n">
         <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="n">
         <v>38</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -1619,64 +1619,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="Q5" t="n">
         <v>2.44</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
         <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1685,34 +1685,34 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>40</v>
+        <v>17.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>27</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1721,7 +1721,7 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
@@ -1733,22 +1733,22 @@
         <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
         <v>4.9</v>
@@ -1757,82 +1757,82 @@
         <v>5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.2</v>
+        <v>3.85</v>
       </c>
       <c r="BA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC5" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BD5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
         <v>6</v>
       </c>
-      <c r="BC5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.31</v>
+        <v>2.22</v>
       </c>
       <c r="BN5" t="n">
         <v>4.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.02</v>
+        <v>6.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.31</v>
+        <v>2.14</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.32</v>
+        <v>2.16</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.3</v>
+        <v>2.18</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -1873,67 +1873,67 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="G6" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M6" t="n">
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.48</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>1.06</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
@@ -1942,136 +1942,136 @@
         <v>7</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>700</v>
       </c>
       <c r="AF6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
         <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
         <v>700</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AL6" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
         <v>700</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY6" t="n">
         <v>5.2</v>
       </c>
-      <c r="AR6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK6" t="n">
         <v>6</v>
       </c>
-      <c r="BC6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BI6" t="n">
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
         <v>2.34</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>2.32</v>
-      </c>
       <c r="BN6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BP6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BT6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BU6" t="n">
         <v>5.1</v>
@@ -2080,7 +2080,7 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -2127,64 +2127,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
         <v>15</v>
@@ -2196,22 +2196,22 @@
         <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
         <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AF7" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AG7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -2220,7 +2220,7 @@
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
         <v>200</v>
@@ -2229,128 +2229,128 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>600</v>
+        <v>240</v>
       </c>
       <c r="AO7" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC7" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC7" t="n">
+      <c r="BD7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG7" t="n">
         <v>5.4</v>
       </c>
-      <c r="BD7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BH7" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10.5</v>
+        <v>2.56</v>
       </c>
       <c r="BN7" t="n">
         <v>7.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BV7" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G8" t="n">
         <v>1.7</v>
@@ -2390,34 +2390,34 @@
         <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
         <v>3.15</v>
@@ -2426,10 +2426,10 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
         <v>2.42</v>
@@ -2438,7 +2438,7 @@
         <v>90</v>
       </c>
       <c r="Y8" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
@@ -2447,34 +2447,34 @@
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AD8" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2492,13 +2492,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>2.44</v>
       </c>
       <c r="AT8" t="n">
         <v>4.4</v>
@@ -2507,94 +2507,94 @@
         <v>5.1</v>
       </c>
       <c r="AV8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY8" t="n">
         <v>5.2</v>
       </c>
-      <c r="AW8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>5.3</v>
+        <v>2.86</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.95</v>
+        <v>2.38</v>
       </c>
       <c r="BE8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BN8" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.13</v>
+        <v>2.26</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.26</v>
+        <v>2.82</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -2638,58 +2638,58 @@
         <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K9" t="n">
         <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T9" t="n">
         <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
         <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
@@ -2719,7 +2719,7 @@
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI9" t="n">
         <v>540</v>
@@ -2740,19 +2740,19 @@
         <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>5.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.4</v>
+        <v>3.55</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="AT9" t="n">
         <v>4.2</v>
@@ -2761,10 +2761,10 @@
         <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AX9" t="n">
         <v>6.4</v>
@@ -2776,25 +2776,25 @@
         <v>7</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC9" t="n">
         <v>7.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="BH9" t="n">
         <v>3.85</v>
@@ -2806,7 +2806,7 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2824,7 +2824,7 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2836,7 +2836,7 @@
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.36</v>
+        <v>4.3</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -2889,58 +2889,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="H10" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
         <v>1.95</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
         <v>13.5</v>
@@ -2955,10 +2955,10 @@
         <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
         <v>14</v>
@@ -2967,7 +2967,7 @@
         <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
@@ -2976,7 +2976,7 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ10" t="n">
         <v>42</v>
@@ -2988,16 +2988,16 @@
         <v>120</v>
       </c>
       <c r="AM10" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>32</v>
       </c>
       <c r="AO10" t="n">
-        <v>42</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ10" t="n">
         <v>9.6</v>
@@ -3006,19 +3006,19 @@
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX10" t="n">
         <v>14</v>
@@ -3027,10 +3027,10 @@
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BB10" t="n">
         <v>34</v>
@@ -3039,80 +3039,80 @@
         <v>26</v>
       </c>
       <c r="BD10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE10" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="BF10" t="n">
         <v>24</v>
       </c>
       <c r="BG10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="BJ10" t="n">
         <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP10" t="n">
         <v>24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BT10" t="n">
         <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -3146,22 +3146,22 @@
         <v>1.2</v>
       </c>
       <c r="G11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>21</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L11" t="n">
         <v>1.24</v>
-      </c>
-      <c r="H11" t="n">
-        <v>17</v>
-      </c>
-      <c r="I11" t="n">
-        <v>22</v>
-      </c>
-      <c r="J11" t="n">
-        <v>7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.2</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
@@ -3173,142 +3173,142 @@
         <v>1.14</v>
       </c>
       <c r="P11" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R11" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="X11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Z11" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD11" t="n">
         <v>70</v>
       </c>
       <c r="AE11" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="AF11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>9.4</v>
       </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>220</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AK11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL11" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AO11" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AT11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AW11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="AY11" t="n">
         <v>5.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="BG11" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="n">
         <v>5.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BJ11" t="n">
         <v>14</v>
@@ -3320,37 +3320,37 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP11" t="n">
         <v>6.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS11" t="n">
         <v>7.2</v>
       </c>
       <c r="BT11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
@@ -3362,11 +3362,11 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -3400,22 +3400,22 @@
         <v>5.4</v>
       </c>
       <c r="G12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="I12" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -3424,40 +3424,40 @@
         <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V12" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
         <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>40</v>
+        <v>17.5</v>
       </c>
       <c r="AA12" t="n">
         <v>180</v>
@@ -3481,7 +3481,7 @@
         <v>950</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
         <v>500</v>
@@ -3505,58 +3505,58 @@
         <v>29</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AQ12" t="n">
         <v>4.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS12" t="n">
         <v>5.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU12" t="n">
         <v>4.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="AW12" t="n">
         <v>5.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>6.2</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BA12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE12" t="n">
         <v>7</v>
       </c>
-      <c r="BB12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BF12" t="n">
-        <v>2.68</v>
+        <v>9</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="n">
         <v>3.75</v>
@@ -3565,19 +3565,19 @@
         <v>2.96</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO12" t="n">
         <v>4.9</v>
@@ -3586,13 +3586,13 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BT12" t="n">
         <v>4.4</v>
@@ -3601,26 +3601,26 @@
         <v>3.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -3651,61 +3651,61 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="G13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H13" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="I13" t="n">
         <v>16.5</v>
       </c>
       <c r="J13" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V13" t="n">
         <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y13" t="n">
         <v>44</v>
@@ -3717,16 +3717,16 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AE13" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -3741,94 +3741,94 @@
         <v>230</v>
       </c>
       <c r="AJ13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK13" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM13" t="n">
         <v>250</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AO13" t="n">
         <v>480</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AX13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC13" t="n">
         <v>6</v>
       </c>
-      <c r="AY13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BD13" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="n">
         <v>4.4</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BJ13" t="n">
         <v>14</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13" t="n">
         <v>3.8</v>
@@ -3840,7 +3840,7 @@
         <v>7.4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BR13" t="n">
         <v>26</v>
@@ -3849,32 +3849,32 @@
         <v>7.2</v>
       </c>
       <c r="BT13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA13" t="n">
         <v>5.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="H15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
         <v>2.04</v>
@@ -4201,22 +4201,22 @@
         <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="W15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
         <v>25</v>
       </c>
       <c r="Y15" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
         <v>970</v>
@@ -4240,7 +4240,7 @@
         <v>500</v>
       </c>
       <c r="AG15" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AH15" t="n">
         <v>29</v>
@@ -4261,7 +4261,7 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4276,113 +4276,113 @@
         <v>8.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AV15" t="n">
         <v>6.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
         <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC15" t="n">
         <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BE15" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="BF15" t="n">
         <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="n">
         <v>3.45</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>44</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT15" t="n">
         <v>5.4</v>
       </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BU15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>8.6</v>
+        <v>3.7</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -4413,64 +4413,64 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G16" t="n">
         <v>3.75</v>
       </c>
-      <c r="G16" t="n">
-        <v>3.85</v>
-      </c>
       <c r="H16" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S16" t="n">
         <v>3.45</v>
       </c>
-      <c r="K16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T16" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
         <v>2.16</v>
       </c>
       <c r="V16" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="W16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
         <v>18</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
         <v>17</v>
@@ -4485,10 +4485,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AF16" t="n">
         <v>34</v>
@@ -4509,34 +4509,34 @@
         <v>120</v>
       </c>
       <c r="AL16" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO16" t="n">
         <v>20</v>
       </c>
       <c r="AP16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="AT16" t="n">
         <v>8.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV16" t="n">
         <v>6.2</v>
@@ -4545,10 +4545,10 @@
         <v>19.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
@@ -4557,28 +4557,28 @@
         <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>23</v>
+        <v>5.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>34</v>
+        <v>5.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF16" t="n">
         <v>5.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.4</v>
@@ -4590,13 +4590,13 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="BN16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
@@ -4608,19 +4608,19 @@
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -4667,79 +4667,79 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I17" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="n">
-        <v>3.15</v>
-      </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="U17" t="n">
         <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE17" t="n">
         <v>40</v>
@@ -4751,34 +4751,34 @@
         <v>13</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
         <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="n">
         <v>36</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="AN17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR17" t="n">
         <v>16.5</v>
@@ -4790,7 +4790,7 @@
         <v>8.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
         <v>12</v>
@@ -4799,46 +4799,46 @@
         <v>32</v>
       </c>
       <c r="AX17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
         <v>17</v>
       </c>
       <c r="BA17" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF17" t="n">
         <v>10</v>
       </c>
-      <c r="BB17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>9</v>
-      </c>
       <c r="BG17" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="BH17" t="n">
         <v>3.1</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4853,19 +4853,19 @@
         <v>4.5</v>
       </c>
       <c r="BP17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR17" t="n">
         <v>42</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU17" t="n">
         <v>4.6</v>
@@ -4874,23 +4874,23 @@
         <v>26</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX17" t="n">
         <v>44</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ17" t="n">
         <v>40</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -4924,28 +4924,28 @@
         <v>1.27</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.1</v>
@@ -4954,13 +4954,13 @@
         <v>3.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="R18" t="n">
         <v>2.1</v>
       </c>
       <c r="S18" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="T18" t="n">
         <v>1.72</v>
@@ -4972,25 +4972,25 @@
         <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X18" t="n">
         <v>240</v>
       </c>
       <c r="Y18" t="n">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="Z18" t="n">
         <v>140</v>
       </c>
       <c r="AA18" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AB18" t="n">
-        <v>19.5</v>
+        <v>38</v>
       </c>
       <c r="AC18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AD18" t="n">
         <v>120</v>
@@ -4999,85 +4999,85 @@
         <v>160</v>
       </c>
       <c r="AF18" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI18" t="n">
         <v>390</v>
       </c>
       <c r="AJ18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK18" t="n">
         <v>14</v>
       </c>
       <c r="AL18" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM18" t="n">
         <v>320</v>
       </c>
       <c r="AN18" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AO18" t="n">
         <v>130</v>
       </c>
       <c r="AP18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AQ18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX18" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS18" t="n">
+      <c r="AY18" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE18" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="BG18" t="n">
         <v>10.5</v>
@@ -5086,31 +5086,31 @@
         <v>6.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BJ18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN18" t="n">
         <v>4.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BP18" t="n">
         <v>7</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR18" t="n">
         <v>17.5</v>
@@ -5128,23 +5128,23 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -5175,58 +5175,58 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H19" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
         <v>5.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.58</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.59</v>
-      </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
         <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X19" t="n">
         <v>24</v>
@@ -5238,37 +5238,37 @@
         <v>25</v>
       </c>
       <c r="AA19" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
         <v>15</v>
       </c>
       <c r="AI19" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ19" t="n">
         <v>36</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>32</v>
@@ -5280,85 +5280,85 @@
         <v>14</v>
       </c>
       <c r="AO19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP19" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="AR19" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="AS19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX19" t="n">
         <v>6</v>
       </c>
-      <c r="AT19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU19" t="n">
+      <c r="AY19" t="n">
         <v>7</v>
       </c>
-      <c r="AV19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="BA19" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BC19" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>38</v>
+        <v>7.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="BH19" t="n">
         <v>4.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BJ19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BK19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BN19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP19" t="n">
         <v>17</v>
@@ -5376,7 +5376,7 @@
         <v>6.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BV19" t="n">
         <v>21</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -5432,28 +5432,28 @@
         <v>2.94</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H20" t="n">
         <v>2.88</v>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J20" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="K20" t="n">
         <v>3.05</v>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
         <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
         <v>1.54</v>
@@ -5462,10 +5462,10 @@
         <v>1.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S20" t="n">
         <v>5.7</v>
@@ -5477,10 +5477,10 @@
         <v>1.77</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
         <v>8.199999999999999</v>
@@ -5492,7 +5492,7 @@
         <v>48</v>
       </c>
       <c r="AA20" t="n">
-        <v>900</v>
+        <v>420</v>
       </c>
       <c r="AB20" t="n">
         <v>9.4</v>
@@ -5537,58 +5537,58 @@
         <v>500</v>
       </c>
       <c r="AP20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY20" t="n">
         <v>5.9</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS20" t="n">
+      <c r="AZ20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA20" t="n">
         <v>8.6</v>
       </c>
-      <c r="AT20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW20" t="n">
+      <c r="BB20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF20" t="n">
         <v>8.4</v>
       </c>
-      <c r="AX20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC20" t="n">
+      <c r="BG20" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BH20" t="n">
         <v>2.74</v>
@@ -5606,43 +5606,43 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>11</v>
+        <v>2.2</v>
       </c>
       <c r="BN20" t="n">
         <v>6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8.4</v>
+        <v>2.06</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>9.800000000000001</v>
+        <v>2.14</v>
       </c>
       <c r="BT20" t="n">
         <v>5.9</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BV20" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.4</v>
+        <v>2.06</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.800000000000001</v>
+        <v>2.14</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -5683,82 +5683,82 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="G21" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="J21" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L21" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
         <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="O21" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="P21" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
         <v>14</v>
       </c>
       <c r="Y21" t="n">
-        <v>500</v>
+        <v>5.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AB21" t="n">
         <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AD21" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE21" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AF21" t="n">
         <v>500</v>
@@ -5785,118 +5785,118 @@
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO21" t="n">
         <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT21" t="n">
         <v>4.9</v>
       </c>
       <c r="AU21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE21" t="n">
         <v>6</v>
       </c>
-      <c r="AV21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>5.1</v>
       </c>
-      <c r="AX21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BE21" t="n">
+      <c r="BG21" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>7.2</v>
       </c>
       <c r="BH21" t="n">
         <v>2.58</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.4</v>
+        <v>2</v>
       </c>
       <c r="BT21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.6</v>
+        <v>1.87</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -5937,55 +5937,55 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="G22" t="n">
         <v>2.76</v>
       </c>
       <c r="H22" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="I22" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P22" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T22" t="n">
         <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
         <v>1.56</v>
@@ -5994,7 +5994,7 @@
         <v>17</v>
       </c>
       <c r="Y22" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z22" t="n">
         <v>970</v>
@@ -6015,7 +6015,7 @@
         <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG22" t="n">
         <v>970</v>
@@ -6027,7 +6027,7 @@
         <v>500</v>
       </c>
       <c r="AJ22" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
         <v>500</v>
@@ -6048,13 +6048,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AR22" t="n">
         <v>14</v>
       </c>
       <c r="AS22" t="n">
-        <v>18</v>
+        <v>8.4</v>
       </c>
       <c r="AT22" t="n">
         <v>7.2</v>
@@ -6075,25 +6075,25 @@
         <v>7.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB22" t="n">
         <v>8</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="BG22" t="n">
         <v>6.8</v>
@@ -6105,7 +6105,7 @@
         <v>2.42</v>
       </c>
       <c r="BJ22" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
         <v>5.3</v>
@@ -6114,7 +6114,7 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN22" t="n">
         <v>5.8</v>
@@ -6126,13 +6126,13 @@
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT22" t="n">
         <v>6.2</v>
@@ -6144,23 +6144,23 @@
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -6191,76 +6191,76 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I23" t="n">
         <v>4.4</v>
-      </c>
-      <c r="I23" t="n">
-        <v>4.5</v>
       </c>
       <c r="J23" t="n">
         <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L23" t="n">
         <v>1.51</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T23" t="n">
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W23" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X23" t="n">
         <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA23" t="n">
         <v>110</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD23" t="n">
         <v>17.5</v>
@@ -6275,34 +6275,34 @@
         <v>10.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
         <v>75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM23" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN23" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP23" t="n">
         <v>11</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
         <v>29</v>
@@ -6311,16 +6311,16 @@
         <v>95</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX23" t="n">
         <v>10</v>
@@ -6329,34 +6329,34 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BB23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD23" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE23" t="n">
         <v>100</v>
       </c>
       <c r="BF23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BG23" t="n">
         <v>75</v>
       </c>
       <c r="BH23" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
@@ -6365,28 +6365,28 @@
         <v>9.4</v>
       </c>
       <c r="BL23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BN23" t="n">
         <v>4.5</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ23" t="n">
         <v>11</v>
       </c>
       <c r="BR23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS23" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BT23" t="n">
         <v>7.8</v>
@@ -6398,13 +6398,13 @@
         <v>42</v>
       </c>
       <c r="BW23" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BX23" t="n">
         <v>55</v>
       </c>
       <c r="BY23" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -6451,64 +6451,64 @@
         <v>4.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="I24" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="J24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K24" t="n">
         <v>5.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="R24" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S24" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="T24" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U24" t="n">
         <v>2.88</v>
       </c>
       <c r="V24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W24" t="n">
         <v>1.31</v>
       </c>
       <c r="X24" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Y24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB24" t="n">
         <v>48</v>
@@ -6517,16 +6517,16 @@
         <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="AG24" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH24" t="n">
         <v>15.5</v>
@@ -6535,127 +6535,127 @@
         <v>40</v>
       </c>
       <c r="AJ24" t="n">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="AK24" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AL24" t="n">
         <v>80</v>
       </c>
       <c r="AM24" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO24" t="n">
         <v>6.4</v>
       </c>
       <c r="AP24" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="AX24" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>16</v>
+        <v>7.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BF24" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="BH24" t="n">
         <v>5.6</v>
       </c>
       <c r="BI24" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="BJ24" t="n">
         <v>8.6</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN24" t="n">
         <v>8.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP24" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BV24" t="n">
         <v>12</v>
       </c>
       <c r="BW24" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BX24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BY24" t="n">
         <v>6.8</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -6699,46 +6699,46 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G25" t="n">
         <v>1.4</v>
       </c>
       <c r="H25" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K25" t="n">
         <v>6.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="S25" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
         <v>1.91</v>
@@ -6762,7 +6762,7 @@
         <v>540</v>
       </c>
       <c r="AA25" t="n">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="AB25" t="n">
         <v>10.5</v>
@@ -6777,7 +6777,7 @@
         <v>160</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG25" t="n">
         <v>11</v>
@@ -6804,85 +6804,85 @@
         <v>5.2</v>
       </c>
       <c r="AO25" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AP25" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AT25" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX25" t="n">
         <v>8</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB25" t="n">
         <v>6.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>25</v>
+        <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BG25" t="n">
         <v>10.5</v>
       </c>
       <c r="BH25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BN25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP25" t="n">
         <v>8</v>
@@ -6894,35 +6894,35 @@
         <v>23</v>
       </c>
       <c r="BS25" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BT25" t="n">
         <v>14</v>
       </c>
       <c r="BU25" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BZ25" t="n">
         <v>12</v>
       </c>
       <c r="CA25" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G26" t="n">
         <v>3.95</v>
@@ -6962,16 +6962,16 @@
         <v>1.92</v>
       </c>
       <c r="I26" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="J26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
         <v>4.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
@@ -6983,160 +6983,160 @@
         <v>1.17</v>
       </c>
       <c r="P26" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S26" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U26" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V26" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Y26" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB26" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AC26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD26" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE26" t="n">
         <v>18.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG26" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AH26" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AJ26" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AK26" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL26" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM26" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO26" t="n">
         <v>8.4</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="AT26" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="AV26" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AX26" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG26" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>6.2</v>
       </c>
       <c r="BH26" t="n">
         <v>4.8</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BJ26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN26" t="n">
         <v>7.8</v>
       </c>
       <c r="BO26" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP26" t="n">
         <v>26</v>
@@ -7145,19 +7145,19 @@
         <v>8.6</v>
       </c>
       <c r="BR26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS26" t="n">
         <v>9</v>
       </c>
       <c r="BT26" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU26" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BV26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BW26" t="n">
         <v>6.4</v>
@@ -7169,14 +7169,14 @@
         <v>8</v>
       </c>
       <c r="BZ26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CA26" t="n">
         <v>6.6</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -7207,76 +7207,76 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="G27" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="H27" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M27" t="n">
         <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P27" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="R27" t="n">
         <v>1.96</v>
       </c>
       <c r="S27" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="T27" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="U27" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="V27" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="X27" t="n">
         <v>100</v>
       </c>
       <c r="Y27" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="Z27" t="n">
         <v>170</v>
       </c>
       <c r="AA27" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AB27" t="n">
         <v>16.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD27" t="n">
         <v>75</v>
@@ -7285,85 +7285,85 @@
         <v>190</v>
       </c>
       <c r="AF27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
         <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
         <v>150</v>
       </c>
       <c r="AJ27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK27" t="n">
         <v>14.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AM27" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN27" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AO27" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT27" t="n">
         <v>13.5</v>
       </c>
       <c r="AU27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX27" t="n">
         <v>12.5</v>
       </c>
-      <c r="AV27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW27" t="n">
+      <c r="AY27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE27" t="n">
         <v>9</v>
       </c>
-      <c r="AX27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF27" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BG27" t="n">
         <v>10.5</v>
@@ -7375,10 +7375,10 @@
         <v>4.4</v>
       </c>
       <c r="BJ27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
@@ -7387,16 +7387,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ27" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>4.8</v>
       </c>
       <c r="BR27" t="n">
         <v>17.5</v>
@@ -7405,10 +7405,10 @@
         <v>6.6</v>
       </c>
       <c r="BT27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU27" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
@@ -7420,7 +7420,7 @@
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ27" t="n">
         <v>9.199999999999999</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G28" t="n">
         <v>1.47</v>
       </c>
       <c r="H28" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J28" t="n">
         <v>5.1</v>
@@ -7479,40 +7479,40 @@
         <v>5.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R28" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="T28" t="n">
         <v>1.97</v>
       </c>
       <c r="U28" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X28" t="n">
         <v>21</v>
@@ -7524,7 +7524,7 @@
         <v>170</v>
       </c>
       <c r="AA28" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AB28" t="n">
         <v>9</v>
@@ -7536,19 +7536,19 @@
         <v>75</v>
       </c>
       <c r="AE28" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AF28" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
         <v>950</v>
       </c>
       <c r="AI28" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AJ28" t="n">
         <v>13</v>
@@ -7566,19 +7566,19 @@
         <v>6.8</v>
       </c>
       <c r="AO28" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP28" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ28" t="n">
         <v>21</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT28" t="n">
         <v>7.4</v>
@@ -7587,10 +7587,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX28" t="n">
         <v>7.6</v>
@@ -7602,7 +7602,7 @@
         <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BB28" t="n">
         <v>9.4</v>
@@ -7611,16 +7611,16 @@
         <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH28" t="n">
         <v>4.1</v>
@@ -7650,7 +7650,7 @@
         <v>9</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR28" t="n">
         <v>25</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -7715,49 +7715,49 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G29" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H29" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="R29" t="n">
         <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U29" t="n">
         <v>1.9</v>
@@ -7766,25 +7766,25 @@
         <v>1.27</v>
       </c>
       <c r="W29" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X29" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Y29" t="n">
         <v>14</v>
       </c>
       <c r="Z29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA29" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD29" t="n">
         <v>18.5</v>
@@ -7793,91 +7793,91 @@
         <v>70</v>
       </c>
       <c r="AF29" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
         <v>23</v>
       </c>
       <c r="AI29" t="n">
-        <v>490</v>
+        <v>85</v>
       </c>
       <c r="AJ29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM29" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="n">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR29" t="n">
         <v>14.5</v>
       </c>
       <c r="AS29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU29" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7</v>
-      </c>
       <c r="AV29" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="AX29" t="n">
         <v>10</v>
       </c>
       <c r="AY29" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BA29" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BB29" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD29" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BF29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG29" t="n">
-        <v>12.5</v>
+        <v>65</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI29" t="n">
         <v>2.5</v>
@@ -7886,13 +7886,13 @@
         <v>11</v>
       </c>
       <c r="BK29" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN29" t="n">
         <v>4.7</v>
@@ -7901,16 +7901,16 @@
         <v>3.55</v>
       </c>
       <c r="BP29" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR29" t="n">
         <v>34</v>
       </c>
       <c r="BS29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT29" t="n">
         <v>8</v>
@@ -7919,26 +7919,26 @@
         <v>5.8</v>
       </c>
       <c r="BV29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW29" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX29" t="n">
         <v>60</v>
       </c>
       <c r="BY29" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ29" t="n">
         <v>34</v>
       </c>
       <c r="CA29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G30" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H30" t="n">
         <v>6.6</v>
@@ -7981,46 +7981,46 @@
         <v>7</v>
       </c>
       <c r="J30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.55</v>
       </c>
-      <c r="K30" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M30" t="n">
         <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="O30" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P30" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R30" t="n">
         <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
         <v>1.64</v>
       </c>
       <c r="V30" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W30" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X30" t="n">
         <v>10.5</v>
@@ -8029,34 +8029,34 @@
         <v>16.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA30" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AB30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AC30" t="n">
         <v>9.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE30" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF30" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG30" t="n">
         <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI30" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ30" t="n">
         <v>19.5</v>
@@ -8068,25 +8068,25 @@
         <v>65</v>
       </c>
       <c r="AM30" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="n">
         <v>22</v>
       </c>
       <c r="AO30" t="n">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AP30" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>40</v>
       </c>
       <c r="AS30" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT30" t="n">
         <v>5.6</v>
@@ -8098,7 +8098,7 @@
         <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX30" t="n">
         <v>7.8</v>
@@ -8110,10 +8110,10 @@
         <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB30" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC30" t="n">
         <v>21</v>
@@ -8122,16 +8122,16 @@
         <v>46</v>
       </c>
       <c r="BE30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF30" t="n">
         <v>16</v>
       </c>
       <c r="BG30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH30" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BI30" t="n">
         <v>2.44</v>
@@ -8146,7 +8146,7 @@
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BN30" t="n">
         <v>4</v>
@@ -8158,31 +8158,31 @@
         <v>13.5</v>
       </c>
       <c r="BQ30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT30" t="n">
         <v>9.6</v>
       </c>
       <c r="BU30" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -8223,52 +8223,52 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G31" t="n">
         <v>1.18</v>
       </c>
       <c r="H31" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="L31" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M31" t="n">
         <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O31" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P31" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R31" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="S31" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="T31" t="n">
         <v>2.46</v>
       </c>
       <c r="U31" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="V31" t="n">
         <v>1.04</v>
@@ -8280,40 +8280,40 @@
         <v>36</v>
       </c>
       <c r="Y31" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="Z31" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AD31" t="n">
         <v>950</v>
       </c>
       <c r="AE31" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="AF31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG31" t="n">
         <v>15</v>
       </c>
       <c r="AH31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AI31" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AK31" t="n">
         <v>17.5</v>
@@ -8325,34 +8325,34 @@
         <v>360</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU31" t="n">
         <v>17</v>
       </c>
       <c r="AV31" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
         <v>6.2</v>
@@ -8361,28 +8361,28 @@
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC31" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF31" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="BG31" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH31" t="n">
         <v>5</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="G32" t="n">
         <v>1.93</v>
@@ -8486,13 +8486,13 @@
         <v>4.9</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J32" t="n">
         <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L32" t="n">
         <v>1.53</v>
@@ -8501,22 +8501,22 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P32" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="R32" t="n">
         <v>1.24</v>
       </c>
       <c r="S32" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T32" t="n">
         <v>2.12</v>
@@ -8525,22 +8525,22 @@
         <v>1.8</v>
       </c>
       <c r="V32" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W32" t="n">
         <v>2.06</v>
       </c>
       <c r="X32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z32" t="n">
         <v>38</v>
       </c>
       <c r="AA32" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AB32" t="n">
         <v>7</v>
@@ -8552,7 +8552,7 @@
         <v>21</v>
       </c>
       <c r="AE32" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF32" t="n">
         <v>10</v>
@@ -8561,88 +8561,88 @@
         <v>11</v>
       </c>
       <c r="AH32" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AI32" t="n">
         <v>110</v>
       </c>
       <c r="AJ32" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL32" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM32" t="n">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="AN32" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP32" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AS32" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU32" t="n">
         <v>7.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AX32" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BA32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB32" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC32" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD32" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE32" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF32" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ32" t="n">
         <v>11.5</v>
@@ -8657,13 +8657,13 @@
         <v>15.5</v>
       </c>
       <c r="BN32" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BP32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ32" t="n">
         <v>7.8</v>
@@ -8672,19 +8672,19 @@
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU32" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV32" t="n">
         <v>55</v>
       </c>
       <c r="BW32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -8734,61 +8734,61 @@
         <v>2.48</v>
       </c>
       <c r="G33" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H33" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="I33" t="n">
         <v>3.05</v>
       </c>
       <c r="J33" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M33" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N33" t="n">
         <v>4.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P33" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="R33" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="U33" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W33" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X33" t="n">
         <v>17.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z33" t="n">
         <v>22</v>
@@ -8797,10 +8797,10 @@
         <v>50</v>
       </c>
       <c r="AB33" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD33" t="n">
         <v>13</v>
@@ -8818,28 +8818,28 @@
         <v>16.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AJ33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK33" t="n">
         <v>27</v>
       </c>
       <c r="AL33" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM33" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AN33" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AO33" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AP33" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>12</v>
@@ -8851,7 +8851,7 @@
         <v>38</v>
       </c>
       <c r="AT33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU33" t="n">
         <v>7.6</v>
@@ -8863,7 +8863,7 @@
         <v>25</v>
       </c>
       <c r="AX33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY33" t="n">
         <v>10.5</v>
@@ -8872,7 +8872,7 @@
         <v>14</v>
       </c>
       <c r="BA33" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BB33" t="n">
         <v>32</v>
@@ -8881,13 +8881,13 @@
         <v>23</v>
       </c>
       <c r="BD33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE33" t="n">
         <v>55</v>
       </c>
       <c r="BF33" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG33" t="n">
         <v>17.5</v>
@@ -8896,13 +8896,13 @@
         <v>3.9</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK33" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
@@ -8917,7 +8917,7 @@
         <v>4.4</v>
       </c>
       <c r="BP33" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ33" t="n">
         <v>7</v>
@@ -8926,7 +8926,7 @@
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT33" t="n">
         <v>6.4</v>
@@ -8947,14 +8947,14 @@
         <v>8.4</v>
       </c>
       <c r="BZ33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA33" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -857,178 +857,178 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="G2" t="n">
-        <v>600</v>
+        <v>4.9</v>
       </c>
       <c r="H2" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J2" t="n">
-        <v>2.58</v>
+        <v>2.94</v>
       </c>
       <c r="K2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG2" t="n">
         <v>950</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="AH2" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>5.5</v>
       </c>
-      <c r="T2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X2" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BA2" t="n">
-        <v>1.21</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.21</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.21</v>
+        <v>6.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.21</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
         <v>130</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.21</v>
+        <v>6.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.21</v>
+        <v>5.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,40 +1037,40 @@
         <v>150</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -1111,178 +1111,178 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.88</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="AB3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC3" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AF3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
         <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="AN3" t="n">
         <v>21</v>
       </c>
       <c r="AO3" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.1</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BE3" t="n">
         <v>85</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="BG3" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,40 +1291,40 @@
         <v>110</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BP3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>960</v>
       </c>
       <c r="BY3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -1365,217 +1365,217 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AM4" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO4" t="n">
         <v>500</v>
       </c>
-      <c r="AN4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>28</v>
-      </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>80</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="BS4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT4" t="n">
         <v>6.8</v>
       </c>
-      <c r="BT4" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BU4" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
         <v>38</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -1619,100 +1619,100 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="P5" t="n">
         <v>1.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U5" t="n">
         <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>30</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1727,112 +1727,112 @@
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.75</v>
+        <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.85</v>
+        <v>22</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.75</v>
+        <v>18.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>42</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>130</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.22</v>
+        <v>90</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.14</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
         <v>9</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>2.16</v>
+        <v>11</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.18</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -1873,64 +1873,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
         <v>4.8</v>
       </c>
       <c r="I6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
         <v>5.8</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="V6" t="n">
         <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
         <v>120</v>
@@ -1939,10 +1939,10 @@
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
         <v>23</v>
@@ -1954,19 +1954,19 @@
         <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AI6" t="n">
         <v>700</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AK6" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
         <v>180</v>
@@ -1975,118 +1975,118 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AO6" t="n">
         <v>700</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AS6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX6" t="n">
         <v>9</v>
       </c>
-      <c r="AT6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AY6" t="n">
-        <v>5.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="BG6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="BJ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
         <v>12</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>2.34</v>
       </c>
       <c r="BN6" t="n">
         <v>4.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BP6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.22</v>
+        <v>10</v>
       </c>
       <c r="BT6" t="n">
         <v>9</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.28</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.28</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -2127,94 +2127,94 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="I7" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.85</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z7" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z7" t="n">
-        <v>15</v>
-      </c>
       <c r="AA7" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AG7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
@@ -2223,134 +2223,134 @@
         <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="AO7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW7" t="n">
         <v>17.5</v>
       </c>
-      <c r="AP7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6</v>
-      </c>
       <c r="AX7" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.3</v>
+        <v>18.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.56</v>
+        <v>14</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BV7" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BW7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BX7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BZ7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -2381,64 +2381,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
@@ -2447,34 +2447,34 @@
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>27</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="AH8" t="n">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AI8" t="n">
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2483,7 +2483,7 @@
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
         <v>700</v>
@@ -2492,109 +2492,109 @@
         <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.1</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.44</v>
+        <v>10.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.55</v>
+        <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.46</v>
+        <v>10</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.86</v>
+        <v>14.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.44</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.8</v>
+        <v>12.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.38</v>
+        <v>9</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.46</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.44</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.55</v>
+        <v>5.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.37</v>
+        <v>3.5</v>
       </c>
       <c r="BN8" t="n">
         <v>4.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.26</v>
+        <v>5.9</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.37</v>
+        <v>4.7</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BU8" t="n">
-        <v>2.82</v>
+        <v>5.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.34</v>
+        <v>3.55</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -2635,61 +2635,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.3</v>
       </c>
-      <c r="I9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
         <v>1.71</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
         <v>1.64</v>
       </c>
       <c r="X9" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
@@ -2719,13 +2719,13 @@
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
         <v>540</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AK9" t="n">
         <v>500</v>
@@ -2743,16 +2743,16 @@
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>5.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.55</v>
+        <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="AT9" t="n">
         <v>4.2</v>
@@ -2761,43 +2761,43 @@
         <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.14</v>
+        <v>9.4</v>
       </c>
       <c r="AX9" t="n">
         <v>6.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF9" t="n">
         <v>8.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.85</v>
+        <v>2.72</v>
       </c>
       <c r="BI9" t="n">
         <v>2.26</v>
@@ -2806,49 +2806,49 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.09</v>
+        <v>1.7</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.35</v>
+        <v>2.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.09</v>
+        <v>1.68</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.09</v>
+        <v>1.74</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.07</v>
+        <v>1.7</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -2889,136 +2889,136 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
         <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z10" t="n">
         <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK10" t="n">
         <v>34</v>
       </c>
       <c r="AL10" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AR10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS10" t="n">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="AT10" t="n">
         <v>7.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="AX10" t="n">
         <v>14</v>
@@ -3027,92 +3027,92 @@
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BB10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD10" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BE10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>11</v>
-      </c>
       <c r="BK10" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="BN10" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
         <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BV10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BZ10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -3146,19 +3146,19 @@
         <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="I11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="K11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.24</v>
@@ -3182,19 +3182,19 @@
         <v>1.8</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="X11" t="n">
         <v>40</v>
@@ -3212,118 +3212,118 @@
         <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AD11" t="n">
         <v>70</v>
       </c>
       <c r="AE11" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AF11" t="n">
         <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>40</v>
       </c>
       <c r="AI11" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AK11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN11" t="n">
         <v>3.45</v>
       </c>
       <c r="AO11" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="AV11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="n">
         <v>5.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ11" t="n">
         <v>14</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO11" t="n">
         <v>3</v>
@@ -3338,7 +3338,7 @@
         <v>23</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT11" t="n">
         <v>19</v>
@@ -3350,13 +3350,13 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
         <v>8.199999999999999</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -3397,61 +3397,61 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="I12" t="n">
         <v>1.69</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U12" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y12" t="n">
         <v>14</v>
@@ -3481,7 +3481,7 @@
         <v>950</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI12" t="n">
         <v>500</v>
@@ -3505,79 +3505,79 @@
         <v>29</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU12" t="n">
         <v>4.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF12" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>9</v>
       </c>
       <c r="BG12" t="n">
         <v>4.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO12" t="n">
         <v>4.9</v>
@@ -3586,41 +3586,41 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="G13" t="n">
         <v>1.31</v>
       </c>
       <c r="H13" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="I13" t="n">
         <v>16.5</v>
       </c>
       <c r="J13" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="K13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
         <v>1.31</v>
@@ -3675,28 +3675,28 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T13" t="n">
         <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
         <v>1.06</v>
@@ -3711,7 +3711,7 @@
         <v>44</v>
       </c>
       <c r="Z13" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -3726,7 +3726,7 @@
         <v>130</v>
       </c>
       <c r="AE13" t="n">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -3735,10 +3735,10 @@
         <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI13" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AJ13" t="n">
         <v>9.800000000000001</v>
@@ -3750,85 +3750,85 @@
         <v>46</v>
       </c>
       <c r="AM13" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN13" t="n">
         <v>4.9</v>
       </c>
       <c r="AO13" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BD13" t="n">
         <v>9.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BH13" t="n">
         <v>4.4</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="BN13" t="n">
         <v>3.8</v>
@@ -3840,41 +3840,41 @@
         <v>7.4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
         <v>11.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
         <v>3.55</v>
@@ -4189,34 +4189,34 @@
         <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q15" t="n">
         <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
         <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X15" t="n">
         <v>25</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
         <v>970</v>
@@ -4267,10 +4267,10 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR15" t="n">
         <v>8.4</v>
@@ -4279,19 +4279,19 @@
         <v>16</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="AU15" t="n">
         <v>5.7</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AX15" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
         <v>11</v>
@@ -4300,31 +4300,31 @@
         <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BB15" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC15" t="n">
         <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4336,53 +4336,53 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>3.25</v>
+        <v>2.14</v>
       </c>
       <c r="BN15" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BO15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.7</v>
+        <v>2.24</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="BT15" t="n">
         <v>5.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.7</v>
+        <v>2.26</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J16" t="n">
         <v>3.5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.4</v>
       </c>
       <c r="K16" t="n">
         <v>3.7</v>
@@ -4440,73 +4440,73 @@
         <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
         <v>2.16</v>
       </c>
       <c r="V16" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="W16" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y16" t="n">
         <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="AB16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE16" t="n">
         <v>65</v>
       </c>
       <c r="AF16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AG16" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="n">
         <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
         <v>150</v>
@@ -4518,82 +4518,82 @@
         <v>600</v>
       </c>
       <c r="AO16" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16" t="n">
         <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
         <v>19.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.4</v>
+        <v>17.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.4</v>
+        <v>32</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.3</v>
+        <v>25</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.3</v>
+        <v>28</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.5</v>
+        <v>42</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.4</v>
       </c>
       <c r="BK16" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="BN16" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
         <v>5.3</v>
@@ -4602,41 +4602,41 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.199999999999999</v>
+        <v>3.85</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -4667,154 +4667,154 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="G17" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="I17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N17" t="n">
         <v>3</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="X17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y17" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y17" t="n">
-        <v>10.5</v>
-      </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AA17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE17" t="n">
         <v>50</v>
       </c>
-      <c r="AB17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>40</v>
-      </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="AK17" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>140</v>
       </c>
       <c r="AN17" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AO17" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX17" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BB17" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BC17" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
         <v>44</v>
@@ -4823,22 +4823,22 @@
         <v>12.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BG17" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4847,40 +4847,40 @@
         <v>10</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BP17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS17" t="n">
         <v>8.4</v>
       </c>
       <c r="BT17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV17" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX17" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ17" t="n">
         <v>40</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -4927,16 +4927,16 @@
         <v>1.29</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I18" t="n">
         <v>12.5</v>
       </c>
       <c r="J18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>1.2</v>
@@ -4945,28 +4945,28 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S18" t="n">
         <v>1.84</v>
       </c>
       <c r="T18" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
         <v>1.08</v>
@@ -4975,7 +4975,7 @@
         <v>4.3</v>
       </c>
       <c r="X18" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="Y18" t="n">
         <v>460</v>
@@ -4984,10 +4984,10 @@
         <v>140</v>
       </c>
       <c r="AA18" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AB18" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="AC18" t="n">
         <v>25</v>
@@ -4996,10 +4996,10 @@
         <v>120</v>
       </c>
       <c r="AE18" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG18" t="n">
         <v>12.5</v>
@@ -5014,137 +5014,137 @@
         <v>12</v>
       </c>
       <c r="AK18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM18" t="n">
         <v>320</v>
       </c>
       <c r="AN18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AO18" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB18" t="n">
         <v>10</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BC18" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BE18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BG18" t="n">
         <v>11</v>
       </c>
-      <c r="BF18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BH18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BI18" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BJ18" t="n">
         <v>11</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP18" t="n">
         <v>7</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR18" t="n">
         <v>17.5</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT18" t="n">
         <v>15</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BZ18" t="n">
         <v>7.2</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G19" t="n">
         <v>2.54</v>
       </c>
       <c r="H19" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -5190,10 +5190,10 @@
         <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
@@ -5202,25 +5202,25 @@
         <v>5.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P19" t="n">
         <v>2.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R19" t="n">
         <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T19" t="n">
         <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="V19" t="n">
         <v>1.5</v>
@@ -5229,28 +5229,28 @@
         <v>1.64</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB19" t="n">
         <v>16</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF19" t="n">
         <v>20</v>
@@ -5262,7 +5262,7 @@
         <v>15</v>
       </c>
       <c r="AI19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ19" t="n">
         <v>36</v>
@@ -5277,106 +5277,106 @@
         <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO19" t="n">
         <v>19</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="BG19" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BJ19" t="n">
         <v>9</v>
       </c>
       <c r="BK19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BP19" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ19" t="n">
         <v>6.2</v>
       </c>
       <c r="BR19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS19" t="n">
         <v>7</v>
       </c>
       <c r="BT19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BV19" t="n">
         <v>21</v>
@@ -5391,14 +5391,14 @@
         <v>7.2</v>
       </c>
       <c r="BZ19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CA19" t="n">
         <v>6.2</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
         <v>2.88</v>
       </c>
       <c r="I20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>2.74</v>
@@ -5456,13 +5456,13 @@
         <v>2.56</v>
       </c>
       <c r="O20" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R20" t="n">
         <v>1.17</v>
@@ -5471,10 +5471,10 @@
         <v>5.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V20" t="n">
         <v>1.46</v>
@@ -5489,7 +5489,7 @@
         <v>9.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
         <v>420</v>
@@ -5507,13 +5507,13 @@
         <v>290</v>
       </c>
       <c r="AF20" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
@@ -5531,31 +5531,31 @@
         <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO20" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP20" t="n">
         <v>4.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS20" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AW20" t="n">
         <v>8</v>
@@ -5564,10 +5564,10 @@
         <v>6.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA20" t="n">
         <v>8.6</v>
@@ -5582,13 +5582,13 @@
         <v>8.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF20" t="n">
         <v>8.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH20" t="n">
         <v>2.74</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="BN20" t="n">
         <v>6</v>
@@ -5618,13 +5618,13 @@
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>2.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT20" t="n">
         <v>5.9</v>
@@ -5636,13 +5636,13 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="H21" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I21" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J21" t="n">
         <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L21" t="n">
         <v>1.67</v>
@@ -5722,7 +5722,7 @@
         <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="T21" t="n">
         <v>2.32</v>
@@ -5734,7 +5734,7 @@
         <v>1.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X21" t="n">
         <v>14</v>
@@ -5752,7 +5752,7 @@
         <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="AD21" t="n">
         <v>36</v>
@@ -5779,76 +5779,76 @@
         <v>500</v>
       </c>
       <c r="AL21" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AM21" t="n">
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AT21" t="n">
         <v>4.9</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH21" t="n">
         <v>2.58</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
@@ -5860,43 +5860,43 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="BT21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.87</v>
+        <v>6.8</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -5937,79 +5937,79 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
         <v>2.76</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I22" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K22" t="n">
         <v>3.45</v>
       </c>
       <c r="L22" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W22" t="n">
         <v>1.56</v>
       </c>
       <c r="X22" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
         <v>18</v>
       </c>
       <c r="Z22" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC22" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AE22" t="n">
         <v>500</v>
@@ -6021,7 +6021,7 @@
         <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI22" t="n">
         <v>500</v>
@@ -6045,52 +6045,52 @@
         <v>500</v>
       </c>
       <c r="AP22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX22" t="n">
         <v>8.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB22" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BC22" t="n">
         <v>25</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BF22" t="n">
         <v>25</v>
@@ -6099,40 +6099,40 @@
         <v>6.8</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT22" t="n">
         <v>6.2</v>
@@ -6144,23 +6144,23 @@
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -6191,61 +6191,61 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L23" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M23" t="n">
         <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P23" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.27</v>
       </c>
-      <c r="S23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.29</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y23" t="n">
         <v>13</v>
@@ -6257,67 +6257,67 @@
         <v>110</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD23" t="n">
         <v>17.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG23" t="n">
         <v>11</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
         <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM23" t="n">
         <v>140</v>
       </c>
       <c r="AN23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
         <v>95</v>
       </c>
       <c r="AP23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>12</v>
       </c>
       <c r="AR23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS23" t="n">
         <v>95</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW23" t="n">
         <v>60</v>
@@ -6326,82 +6326,82 @@
         <v>10</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
         <v>21</v>
       </c>
       <c r="BA23" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE23" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BH23" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BJ23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK23" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BL23" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="BM23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BN23" t="n">
         <v>4.5</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP23" t="n">
         <v>15</v>
       </c>
       <c r="BQ23" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BR23" t="n">
         <v>34</v>
       </c>
       <c r="BS23" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BT23" t="n">
         <v>7.8</v>
       </c>
       <c r="BU23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BX23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY23" t="n">
         <v>16.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -6448,10 +6448,10 @@
         <v>3.7</v>
       </c>
       <c r="G24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I24" t="n">
         <v>1.93</v>
@@ -6460,7 +6460,7 @@
         <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.22</v>
@@ -6484,10 +6484,10 @@
         <v>1.9</v>
       </c>
       <c r="S24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T24" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U24" t="n">
         <v>2.88</v>
@@ -6496,28 +6496,28 @@
         <v>2.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X24" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Y24" t="n">
         <v>20</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA24" t="n">
         <v>25</v>
       </c>
       <c r="AB24" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AC24" t="n">
         <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE24" t="n">
         <v>17.5</v>
@@ -6526,10 +6526,10 @@
         <v>140</v>
       </c>
       <c r="AG24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI24" t="n">
         <v>40</v>
@@ -6538,7 +6538,7 @@
         <v>500</v>
       </c>
       <c r="AK24" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AL24" t="n">
         <v>80</v>
@@ -6550,125 +6550,125 @@
         <v>20</v>
       </c>
       <c r="AO24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AP24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT24" t="n">
         <v>8</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AU24" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="BE24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF24" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ24" t="n">
         <v>8.6</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT24" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV24" t="n">
         <v>12</v>
       </c>
       <c r="BW24" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BX24" t="n">
         <v>18.5</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ24" t="n">
         <v>11</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -6702,40 +6702,40 @@
         <v>1.36</v>
       </c>
       <c r="G25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H25" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J25" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.29</v>
       </c>
       <c r="M25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
         <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P25" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q25" t="n">
         <v>1.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S25" t="n">
         <v>2.5</v>
@@ -6744,13 +6744,13 @@
         <v>1.91</v>
       </c>
       <c r="U25" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X25" t="n">
         <v>44</v>
@@ -6762,22 +6762,22 @@
         <v>540</v>
       </c>
       <c r="AA25" t="n">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="AB25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD25" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AE25" t="n">
         <v>160</v>
       </c>
       <c r="AF25" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG25" t="n">
         <v>11</v>
@@ -6801,128 +6801,128 @@
         <v>390</v>
       </c>
       <c r="AN25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO25" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7.4</v>
+        <v>17.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY25" t="n">
         <v>9</v>
       </c>
-      <c r="AT25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="BG25" t="n">
         <v>10.5</v>
       </c>
       <c r="BH25" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BN25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP25" t="n">
         <v>8</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BR25" t="n">
         <v>23</v>
       </c>
       <c r="BS25" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BT25" t="n">
         <v>14</v>
       </c>
       <c r="BU25" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BZ25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         <v>3.95</v>
       </c>
       <c r="H26" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I26" t="n">
         <v>1.99</v>
@@ -6971,34 +6971,34 @@
         <v>4.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P26" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T26" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="U26" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="V26" t="n">
         <v>2</v>
@@ -7007,13 +7007,13 @@
         <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="Y26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z26" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA26" t="n">
         <v>24</v>
@@ -7028,155 +7028,155 @@
         <v>11.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF26" t="n">
         <v>34</v>
       </c>
       <c r="AG26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH26" t="n">
         <v>15.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AK26" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AL26" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AM26" t="n">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="AN26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO26" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AV26" t="n">
         <v>6.2</v>
       </c>
       <c r="AW26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>7.2</v>
       </c>
-      <c r="AX26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BA26" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF26" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH26" t="n">
         <v>4.8</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BJ26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BN26" t="n">
         <v>7.8</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BP26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ26" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BR26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT26" t="n">
         <v>5.3</v>
       </c>
       <c r="BU26" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BV26" t="n">
         <v>12.5</v>
       </c>
       <c r="BW26" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BX26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY26" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CA26" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -7216,13 +7216,13 @@
         <v>6.2</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J27" t="n">
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L27" t="n">
         <v>1.21</v>
@@ -7234,7 +7234,7 @@
         <v>8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P27" t="n">
         <v>3.35</v>
@@ -7249,16 +7249,16 @@
         <v>1.96</v>
       </c>
       <c r="T27" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U27" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="V27" t="n">
         <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X27" t="n">
         <v>100</v>
@@ -7273,10 +7273,10 @@
         <v>170</v>
       </c>
       <c r="AB27" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD27" t="n">
         <v>75</v>
@@ -7285,7 +7285,7 @@
         <v>190</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG27" t="n">
         <v>11.5</v>
@@ -7297,7 +7297,7 @@
         <v>150</v>
       </c>
       <c r="AJ27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK27" t="n">
         <v>14.5</v>
@@ -7309,22 +7309,22 @@
         <v>60</v>
       </c>
       <c r="AN27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT27" t="n">
         <v>13.5</v>
@@ -7333,13 +7333,13 @@
         <v>11.5</v>
       </c>
       <c r="AV27" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AW27" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY27" t="n">
         <v>9.4</v>
@@ -7360,77 +7360,77 @@
         <v>19</v>
       </c>
       <c r="BE27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BG27" t="n">
         <v>10.5</v>
       </c>
       <c r="BH27" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.6</v>
       </c>
       <c r="BK27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ27" t="n">
         <v>5</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>4.9</v>
       </c>
       <c r="BR27" t="n">
         <v>17.5</v>
       </c>
       <c r="BS27" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BT27" t="n">
         <v>11</v>
       </c>
       <c r="BU27" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G28" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J28" t="n">
         <v>5.1</v>
@@ -7491,28 +7491,28 @@
         <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U28" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V28" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W28" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X28" t="n">
         <v>21</v>
@@ -7566,7 +7566,7 @@
         <v>6.8</v>
       </c>
       <c r="AO28" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP28" t="n">
         <v>16.5</v>
@@ -7590,7 +7590,7 @@
         <v>25</v>
       </c>
       <c r="AW28" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX28" t="n">
         <v>7.6</v>
@@ -7626,65 +7626,65 @@
         <v>4.1</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ28" t="n">
         <v>12</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN28" t="n">
         <v>4.1</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BP28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR28" t="n">
         <v>25</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT28" t="n">
         <v>12.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA28" t="n">
         <v>6</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H29" t="n">
         <v>4.3</v>
@@ -7739,13 +7739,13 @@
         <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
         <v>1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q29" t="n">
         <v>2.26</v>
@@ -7760,19 +7760,19 @@
         <v>1.97</v>
       </c>
       <c r="U29" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W29" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X29" t="n">
         <v>12</v>
       </c>
       <c r="Y29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z29" t="n">
         <v>32</v>
@@ -7787,7 +7787,7 @@
         <v>8</v>
       </c>
       <c r="AD29" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
         <v>70</v>
@@ -7796,31 +7796,31 @@
         <v>11.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="n">
         <v>25</v>
       </c>
       <c r="AK29" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL29" t="n">
         <v>46</v>
       </c>
       <c r="AM29" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="AN29" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP29" t="n">
         <v>10</v>
@@ -7829,10 +7829,10 @@
         <v>12.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="AS29" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT29" t="n">
         <v>7</v>
@@ -7844,7 +7844,7 @@
         <v>16.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AX29" t="n">
         <v>10</v>
@@ -7856,7 +7856,7 @@
         <v>19</v>
       </c>
       <c r="BA29" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
@@ -7868,13 +7868,13 @@
         <v>38</v>
       </c>
       <c r="BE29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF29" t="n">
         <v>16</v>
       </c>
       <c r="BG29" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="BH29" t="n">
         <v>3.15</v>
@@ -7886,59 +7886,59 @@
         <v>11</v>
       </c>
       <c r="BK29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN29" t="n">
         <v>4.7</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP29" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR29" t="n">
         <v>34</v>
       </c>
       <c r="BS29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT29" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU29" t="n">
         <v>5.8</v>
       </c>
       <c r="BV29" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY29" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ29" t="n">
         <v>34</v>
       </c>
       <c r="CA29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G30" t="n">
         <v>1.77</v>
@@ -7978,31 +7978,31 @@
         <v>6.6</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J30" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
         <v>3.55</v>
       </c>
       <c r="L30" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M30" t="n">
         <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="O30" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P30" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R30" t="n">
         <v>1.2</v>
@@ -8011,7 +8011,7 @@
         <v>5.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
         <v>1.64</v>
@@ -8023,7 +8023,7 @@
         <v>2.28</v>
       </c>
       <c r="X30" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y30" t="n">
         <v>16.5</v>
@@ -8038,22 +8038,22 @@
         <v>6</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD30" t="n">
         <v>29</v>
       </c>
       <c r="AE30" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF30" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG30" t="n">
         <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI30" t="n">
         <v>170</v>
@@ -8068,13 +8068,13 @@
         <v>65</v>
       </c>
       <c r="AM30" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AN30" t="n">
         <v>22</v>
       </c>
       <c r="AO30" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="AP30" t="n">
         <v>7.8</v>
@@ -8086,7 +8086,7 @@
         <v>40</v>
       </c>
       <c r="AS30" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AT30" t="n">
         <v>5.6</v>
@@ -8098,7 +8098,7 @@
         <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX30" t="n">
         <v>7.8</v>
@@ -8107,10 +8107,10 @@
         <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BB30" t="n">
         <v>16.5</v>
@@ -8122,19 +8122,19 @@
         <v>46</v>
       </c>
       <c r="BE30" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF30" t="n">
         <v>16</v>
       </c>
       <c r="BG30" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BH30" t="n">
         <v>2.78</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ30" t="n">
         <v>12.5</v>
@@ -8146,16 +8146,16 @@
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BN30" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO30" t="n">
         <v>3.6</v>
       </c>
       <c r="BP30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ30" t="n">
         <v>8</v>
@@ -8164,35 +8164,35 @@
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT30" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU30" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -8235,10 +8235,10 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.27</v>
@@ -8253,7 +8253,7 @@
         <v>1.17</v>
       </c>
       <c r="P31" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q31" t="n">
         <v>1.53</v>
@@ -8265,10 +8265,10 @@
         <v>2.36</v>
       </c>
       <c r="T31" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="U31" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="V31" t="n">
         <v>1.04</v>
@@ -8283,7 +8283,7 @@
         <v>950</v>
       </c>
       <c r="Z31" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
@@ -8298,7 +8298,7 @@
         <v>950</v>
       </c>
       <c r="AE31" t="n">
-        <v>530</v>
+        <v>430</v>
       </c>
       <c r="AF31" t="n">
         <v>7.6</v>
@@ -8307,52 +8307,52 @@
         <v>15</v>
       </c>
       <c r="AH31" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AI31" t="n">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="AJ31" t="n">
         <v>8.4</v>
       </c>
       <c r="AK31" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM31" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW31" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>8</v>
       </c>
       <c r="AX31" t="n">
         <v>6.2</v>
@@ -8364,7 +8364,7 @@
         <v>7.2</v>
       </c>
       <c r="BA31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB31" t="n">
         <v>7</v>
@@ -8373,16 +8373,16 @@
         <v>12.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH31" t="n">
         <v>5</v>
@@ -8391,16 +8391,16 @@
         <v>4.2</v>
       </c>
       <c r="BJ31" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BK31" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN31" t="n">
         <v>3.7</v>
@@ -8415,38 +8415,38 @@
         <v>5.1</v>
       </c>
       <c r="BR31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BS31" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BU31" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ31" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CA31" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="H32" t="n">
         <v>4.9</v>
       </c>
       <c r="I32" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K32" t="n">
         <v>3.6</v>
@@ -8507,7 +8507,7 @@
         <v>1.47</v>
       </c>
       <c r="P32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q32" t="n">
         <v>2.44</v>
@@ -8519,52 +8519,52 @@
         <v>4.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U32" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V32" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W32" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y32" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="Z32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA32" t="n">
         <v>150</v>
       </c>
       <c r="AB32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE32" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF32" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI32" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ32" t="n">
         <v>24</v>
@@ -8573,13 +8573,13 @@
         <v>23</v>
       </c>
       <c r="AL32" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM32" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN32" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AO32" t="n">
         <v>130</v>
@@ -8591,22 +8591,22 @@
         <v>12.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS32" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AT32" t="n">
         <v>6.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV32" t="n">
         <v>18.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="AX32" t="n">
         <v>9</v>
@@ -8615,10 +8615,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA32" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BB32" t="n">
         <v>19</v>
@@ -8627,34 +8627,34 @@
         <v>20</v>
       </c>
       <c r="BD32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF32" t="n">
         <v>16.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ32" t="n">
         <v>11.5</v>
       </c>
       <c r="BK32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN32" t="n">
         <v>4.3</v>
@@ -8666,16 +8666,16 @@
         <v>14.5</v>
       </c>
       <c r="BQ32" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT32" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU32" t="n">
         <v>5.7</v>
@@ -8684,23 +8684,23 @@
         <v>55</v>
       </c>
       <c r="BW32" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ32" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -8731,16 +8731,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="G33" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="H33" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="I33" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>3.65</v>
@@ -8761,10 +8761,10 @@
         <v>1.29</v>
       </c>
       <c r="P33" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R33" t="n">
         <v>1.42</v>
@@ -8773,34 +8773,34 @@
         <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U33" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V33" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W33" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="X33" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB33" t="n">
         <v>12.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD33" t="n">
         <v>13</v>
@@ -8818,13 +8818,13 @@
         <v>16.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL33" t="n">
         <v>42</v>
@@ -8836,7 +8836,7 @@
         <v>22</v>
       </c>
       <c r="AO33" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP33" t="n">
         <v>13.5</v>
@@ -8872,7 +8872,7 @@
         <v>14</v>
       </c>
       <c r="BA33" t="n">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="BB33" t="n">
         <v>32</v>
@@ -8884,31 +8884,31 @@
         <v>32</v>
       </c>
       <c r="BE33" t="n">
-        <v>55</v>
+        <v>9.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG33" t="n">
         <v>17.5</v>
       </c>
       <c r="BH33" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN33" t="n">
         <v>5.8</v>
@@ -8920,13 +8920,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ33" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT33" t="n">
         <v>6.4</v>
@@ -8938,23 +8938,23 @@
         <v>970</v>
       </c>
       <c r="BW33" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ33" t="n">
         <v>23</v>
       </c>
       <c r="CA33" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24</v>
+      </c>
+      <c r="I2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.6</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="V2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W2" t="n">
         <v>6.6</v>
       </c>
-      <c r="J2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.62</v>
-      </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="Z2" t="n">
-        <v>50</v>
+        <v>290</v>
       </c>
       <c r="AA2" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="AE2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>370</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="AK2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>340</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>15.5</v>
       </c>
-      <c r="AL2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>10</v>
-      </c>
       <c r="BK2" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS2" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BV2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
         <v>15.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>16.5</v>
+        <v>8.4</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -1097,244 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="H3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.1</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="U3" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>110</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>160</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX3" t="n">
+      <c r="BK3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>140</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP3" t="n">
         <v>11</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BQ3" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>100</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>170</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>130</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>9</v>
       </c>
       <c r="BR3" t="n">
         <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BV3" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="BX3" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="BY3" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="CA3" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -1356,239 +1356,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>1.19</v>
+        <v>1.77</v>
       </c>
       <c r="H4" t="n">
-        <v>19.5</v>
+        <v>6.6</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>9.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.54</v>
+        <v>2.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.71</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>2.36</v>
+        <v>5.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="X4" t="n">
-        <v>36</v>
+        <v>8.4</v>
       </c>
       <c r="Y4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>830</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS4" t="n">
         <v>60</v>
       </c>
-      <c r="Z4" t="n">
-        <v>210</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AT4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>420</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>280</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>12.5</v>
       </c>
-      <c r="BD4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BK4" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BP4" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="BT4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>85</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA4" t="n">
         <v>20</v>
       </c>
-      <c r="BU4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -1610,747 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>2.82</v>
       </c>
       <c r="G5" t="n">
-        <v>1.81</v>
+        <v>2.84</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>2.74</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.79</v>
+        <v>2.24</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
-        <v>2.22</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="AA5" t="n">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="AB5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18.5</v>
+        <v>42</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AM5" t="n">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>38</v>
+        <v>16.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG5" t="n">
         <v>20</v>
       </c>
-      <c r="AW5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>85</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>120</v>
-      </c>
       <c r="BH5" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BR5" t="n">
         <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BU5" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="BW5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BX5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="CA5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Corinthians</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CA Platense</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>95</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>80</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>38</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>13</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-05-27 19:06:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Bolivar</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Independiente Rivadavia</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>24</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>9</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-27.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>500</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>25</v>
       </c>
-      <c r="J2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="AR2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG2" t="n">
         <v>1.02</v>
       </c>
-      <c r="N2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="X2" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>290</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>370</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>340</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>34</v>
-      </c>
       <c r="BH2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.65</v>
+        <v>110</v>
       </c>
       <c r="G3" t="n">
-        <v>1.66</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6</v>
+        <v>1.13</v>
       </c>
       <c r="I3" t="n">
-        <v>6.8</v>
+        <v>1.15</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>34</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S3" t="n">
         <v>1.09</v>
       </c>
-      <c r="N3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="T3" t="n">
-        <v>2.24</v>
+        <v>4.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>9.4</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.5</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA3" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS3" t="n">
         <v>48</v>
       </c>
-      <c r="AM3" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>55</v>
-      </c>
       <c r="AT3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AY3" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="BA3" t="n">
-        <v>110</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>46</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>110</v>
+        <v>4.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="BG3" t="n">
-        <v>160</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1000</v>
       </c>
       <c r="G4" t="n">
-        <v>1.77</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>150</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.76</v>
+        <v>4.4</v>
       </c>
       <c r="R4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S4" t="n">
+        <v>34</v>
+      </c>
+      <c r="T4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>100</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>850</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.2</v>
       </c>
-      <c r="S4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AS4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>27</v>
       </c>
-      <c r="AE4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>830</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>410</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>30</v>
-      </c>
       <c r="BA4" t="n">
-        <v>130</v>
+        <v>5.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>16</v>
+        <v>5.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>5.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>65</v>
+        <v>1.07</v>
       </c>
       <c r="BE4" t="n">
-        <v>34</v>
+        <v>5.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>17</v>
+        <v>1.07</v>
       </c>
       <c r="BG4" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.82</v>
+        <v>5.2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.84</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7</v>
+        <v>9.4</v>
       </c>
       <c r="I5" t="n">
-        <v>2.74</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>1.38</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>1.43</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>1.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.54</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF5" t="n">
         <v>8</v>
       </c>
-      <c r="AD5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>24</v>
-      </c>
       <c r="BG5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
